--- a/create_forecast_basic/utils/monitoring_df_fixed_1.xlsx
+++ b/create_forecast_basic/utils/monitoring_df_fixed_1.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1529" uniqueCount="1509">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1543" uniqueCount="1523">
   <si>
     <t>2020</t>
   </si>
@@ -244,22 +244,22 @@
     <t>percentage growth arabs_behined_seperation_wall 2045-2050</t>
   </si>
   <si>
-    <t>percentage growth U_Orthodox age15_24 2020-2025</t>
-  </si>
-  <si>
-    <t>percentage growth U_Orthodox age15_24 2025-2030</t>
-  </si>
-  <si>
-    <t>percentage growth U_Orthodox age15_24 2030-2035</t>
-  </si>
-  <si>
-    <t>percentage growth U_Orthodox age15_24 2035-2040</t>
-  </si>
-  <si>
-    <t>percentage growth U_Orthodox age15_24 2040-2045</t>
-  </si>
-  <si>
-    <t>percentage growth U_Orthodox age15_24 2045-2050</t>
+    <t>percentage growth U_Orthodox age18_24 2020-2025</t>
+  </si>
+  <si>
+    <t>percentage growth U_Orthodox age18_24 2025-2030</t>
+  </si>
+  <si>
+    <t>percentage growth U_Orthodox age18_24 2030-2035</t>
+  </si>
+  <si>
+    <t>percentage growth U_Orthodox age18_24 2035-2040</t>
+  </si>
+  <si>
+    <t>percentage growth U_Orthodox age18_24 2040-2045</t>
+  </si>
+  <si>
+    <t>percentage growth U_Orthodox age18_24 2045-2050</t>
   </si>
   <si>
     <t>percentage growth Arab age20_29 2020-2025</t>
@@ -3166,31 +3166,31 @@
     <t>emp_okev at הר אדר in 2050</t>
   </si>
   <si>
-    <t>emp_okev at הר חברון_x000D_
+    <t>emp_okev at הר חברון_x005F_x000D_
  in 2020</t>
   </si>
   <si>
-    <t>emp_okev at הר חברון_x000D_
+    <t>emp_okev at הר חברון_x005F_x000D_
  in 2025</t>
   </si>
   <si>
-    <t>emp_okev at הר חברון_x000D_
+    <t>emp_okev at הר חברון_x005F_x000D_
  in 2030</t>
   </si>
   <si>
-    <t>emp_okev at הר חברון_x000D_
+    <t>emp_okev at הר חברון_x005F_x000D_
  in 2035</t>
   </si>
   <si>
-    <t>emp_okev at הר חברון_x000D_
+    <t>emp_okev at הר חברון_x005F_x000D_
  in 2040</t>
   </si>
   <si>
-    <t>emp_okev at הר חברון_x000D_
+    <t>emp_okev at הר חברון_x005F_x000D_
  in 2045</t>
   </si>
   <si>
-    <t>emp_okev at הר חברון_x000D_
+    <t>emp_okev at הר חברון_x005F_x000D_
  in 2050</t>
   </si>
   <si>
@@ -3236,31 +3236,31 @@
     <t>emp_okev at מבשרת ציון in 2050</t>
   </si>
   <si>
-    <t>emp_okev at מגילות ים המלח_x000D_
+    <t>emp_okev at מגילות ים המלח_x005F_x000D_
  in 2020</t>
   </si>
   <si>
-    <t>emp_okev at מגילות ים המלח_x000D_
+    <t>emp_okev at מגילות ים המלח_x005F_x000D_
  in 2025</t>
   </si>
   <si>
-    <t>emp_okev at מגילות ים המלח_x000D_
+    <t>emp_okev at מגילות ים המלח_x005F_x000D_
  in 2030</t>
   </si>
   <si>
-    <t>emp_okev at מגילות ים המלח_x000D_
+    <t>emp_okev at מגילות ים המלח_x005F_x000D_
  in 2035</t>
   </si>
   <si>
-    <t>emp_okev at מגילות ים המלח_x000D_
+    <t>emp_okev at מגילות ים המלח_x005F_x000D_
  in 2040</t>
   </si>
   <si>
-    <t>emp_okev at מגילות ים המלח_x000D_
+    <t>emp_okev at מגילות ים המלח_x005F_x000D_
  in 2045</t>
   </si>
   <si>
-    <t>emp_okev at מגילות ים המלח_x000D_
+    <t>emp_okev at מגילות ים המלח_x005F_x000D_
  in 2050</t>
   </si>
   <si>
@@ -3411,31 +3411,31 @@
     <t>emp_okev at עמנואל in 2050</t>
   </si>
   <si>
-    <t>emp_okev at ערבות הירדן_x000D_
+    <t>emp_okev at ערבות הירדן_x005F_x000D_
  in 2020</t>
   </si>
   <si>
-    <t>emp_okev at ערבות הירדן_x000D_
+    <t>emp_okev at ערבות הירדן_x005F_x000D_
  in 2025</t>
   </si>
   <si>
-    <t>emp_okev at ערבות הירדן_x000D_
+    <t>emp_okev at ערבות הירדן_x005F_x000D_
  in 2030</t>
   </si>
   <si>
-    <t>emp_okev at ערבות הירדן_x000D_
+    <t>emp_okev at ערבות הירדן_x005F_x000D_
  in 2035</t>
   </si>
   <si>
-    <t>emp_okev at ערבות הירדן_x000D_
+    <t>emp_okev at ערבות הירדן_x005F_x000D_
  in 2040</t>
   </si>
   <si>
-    <t>emp_okev at ערבות הירדן_x000D_
+    <t>emp_okev at ערבות הירדן_x005F_x000D_
  in 2045</t>
   </si>
   <si>
-    <t>emp_okev at ערבות הירדן_x000D_
+    <t>emp_okev at ערבות הירדן_x005F_x000D_
  in 2050</t>
   </si>
   <si>
@@ -3817,31 +3817,31 @@
     <t>total_emp at הר אדר in 2050</t>
   </si>
   <si>
-    <t>total_emp at הר חברון_x000D_
+    <t>total_emp at הר חברון_x005F_x000D_
  in 2020</t>
   </si>
   <si>
-    <t>total_emp at הר חברון_x000D_
+    <t>total_emp at הר חברון_x005F_x000D_
  in 2025</t>
   </si>
   <si>
-    <t>total_emp at הר חברון_x000D_
+    <t>total_emp at הר חברון_x005F_x000D_
  in 2030</t>
   </si>
   <si>
-    <t>total_emp at הר חברון_x000D_
+    <t>total_emp at הר חברון_x005F_x000D_
  in 2035</t>
   </si>
   <si>
-    <t>total_emp at הר חברון_x000D_
+    <t>total_emp at הר חברון_x005F_x000D_
  in 2040</t>
   </si>
   <si>
-    <t>total_emp at הר חברון_x000D_
+    <t>total_emp at הר חברון_x005F_x000D_
  in 2045</t>
   </si>
   <si>
-    <t>total_emp at הר חברון_x000D_
+    <t>total_emp at הר חברון_x005F_x000D_
  in 2050</t>
   </si>
   <si>
@@ -3887,31 +3887,31 @@
     <t>total_emp at מבשרת ציון in 2050</t>
   </si>
   <si>
-    <t>total_emp at מגילות ים המלח_x000D_
+    <t>total_emp at מגילות ים המלח_x005F_x000D_
  in 2020</t>
   </si>
   <si>
-    <t>total_emp at מגילות ים המלח_x000D_
+    <t>total_emp at מגילות ים המלח_x005F_x000D_
  in 2025</t>
   </si>
   <si>
-    <t>total_emp at מגילות ים המלח_x000D_
+    <t>total_emp at מגילות ים המלח_x005F_x000D_
  in 2030</t>
   </si>
   <si>
-    <t>total_emp at מגילות ים המלח_x000D_
+    <t>total_emp at מגילות ים המלח_x005F_x000D_
  in 2035</t>
   </si>
   <si>
-    <t>total_emp at מגילות ים המלח_x000D_
+    <t>total_emp at מגילות ים המלח_x005F_x000D_
  in 2040</t>
   </si>
   <si>
-    <t>total_emp at מגילות ים המלח_x000D_
+    <t>total_emp at מגילות ים המלח_x005F_x000D_
  in 2045</t>
   </si>
   <si>
-    <t>total_emp at מגילות ים המלח_x000D_
+    <t>total_emp at מגילות ים המלח_x005F_x000D_
  in 2050</t>
   </si>
   <si>
@@ -4062,31 +4062,31 @@
     <t>total_emp at עמנואל in 2050</t>
   </si>
   <si>
-    <t>total_emp at ערבות הירדן_x000D_
+    <t>total_emp at ערבות הירדן_x005F_x000D_
  in 2020</t>
   </si>
   <si>
-    <t>total_emp at ערבות הירדן_x000D_
+    <t>total_emp at ערבות הירדן_x005F_x000D_
  in 2025</t>
   </si>
   <si>
-    <t>total_emp at ערבות הירדן_x000D_
+    <t>total_emp at ערבות הירדן_x005F_x000D_
  in 2030</t>
   </si>
   <si>
-    <t>total_emp at ערבות הירדן_x000D_
+    <t>total_emp at ערבות הירדן_x005F_x000D_
  in 2035</t>
   </si>
   <si>
-    <t>total_emp at ערבות הירדן_x000D_
+    <t>total_emp at ערבות הירדן_x005F_x000D_
  in 2040</t>
   </si>
   <si>
-    <t>total_emp at ערבות הירדן_x000D_
+    <t>total_emp at ערבות הירדן_x005F_x000D_
  in 2045</t>
   </si>
   <si>
-    <t>total_emp at ערבות הירדן_x000D_
+    <t>total_emp at ערבות הירדן_x005F_x000D_
  in 2050</t>
   </si>
   <si>
@@ -4529,6 +4529,48 @@
   </si>
   <si>
     <t>pop division emp_okev at תלפיות מזרח in 2025</t>
+  </si>
+  <si>
+    <t>pop division total_emp in 2020</t>
+  </si>
+  <si>
+    <t>pop division total_emp in 2025</t>
+  </si>
+  <si>
+    <t>pop division total_emp in 2030</t>
+  </si>
+  <si>
+    <t>pop division total_emp in 2035</t>
+  </si>
+  <si>
+    <t>pop division total_emp in 2040</t>
+  </si>
+  <si>
+    <t>pop division total_emp in 2045</t>
+  </si>
+  <si>
+    <t>pop division total_emp in 2050</t>
+  </si>
+  <si>
+    <t>aprt division total_emp in 2020</t>
+  </si>
+  <si>
+    <t>aprt division total_emp in 2025</t>
+  </si>
+  <si>
+    <t>aprt division total_emp in 2030</t>
+  </si>
+  <si>
+    <t>aprt division total_emp in 2035</t>
+  </si>
+  <si>
+    <t>aprt division total_emp in 2040</t>
+  </si>
+  <si>
+    <t>aprt division total_emp in 2045</t>
+  </si>
+  <si>
+    <t>aprt division total_emp in 2050</t>
   </si>
   <si>
     <t>1,758,461</t>
@@ -4940,7 +4982,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E1488"/>
+  <dimension ref="A1:E1502"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -4962,16 +5004,16 @@
         <v>4</v>
       </c>
       <c r="B2" t="s">
-        <v>1491</v>
+        <v>1505</v>
       </c>
       <c r="C2" t="s">
-        <v>1491</v>
+        <v>1505</v>
       </c>
       <c r="D2" t="s">
-        <v>1491</v>
+        <v>1505</v>
       </c>
       <c r="E2" t="s">
-        <v>1491</v>
+        <v>1505</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -4979,13 +5021,13 @@
         <v>5</v>
       </c>
       <c r="C3" t="s">
-        <v>1496</v>
+        <v>1510</v>
       </c>
       <c r="D3" t="s">
-        <v>1501</v>
+        <v>1515</v>
       </c>
       <c r="E3" t="s">
-        <v>1505</v>
+        <v>1519</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -4993,16 +5035,16 @@
         <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>1492</v>
+        <v>1506</v>
       </c>
       <c r="C4" t="s">
-        <v>1492</v>
+        <v>1506</v>
       </c>
       <c r="D4" t="s">
-        <v>1492</v>
+        <v>1506</v>
       </c>
       <c r="E4" t="s">
-        <v>1492</v>
+        <v>1506</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -5010,13 +5052,13 @@
         <v>7</v>
       </c>
       <c r="C5" t="s">
-        <v>1497</v>
+        <v>1511</v>
       </c>
       <c r="D5" t="s">
-        <v>1502</v>
+        <v>1516</v>
       </c>
       <c r="E5" t="s">
-        <v>1506</v>
+        <v>1520</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -5109,16 +5151,16 @@
         <v>13</v>
       </c>
       <c r="B11" t="s">
-        <v>1493</v>
+        <v>1507</v>
       </c>
       <c r="C11" t="s">
-        <v>1493</v>
+        <v>1507</v>
       </c>
       <c r="D11" t="s">
-        <v>1493</v>
+        <v>1507</v>
       </c>
       <c r="E11" t="s">
-        <v>1493</v>
+        <v>1507</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -5126,13 +5168,13 @@
         <v>14</v>
       </c>
       <c r="C12" t="s">
-        <v>1493</v>
+        <v>1507</v>
       </c>
       <c r="D12" t="s">
-        <v>1493</v>
+        <v>1507</v>
       </c>
       <c r="E12" t="s">
-        <v>1493</v>
+        <v>1507</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -5140,16 +5182,16 @@
         <v>15</v>
       </c>
       <c r="B13" t="s">
-        <v>1494</v>
+        <v>1508</v>
       </c>
       <c r="C13" t="s">
-        <v>1494</v>
+        <v>1508</v>
       </c>
       <c r="D13" t="s">
-        <v>1494</v>
+        <v>1508</v>
       </c>
       <c r="E13" t="s">
-        <v>1494</v>
+        <v>1508</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -5157,13 +5199,13 @@
         <v>16</v>
       </c>
       <c r="C14" t="s">
-        <v>1498</v>
+        <v>1512</v>
       </c>
       <c r="D14" t="s">
-        <v>1503</v>
+        <v>1517</v>
       </c>
       <c r="E14" t="s">
-        <v>1507</v>
+        <v>1521</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -5171,16 +5213,16 @@
         <v>17</v>
       </c>
       <c r="B15" t="s">
-        <v>1495</v>
+        <v>1509</v>
       </c>
       <c r="C15" t="s">
-        <v>1495</v>
+        <v>1509</v>
       </c>
       <c r="D15" t="s">
-        <v>1495</v>
+        <v>1509</v>
       </c>
       <c r="E15" t="s">
-        <v>1495</v>
+        <v>1509</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -5188,13 +5230,13 @@
         <v>18</v>
       </c>
       <c r="C16" t="s">
-        <v>1499</v>
+        <v>1513</v>
       </c>
       <c r="D16" t="s">
-        <v>1504</v>
+        <v>1518</v>
       </c>
       <c r="E16" t="s">
-        <v>1508</v>
+        <v>1522</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -5355,10 +5397,10 @@
         <v>28</v>
       </c>
       <c r="C26">
-        <v>188.1410644079084</v>
+        <v>188.1410644079083</v>
       </c>
       <c r="D26">
-        <v>183.9696620191286</v>
+        <v>183.9696620191285</v>
       </c>
       <c r="E26">
         <v>185.6774324006336</v>
@@ -5635,13 +5677,13 @@
         <v>48</v>
       </c>
       <c r="C46" t="s">
-        <v>1500</v>
+        <v>1514</v>
       </c>
       <c r="D46" t="s">
-        <v>1500</v>
+        <v>1514</v>
       </c>
       <c r="E46" t="s">
-        <v>1500</v>
+        <v>1514</v>
       </c>
     </row>
     <row r="47" spans="1:5">
@@ -6027,13 +6069,13 @@
         <v>76</v>
       </c>
       <c r="C74">
-        <v>42.09690954865545</v>
+        <v>41.54781713017986</v>
       </c>
       <c r="D74">
-        <v>40.43492538402597</v>
+        <v>37.86546232469693</v>
       </c>
       <c r="E74">
-        <v>43.61020907067537</v>
+        <v>41.29394131473998</v>
       </c>
     </row>
     <row r="75" spans="1:5">
@@ -6041,13 +6083,13 @@
         <v>77</v>
       </c>
       <c r="C75">
-        <v>15.77758091643236</v>
+        <v>16.20276428907952</v>
       </c>
       <c r="D75">
-        <v>12.02811192808335</v>
+        <v>11.45833333333333</v>
       </c>
       <c r="E75">
-        <v>15.17559404714267</v>
+        <v>14.76593805857682</v>
       </c>
     </row>
     <row r="76" spans="1:5">
@@ -6055,13 +6097,13 @@
         <v>78</v>
       </c>
       <c r="C76">
-        <v>14.69593470691299</v>
+        <v>14.92200295449436</v>
       </c>
       <c r="D76">
-        <v>17.6768672379605</v>
+        <v>15.38038457406811</v>
       </c>
       <c r="E76">
-        <v>20.61501469704239</v>
+        <v>18.26719681746647</v>
       </c>
     </row>
     <row r="77" spans="1:5">
@@ -6069,13 +6111,13 @@
         <v>79</v>
       </c>
       <c r="C77">
-        <v>9.364742508254336</v>
+        <v>9.228582057359025</v>
       </c>
       <c r="D77">
-        <v>16.96278121027581</v>
+        <v>18.89400750040033</v>
       </c>
       <c r="E77">
-        <v>21.28160577934251</v>
+        <v>22.99735241157777</v>
       </c>
     </row>
     <row r="78" spans="1:5">
@@ -6083,13 +6125,13 @@
         <v>80</v>
       </c>
       <c r="C78">
-        <v>18.44823699460291</v>
+        <v>22.02142917674674</v>
       </c>
       <c r="D78">
-        <v>14.17119507982644</v>
+        <v>14.86172408716597</v>
       </c>
       <c r="E78">
-        <v>18.17684869276734</v>
+        <v>18.55999798460181</v>
       </c>
     </row>
     <row r="79" spans="1:5">
@@ -6097,13 +6139,13 @@
         <v>81</v>
       </c>
       <c r="C79">
-        <v>6.347749179942457</v>
+        <v>6.722550328710719</v>
       </c>
       <c r="D79">
-        <v>12.19823562618298</v>
+        <v>12.95406729488314</v>
       </c>
       <c r="E79">
-        <v>16.27268957156985</v>
+        <v>16.97984913411482</v>
       </c>
     </row>
     <row r="80" spans="1:5">
@@ -25830,6 +25872,202 @@
       </c>
       <c r="E1488">
         <v>5.208887551814326</v>
+      </c>
+    </row>
+    <row r="1489" spans="1:5">
+      <c r="A1489" s="1" t="s">
+        <v>1491</v>
+      </c>
+      <c r="C1489">
+        <v>0.274510590027404</v>
+      </c>
+      <c r="D1489">
+        <v>0.274510590027404</v>
+      </c>
+      <c r="E1489">
+        <v>0.274510590027404</v>
+      </c>
+    </row>
+    <row r="1490" spans="1:5">
+      <c r="A1490" s="1" t="s">
+        <v>1492</v>
+      </c>
+      <c r="C1490">
+        <v>0.1085610779961064</v>
+      </c>
+      <c r="D1490">
+        <v>0.1042627101407602</v>
+      </c>
+      <c r="E1490">
+        <v>0.1051127003854925</v>
+      </c>
+    </row>
+    <row r="1491" spans="1:5">
+      <c r="A1491" s="1" t="s">
+        <v>1493</v>
+      </c>
+      <c r="C1491">
+        <v>0.1125054369322683</v>
+      </c>
+      <c r="D1491">
+        <v>0.1060000485240958</v>
+      </c>
+      <c r="E1491">
+        <v>0.108259127712942</v>
+      </c>
+    </row>
+    <row r="1492" spans="1:5">
+      <c r="A1492" s="1" t="s">
+        <v>1494</v>
+      </c>
+      <c r="C1492">
+        <v>0.117776582480796</v>
+      </c>
+      <c r="D1492">
+        <v>0.1088794149716449</v>
+      </c>
+      <c r="E1492">
+        <v>0.1124915624920027</v>
+      </c>
+    </row>
+    <row r="1493" spans="1:5">
+      <c r="A1493" s="1" t="s">
+        <v>1495</v>
+      </c>
+      <c r="C1493">
+        <v>0.1227534623323177</v>
+      </c>
+      <c r="D1493">
+        <v>0.1111431609688907</v>
+      </c>
+      <c r="E1493">
+        <v>0.1165598777550276</v>
+      </c>
+    </row>
+    <row r="1494" spans="1:5">
+      <c r="A1494" s="1" t="s">
+        <v>1496</v>
+      </c>
+      <c r="C1494">
+        <v>0.1292444792424143</v>
+      </c>
+      <c r="D1494">
+        <v>0.1129801244081925</v>
+      </c>
+      <c r="E1494">
+        <v>0.1202497001616002</v>
+      </c>
+    </row>
+    <row r="1495" spans="1:5">
+      <c r="A1495" s="1" t="s">
+        <v>1497</v>
+      </c>
+      <c r="C1495">
+        <v>0.1309869731098417</v>
+      </c>
+      <c r="D1495">
+        <v>0.1150036371136272</v>
+      </c>
+      <c r="E1495">
+        <v>0.1240135292494374</v>
+      </c>
+    </row>
+    <row r="1496" spans="1:5">
+      <c r="A1496" s="1" t="s">
+        <v>1498</v>
+      </c>
+      <c r="C1496">
+        <v>1.114079232346069</v>
+      </c>
+      <c r="D1496">
+        <v>1.114079232346069</v>
+      </c>
+      <c r="E1496">
+        <v>1.114079232346069</v>
+      </c>
+    </row>
+    <row r="1497" spans="1:5">
+      <c r="A1497" s="1" t="s">
+        <v>1499</v>
+      </c>
+      <c r="C1497">
+        <v>1.159182665523671</v>
+      </c>
+      <c r="D1497">
+        <v>1.144472910686225</v>
+      </c>
+      <c r="E1497">
+        <v>1.14517662824113</v>
+      </c>
+    </row>
+    <row r="1498" spans="1:5">
+      <c r="A1498" s="1" t="s">
+        <v>1500</v>
+      </c>
+      <c r="C1498">
+        <v>1.188754352991139</v>
+      </c>
+      <c r="D1498">
+        <v>1.173077736396925</v>
+      </c>
+      <c r="E1498">
+        <v>1.174263741817146</v>
+      </c>
+    </row>
+    <row r="1499" spans="1:5">
+      <c r="A1499" s="1" t="s">
+        <v>1501</v>
+      </c>
+      <c r="C1499">
+        <v>1.218643112621387</v>
+      </c>
+      <c r="D1499">
+        <v>1.206558686088572</v>
+      </c>
+      <c r="E1499">
+        <v>1.208720333611625</v>
+      </c>
+    </row>
+    <row r="1500" spans="1:5">
+      <c r="A1500" s="1" t="s">
+        <v>1502</v>
+      </c>
+      <c r="C1500">
+        <v>1.243413157309403</v>
+      </c>
+      <c r="D1500">
+        <v>1.23518656648838</v>
+      </c>
+      <c r="E1500">
+        <v>1.239806494952869</v>
+      </c>
+    </row>
+    <row r="1501" spans="1:5">
+      <c r="A1501" s="1" t="s">
+        <v>1503</v>
+      </c>
+      <c r="C1501">
+        <v>1.300436413012383</v>
+      </c>
+      <c r="D1501">
+        <v>1.252104471481292</v>
+      </c>
+      <c r="E1501">
+        <v>1.263459048274382</v>
+      </c>
+    </row>
+    <row r="1502" spans="1:5">
+      <c r="A1502" s="1" t="s">
+        <v>1504</v>
+      </c>
+      <c r="C1502">
+        <v>1.329352210290853</v>
+      </c>
+      <c r="D1502">
+        <v>1.275333581933721</v>
+      </c>
+      <c r="E1502">
+        <v>1.291052166578559</v>
       </c>
     </row>
   </sheetData>

--- a/create_forecast_basic/utils/monitoring_df_fixed_1.xlsx
+++ b/create_forecast_basic/utils/monitoring_df_fixed_1.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1543" uniqueCount="1523">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1891" uniqueCount="1859">
   <si>
     <t>2020</t>
   </si>
@@ -154,94 +154,94 @@
     <t>percentage growth student_yeshiva_and_kollim 2045-2050</t>
   </si>
   <si>
-    <t>percentage growth Arab 2020-2025</t>
-  </si>
-  <si>
-    <t>percentage growth Jewish 2020-2025</t>
-  </si>
-  <si>
-    <t>percentage growth Palestinian 2020-2025</t>
-  </si>
-  <si>
-    <t>percentage growth U_Orthodox 2020-2025</t>
-  </si>
-  <si>
-    <t>percentage growth arabs_behined_seperation_wall 2020-2025</t>
-  </si>
-  <si>
-    <t>percentage growth Arab 2025-2030</t>
-  </si>
-  <si>
-    <t>percentage growth Jewish 2025-2030</t>
-  </si>
-  <si>
-    <t>percentage growth Palestinian 2025-2030</t>
-  </si>
-  <si>
-    <t>percentage growth U_Orthodox 2025-2030</t>
-  </si>
-  <si>
-    <t>percentage growth arabs_behined_seperation_wall 2025-2030</t>
-  </si>
-  <si>
-    <t>percentage growth Arab 2030-2035</t>
-  </si>
-  <si>
-    <t>percentage growth Jewish 2030-2035</t>
-  </si>
-  <si>
-    <t>percentage growth Palestinian 2030-2035</t>
-  </si>
-  <si>
-    <t>percentage growth U_Orthodox 2030-2035</t>
-  </si>
-  <si>
-    <t>percentage growth arabs_behined_seperation_wall 2030-2035</t>
-  </si>
-  <si>
-    <t>percentage growth Arab 2035-2040</t>
-  </si>
-  <si>
-    <t>percentage growth Jewish 2035-2040</t>
-  </si>
-  <si>
-    <t>percentage growth Palestinian 2035-2040</t>
-  </si>
-  <si>
-    <t>percentage growth U_Orthodox 2035-2040</t>
-  </si>
-  <si>
-    <t>percentage growth arabs_behined_seperation_wall 2035-2040</t>
-  </si>
-  <si>
-    <t>percentage growth Arab 2040-2045</t>
-  </si>
-  <si>
-    <t>percentage growth Jewish 2040-2045</t>
-  </si>
-  <si>
-    <t>percentage growth Palestinian 2040-2045</t>
-  </si>
-  <si>
-    <t>percentage growth U_Orthodox 2040-2045</t>
-  </si>
-  <si>
-    <t>percentage growth arabs_behined_seperation_wall 2040-2045</t>
-  </si>
-  <si>
-    <t>percentage growth Arab 2045-2050</t>
-  </si>
-  <si>
-    <t>percentage growth Jewish 2045-2050</t>
-  </si>
-  <si>
-    <t>percentage growth Palestinian 2045-2050</t>
-  </si>
-  <si>
-    <t>percentage growth U_Orthodox 2045-2050</t>
-  </si>
-  <si>
-    <t>percentage growth arabs_behined_seperation_wall 2045-2050</t>
+    <t>percentage growth sector Arab 2020-2025</t>
+  </si>
+  <si>
+    <t>percentage growth sector Jewish 2020-2025</t>
+  </si>
+  <si>
+    <t>percentage growth sector Palestinian 2020-2025</t>
+  </si>
+  <si>
+    <t>percentage growth sector U_Orthodox 2020-2025</t>
+  </si>
+  <si>
+    <t>percentage growth sector arabs_behined_seperation_wall 2020-2025</t>
+  </si>
+  <si>
+    <t>percentage growth sector Arab 2025-2030</t>
+  </si>
+  <si>
+    <t>percentage growth sector Jewish 2025-2030</t>
+  </si>
+  <si>
+    <t>percentage growth sector Palestinian 2025-2030</t>
+  </si>
+  <si>
+    <t>percentage growth sector U_Orthodox 2025-2030</t>
+  </si>
+  <si>
+    <t>percentage growth sector arabs_behined_seperation_wall 2025-2030</t>
+  </si>
+  <si>
+    <t>percentage growth sector Arab 2030-2035</t>
+  </si>
+  <si>
+    <t>percentage growth sector Jewish 2030-2035</t>
+  </si>
+  <si>
+    <t>percentage growth sector Palestinian 2030-2035</t>
+  </si>
+  <si>
+    <t>percentage growth sector U_Orthodox 2030-2035</t>
+  </si>
+  <si>
+    <t>percentage growth sector arabs_behined_seperation_wall 2030-2035</t>
+  </si>
+  <si>
+    <t>percentage growth sector Arab 2035-2040</t>
+  </si>
+  <si>
+    <t>percentage growth sector Jewish 2035-2040</t>
+  </si>
+  <si>
+    <t>percentage growth sector Palestinian 2035-2040</t>
+  </si>
+  <si>
+    <t>percentage growth sector U_Orthodox 2035-2040</t>
+  </si>
+  <si>
+    <t>percentage growth sector arabs_behined_seperation_wall 2035-2040</t>
+  </si>
+  <si>
+    <t>percentage growth sector Arab 2040-2045</t>
+  </si>
+  <si>
+    <t>percentage growth sector Jewish 2040-2045</t>
+  </si>
+  <si>
+    <t>percentage growth sector Palestinian 2040-2045</t>
+  </si>
+  <si>
+    <t>percentage growth sector U_Orthodox 2040-2045</t>
+  </si>
+  <si>
+    <t>percentage growth sector arabs_behined_seperation_wall 2040-2045</t>
+  </si>
+  <si>
+    <t>percentage growth sector Arab 2045-2050</t>
+  </si>
+  <si>
+    <t>percentage growth sector Jewish 2045-2050</t>
+  </si>
+  <si>
+    <t>percentage growth sector Palestinian 2045-2050</t>
+  </si>
+  <si>
+    <t>percentage growth sector U_Orthodox 2045-2050</t>
+  </si>
+  <si>
+    <t>percentage growth sector arabs_behined_seperation_wall 2045-2050</t>
   </si>
   <si>
     <t>percentage growth U_Orthodox age18_24 2020-2025</t>
@@ -4571,6 +4571,1014 @@
   </si>
   <si>
     <t>aprt division total_emp in 2050</t>
+  </si>
+  <si>
+    <t>percentage growth emp education 0 2020-2025</t>
+  </si>
+  <si>
+    <t>percentage growth emp education א-טור 2020-2025</t>
+  </si>
+  <si>
+    <t>percentage growth emp education אבו טור סילוא 2020-2025</t>
+  </si>
+  <si>
+    <t>percentage growth emp education אזור תעשיה גב 2020-2025</t>
+  </si>
+  <si>
+    <t>percentage growth emp education אזור תעשיה עט 2020-2025</t>
+  </si>
+  <si>
+    <t>percentage growth emp education בית הכרם 2020-2025</t>
+  </si>
+  <si>
+    <t>percentage growth emp education בית צפפא,שרפת 2020-2025</t>
+  </si>
+  <si>
+    <t>percentage growth emp education בקעה מושבות 2020-2025</t>
+  </si>
+  <si>
+    <t>percentage growth emp education גבעת המטוס 2020-2025</t>
+  </si>
+  <si>
+    <t>percentage growth emp education גבעת משואה 2020-2025</t>
+  </si>
+  <si>
+    <t>percentage growth emp education גילה 2020-2025</t>
+  </si>
+  <si>
+    <t>percentage growth emp education הגבעה הצרפתי 2020-2025</t>
+  </si>
+  <si>
+    <t>percentage growth emp education העיר העתיקה 2020-2025</t>
+  </si>
+  <si>
+    <t>percentage growth emp education הקריות של ירו 2020-2025</t>
+  </si>
+  <si>
+    <t>percentage growth emp education הר החוצבים 2020-2025</t>
+  </si>
+  <si>
+    <t>percentage growth emp education הר הצופים 2020-2025</t>
+  </si>
+  <si>
+    <t>percentage growth emp education הר נוף 2020-2025</t>
+  </si>
+  <si>
+    <t>percentage growth emp education חומת שמואל - ה 2020-2025</t>
+  </si>
+  <si>
+    <t>percentage growth emp education חומת שמואל-מע 2020-2025</t>
+  </si>
+  <si>
+    <t>percentage growth emp education טלביה רחביה 2020-2025</t>
+  </si>
+  <si>
+    <t>percentage growth emp education יובלים גנים 2020-2025</t>
+  </si>
+  <si>
+    <t>percentage growth emp education כניסה לעיר 2020-2025</t>
+  </si>
+  <si>
+    <t>percentage growth emp education כניסה לעיר - ק 2020-2025</t>
+  </si>
+  <si>
+    <t>percentage growth emp education כפר עקב 2020-2025</t>
+  </si>
+  <si>
+    <t>percentage growth emp education מורשה 2020-2025</t>
+  </si>
+  <si>
+    <t>percentage growth emp education מחנה שועפט 2020-2025</t>
+  </si>
+  <si>
+    <t>percentage growth emp education מנחת - מלחה 2020-2025</t>
+  </si>
+  <si>
+    <t>percentage growth emp education מעלות דפנה 2020-2025</t>
+  </si>
+  <si>
+    <t>percentage growth emp education מער 2020-2025</t>
+  </si>
+  <si>
+    <t>percentage growth emp education מער חרדי 2020-2025</t>
+  </si>
+  <si>
+    <t>percentage growth emp education מער מזרח ואדי 2020-2025</t>
+  </si>
+  <si>
+    <t>percentage growth emp education מקור ברוך 2020-2025</t>
+  </si>
+  <si>
+    <t>percentage growth emp education מרכז רפואי הד 2020-2025</t>
+  </si>
+  <si>
+    <t>percentage growth emp education נוה יעקב 2020-2025</t>
+  </si>
+  <si>
+    <t>percentage growth emp education נחלאות שערי ח 2020-2025</t>
+  </si>
+  <si>
+    <t>percentage growth emp education ניות -גבעת מר 2020-2025</t>
+  </si>
+  <si>
+    <t>percentage growth emp education סנהדריה רמת א 2020-2025</t>
+  </si>
+  <si>
+    <t>percentage growth emp education עין כרם 2020-2025</t>
+  </si>
+  <si>
+    <t>percentage growth emp education עיסאוויה 2020-2025</t>
+  </si>
+  <si>
+    <t>percentage growth emp education פסגת זאב 2020-2025</t>
+  </si>
+  <si>
+    <t>percentage growth emp education פת - קטמונים 2020-2025</t>
+  </si>
+  <si>
+    <t>percentage growth emp education צור באהר מורח 2020-2025</t>
+  </si>
+  <si>
+    <t>percentage growth emp education קטמון הישנה 2020-2025</t>
+  </si>
+  <si>
+    <t>percentage growth emp education קריית הממשלה- 2020-2025</t>
+  </si>
+  <si>
+    <t>percentage growth emp education קריית משה -גב 2020-2025</t>
+  </si>
+  <si>
+    <t>percentage growth emp education ראס אל עמד - ג' 2020-2025</t>
+  </si>
+  <si>
+    <t>percentage growth emp education רכס לבן 2020-2025</t>
+  </si>
+  <si>
+    <t>percentage growth emp education רמות 2020-2025</t>
+  </si>
+  <si>
+    <t>percentage growth emp education רמת שלמה 2020-2025</t>
+  </si>
+  <si>
+    <t>percentage growth emp education רמת שרת - בית 2020-2025</t>
+  </si>
+  <si>
+    <t>percentage growth emp education רסקו 2020-2025</t>
+  </si>
+  <si>
+    <t>percentage growth emp education שדה התעופה עט 2020-2025</t>
+  </si>
+  <si>
+    <t>percentage growth emp education שועפאט - בית 2020-2025</t>
+  </si>
+  <si>
+    <t>percentage growth emp education תלפיות 2020-2025</t>
+  </si>
+  <si>
+    <t>percentage growth emp education תלפיות ארנונ 2020-2025</t>
+  </si>
+  <si>
+    <t>percentage growth emp education תלפיות מזרח 2020-2025</t>
+  </si>
+  <si>
+    <t>percentage growth emp education 0 2025-2030</t>
+  </si>
+  <si>
+    <t>percentage growth emp education א-טור 2025-2030</t>
+  </si>
+  <si>
+    <t>percentage growth emp education אבו טור סילוא 2025-2030</t>
+  </si>
+  <si>
+    <t>percentage growth emp education אזור תעשיה גב 2025-2030</t>
+  </si>
+  <si>
+    <t>percentage growth emp education אזור תעשיה עט 2025-2030</t>
+  </si>
+  <si>
+    <t>percentage growth emp education בית הכרם 2025-2030</t>
+  </si>
+  <si>
+    <t>percentage growth emp education בית צפפא,שרפת 2025-2030</t>
+  </si>
+  <si>
+    <t>percentage growth emp education בקעה מושבות 2025-2030</t>
+  </si>
+  <si>
+    <t>percentage growth emp education גבעת המטוס 2025-2030</t>
+  </si>
+  <si>
+    <t>percentage growth emp education גבעת משואה 2025-2030</t>
+  </si>
+  <si>
+    <t>percentage growth emp education גילה 2025-2030</t>
+  </si>
+  <si>
+    <t>percentage growth emp education הגבעה הצרפתי 2025-2030</t>
+  </si>
+  <si>
+    <t>percentage growth emp education העיר העתיקה 2025-2030</t>
+  </si>
+  <si>
+    <t>percentage growth emp education הקריות של ירו 2025-2030</t>
+  </si>
+  <si>
+    <t>percentage growth emp education הר החוצבים 2025-2030</t>
+  </si>
+  <si>
+    <t>percentage growth emp education הר הצופים 2025-2030</t>
+  </si>
+  <si>
+    <t>percentage growth emp education הר נוף 2025-2030</t>
+  </si>
+  <si>
+    <t>percentage growth emp education חומת שמואל - ה 2025-2030</t>
+  </si>
+  <si>
+    <t>percentage growth emp education חומת שמואל-מע 2025-2030</t>
+  </si>
+  <si>
+    <t>percentage growth emp education טלביה רחביה 2025-2030</t>
+  </si>
+  <si>
+    <t>percentage growth emp education יובלים גנים 2025-2030</t>
+  </si>
+  <si>
+    <t>percentage growth emp education כניסה לעיר 2025-2030</t>
+  </si>
+  <si>
+    <t>percentage growth emp education כניסה לעיר - ק 2025-2030</t>
+  </si>
+  <si>
+    <t>percentage growth emp education כפר עקב 2025-2030</t>
+  </si>
+  <si>
+    <t>percentage growth emp education מורשה 2025-2030</t>
+  </si>
+  <si>
+    <t>percentage growth emp education מחנה שועפט 2025-2030</t>
+  </si>
+  <si>
+    <t>percentage growth emp education מנחת - מלחה 2025-2030</t>
+  </si>
+  <si>
+    <t>percentage growth emp education מעלות דפנה 2025-2030</t>
+  </si>
+  <si>
+    <t>percentage growth emp education מער 2025-2030</t>
+  </si>
+  <si>
+    <t>percentage growth emp education מער חרדי 2025-2030</t>
+  </si>
+  <si>
+    <t>percentage growth emp education מער מזרח ואדי 2025-2030</t>
+  </si>
+  <si>
+    <t>percentage growth emp education מקור ברוך 2025-2030</t>
+  </si>
+  <si>
+    <t>percentage growth emp education מרכז רפואי הד 2025-2030</t>
+  </si>
+  <si>
+    <t>percentage growth emp education נוה יעקב 2025-2030</t>
+  </si>
+  <si>
+    <t>percentage growth emp education נחלאות שערי ח 2025-2030</t>
+  </si>
+  <si>
+    <t>percentage growth emp education ניות -גבעת מר 2025-2030</t>
+  </si>
+  <si>
+    <t>percentage growth emp education סנהדריה רמת א 2025-2030</t>
+  </si>
+  <si>
+    <t>percentage growth emp education עין כרם 2025-2030</t>
+  </si>
+  <si>
+    <t>percentage growth emp education עיסאוויה 2025-2030</t>
+  </si>
+  <si>
+    <t>percentage growth emp education פסגת זאב 2025-2030</t>
+  </si>
+  <si>
+    <t>percentage growth emp education פת - קטמונים 2025-2030</t>
+  </si>
+  <si>
+    <t>percentage growth emp education צור באהר מורח 2025-2030</t>
+  </si>
+  <si>
+    <t>percentage growth emp education קטמון הישנה 2025-2030</t>
+  </si>
+  <si>
+    <t>percentage growth emp education קריית הממשלה- 2025-2030</t>
+  </si>
+  <si>
+    <t>percentage growth emp education קריית משה -גב 2025-2030</t>
+  </si>
+  <si>
+    <t>percentage growth emp education ראס אל עמד - ג' 2025-2030</t>
+  </si>
+  <si>
+    <t>percentage growth emp education רכס לבן 2025-2030</t>
+  </si>
+  <si>
+    <t>percentage growth emp education רמות 2025-2030</t>
+  </si>
+  <si>
+    <t>percentage growth emp education רמת שלמה 2025-2030</t>
+  </si>
+  <si>
+    <t>percentage growth emp education רמת שרת - בית 2025-2030</t>
+  </si>
+  <si>
+    <t>percentage growth emp education רסקו 2025-2030</t>
+  </si>
+  <si>
+    <t>percentage growth emp education שדה התעופה עט 2025-2030</t>
+  </si>
+  <si>
+    <t>percentage growth emp education שועפאט - בית 2025-2030</t>
+  </si>
+  <si>
+    <t>percentage growth emp education תלפיות 2025-2030</t>
+  </si>
+  <si>
+    <t>percentage growth emp education תלפיות ארנונ 2025-2030</t>
+  </si>
+  <si>
+    <t>percentage growth emp education תלפיות מזרח 2025-2030</t>
+  </si>
+  <si>
+    <t>percentage growth emp education 0 2030-2035</t>
+  </si>
+  <si>
+    <t>percentage growth emp education א-טור 2030-2035</t>
+  </si>
+  <si>
+    <t>percentage growth emp education אבו טור סילוא 2030-2035</t>
+  </si>
+  <si>
+    <t>percentage growth emp education אזור תעשיה גב 2030-2035</t>
+  </si>
+  <si>
+    <t>percentage growth emp education אזור תעשיה עט 2030-2035</t>
+  </si>
+  <si>
+    <t>percentage growth emp education בית הכרם 2030-2035</t>
+  </si>
+  <si>
+    <t>percentage growth emp education בית צפפא,שרפת 2030-2035</t>
+  </si>
+  <si>
+    <t>percentage growth emp education בקעה מושבות 2030-2035</t>
+  </si>
+  <si>
+    <t>percentage growth emp education גבעת המטוס 2030-2035</t>
+  </si>
+  <si>
+    <t>percentage growth emp education גבעת משואה 2030-2035</t>
+  </si>
+  <si>
+    <t>percentage growth emp education גילה 2030-2035</t>
+  </si>
+  <si>
+    <t>percentage growth emp education הגבעה הצרפתי 2030-2035</t>
+  </si>
+  <si>
+    <t>percentage growth emp education העיר העתיקה 2030-2035</t>
+  </si>
+  <si>
+    <t>percentage growth emp education הקריות של ירו 2030-2035</t>
+  </si>
+  <si>
+    <t>percentage growth emp education הר החוצבים 2030-2035</t>
+  </si>
+  <si>
+    <t>percentage growth emp education הר הצופים 2030-2035</t>
+  </si>
+  <si>
+    <t>percentage growth emp education הר נוף 2030-2035</t>
+  </si>
+  <si>
+    <t>percentage growth emp education חומת שמואל - ה 2030-2035</t>
+  </si>
+  <si>
+    <t>percentage growth emp education חומת שמואל-מע 2030-2035</t>
+  </si>
+  <si>
+    <t>percentage growth emp education טלביה רחביה 2030-2035</t>
+  </si>
+  <si>
+    <t>percentage growth emp education יובלים גנים 2030-2035</t>
+  </si>
+  <si>
+    <t>percentage growth emp education כניסה לעיר 2030-2035</t>
+  </si>
+  <si>
+    <t>percentage growth emp education כניסה לעיר - ק 2030-2035</t>
+  </si>
+  <si>
+    <t>percentage growth emp education כפר עקב 2030-2035</t>
+  </si>
+  <si>
+    <t>percentage growth emp education מורשה 2030-2035</t>
+  </si>
+  <si>
+    <t>percentage growth emp education מחנה שועפט 2030-2035</t>
+  </si>
+  <si>
+    <t>percentage growth emp education מנחת - מלחה 2030-2035</t>
+  </si>
+  <si>
+    <t>percentage growth emp education מעלות דפנה 2030-2035</t>
+  </si>
+  <si>
+    <t>percentage growth emp education מער 2030-2035</t>
+  </si>
+  <si>
+    <t>percentage growth emp education מער חרדי 2030-2035</t>
+  </si>
+  <si>
+    <t>percentage growth emp education מער מזרח ואדי 2030-2035</t>
+  </si>
+  <si>
+    <t>percentage growth emp education מקור ברוך 2030-2035</t>
+  </si>
+  <si>
+    <t>percentage growth emp education מרכז רפואי הד 2030-2035</t>
+  </si>
+  <si>
+    <t>percentage growth emp education נוה יעקב 2030-2035</t>
+  </si>
+  <si>
+    <t>percentage growth emp education נחלאות שערי ח 2030-2035</t>
+  </si>
+  <si>
+    <t>percentage growth emp education ניות -גבעת מר 2030-2035</t>
+  </si>
+  <si>
+    <t>percentage growth emp education סנהדריה רמת א 2030-2035</t>
+  </si>
+  <si>
+    <t>percentage growth emp education עין כרם 2030-2035</t>
+  </si>
+  <si>
+    <t>percentage growth emp education עיסאוויה 2030-2035</t>
+  </si>
+  <si>
+    <t>percentage growth emp education פסגת זאב 2030-2035</t>
+  </si>
+  <si>
+    <t>percentage growth emp education פת - קטמונים 2030-2035</t>
+  </si>
+  <si>
+    <t>percentage growth emp education צור באהר מורח 2030-2035</t>
+  </si>
+  <si>
+    <t>percentage growth emp education קטמון הישנה 2030-2035</t>
+  </si>
+  <si>
+    <t>percentage growth emp education קריית הממשלה- 2030-2035</t>
+  </si>
+  <si>
+    <t>percentage growth emp education קריית משה -גב 2030-2035</t>
+  </si>
+  <si>
+    <t>percentage growth emp education ראס אל עמד - ג' 2030-2035</t>
+  </si>
+  <si>
+    <t>percentage growth emp education רכס לבן 2030-2035</t>
+  </si>
+  <si>
+    <t>percentage growth emp education רמות 2030-2035</t>
+  </si>
+  <si>
+    <t>percentage growth emp education רמת שלמה 2030-2035</t>
+  </si>
+  <si>
+    <t>percentage growth emp education רמת שרת - בית 2030-2035</t>
+  </si>
+  <si>
+    <t>percentage growth emp education רסקו 2030-2035</t>
+  </si>
+  <si>
+    <t>percentage growth emp education שדה התעופה עט 2030-2035</t>
+  </si>
+  <si>
+    <t>percentage growth emp education שועפאט - בית 2030-2035</t>
+  </si>
+  <si>
+    <t>percentage growth emp education תלפיות 2030-2035</t>
+  </si>
+  <si>
+    <t>percentage growth emp education תלפיות ארנונ 2030-2035</t>
+  </si>
+  <si>
+    <t>percentage growth emp education תלפיות מזרח 2030-2035</t>
+  </si>
+  <si>
+    <t>percentage growth emp education 0 2035-2040</t>
+  </si>
+  <si>
+    <t>percentage growth emp education א-טור 2035-2040</t>
+  </si>
+  <si>
+    <t>percentage growth emp education אבו טור סילוא 2035-2040</t>
+  </si>
+  <si>
+    <t>percentage growth emp education אזור תעשיה גב 2035-2040</t>
+  </si>
+  <si>
+    <t>percentage growth emp education אזור תעשיה עט 2035-2040</t>
+  </si>
+  <si>
+    <t>percentage growth emp education בית הכרם 2035-2040</t>
+  </si>
+  <si>
+    <t>percentage growth emp education בית צפפא,שרפת 2035-2040</t>
+  </si>
+  <si>
+    <t>percentage growth emp education בקעה מושבות 2035-2040</t>
+  </si>
+  <si>
+    <t>percentage growth emp education גבעת המטוס 2035-2040</t>
+  </si>
+  <si>
+    <t>percentage growth emp education גבעת משואה 2035-2040</t>
+  </si>
+  <si>
+    <t>percentage growth emp education גילה 2035-2040</t>
+  </si>
+  <si>
+    <t>percentage growth emp education הגבעה הצרפתי 2035-2040</t>
+  </si>
+  <si>
+    <t>percentage growth emp education העיר העתיקה 2035-2040</t>
+  </si>
+  <si>
+    <t>percentage growth emp education הקריות של ירו 2035-2040</t>
+  </si>
+  <si>
+    <t>percentage growth emp education הר החוצבים 2035-2040</t>
+  </si>
+  <si>
+    <t>percentage growth emp education הר הצופים 2035-2040</t>
+  </si>
+  <si>
+    <t>percentage growth emp education הר נוף 2035-2040</t>
+  </si>
+  <si>
+    <t>percentage growth emp education חומת שמואל - ה 2035-2040</t>
+  </si>
+  <si>
+    <t>percentage growth emp education חומת שמואל-מע 2035-2040</t>
+  </si>
+  <si>
+    <t>percentage growth emp education טלביה רחביה 2035-2040</t>
+  </si>
+  <si>
+    <t>percentage growth emp education יובלים גנים 2035-2040</t>
+  </si>
+  <si>
+    <t>percentage growth emp education כניסה לעיר 2035-2040</t>
+  </si>
+  <si>
+    <t>percentage growth emp education כניסה לעיר - ק 2035-2040</t>
+  </si>
+  <si>
+    <t>percentage growth emp education כפר עקב 2035-2040</t>
+  </si>
+  <si>
+    <t>percentage growth emp education מורשה 2035-2040</t>
+  </si>
+  <si>
+    <t>percentage growth emp education מחנה שועפט 2035-2040</t>
+  </si>
+  <si>
+    <t>percentage growth emp education מנחת - מלחה 2035-2040</t>
+  </si>
+  <si>
+    <t>percentage growth emp education מעלות דפנה 2035-2040</t>
+  </si>
+  <si>
+    <t>percentage growth emp education מער 2035-2040</t>
+  </si>
+  <si>
+    <t>percentage growth emp education מער חרדי 2035-2040</t>
+  </si>
+  <si>
+    <t>percentage growth emp education מער מזרח ואדי 2035-2040</t>
+  </si>
+  <si>
+    <t>percentage growth emp education מקור ברוך 2035-2040</t>
+  </si>
+  <si>
+    <t>percentage growth emp education מרכז רפואי הד 2035-2040</t>
+  </si>
+  <si>
+    <t>percentage growth emp education נוה יעקב 2035-2040</t>
+  </si>
+  <si>
+    <t>percentage growth emp education נחלאות שערי ח 2035-2040</t>
+  </si>
+  <si>
+    <t>percentage growth emp education ניות -גבעת מר 2035-2040</t>
+  </si>
+  <si>
+    <t>percentage growth emp education סנהדריה רמת א 2035-2040</t>
+  </si>
+  <si>
+    <t>percentage growth emp education עין כרם 2035-2040</t>
+  </si>
+  <si>
+    <t>percentage growth emp education עיסאוויה 2035-2040</t>
+  </si>
+  <si>
+    <t>percentage growth emp education פסגת זאב 2035-2040</t>
+  </si>
+  <si>
+    <t>percentage growth emp education פת - קטמונים 2035-2040</t>
+  </si>
+  <si>
+    <t>percentage growth emp education צור באהר מורח 2035-2040</t>
+  </si>
+  <si>
+    <t>percentage growth emp education קטמון הישנה 2035-2040</t>
+  </si>
+  <si>
+    <t>percentage growth emp education קריית הממשלה- 2035-2040</t>
+  </si>
+  <si>
+    <t>percentage growth emp education קריית משה -גב 2035-2040</t>
+  </si>
+  <si>
+    <t>percentage growth emp education ראס אל עמד - ג' 2035-2040</t>
+  </si>
+  <si>
+    <t>percentage growth emp education רכס לבן 2035-2040</t>
+  </si>
+  <si>
+    <t>percentage growth emp education רמות 2035-2040</t>
+  </si>
+  <si>
+    <t>percentage growth emp education רמת שלמה 2035-2040</t>
+  </si>
+  <si>
+    <t>percentage growth emp education רמת שרת - בית 2035-2040</t>
+  </si>
+  <si>
+    <t>percentage growth emp education רסקו 2035-2040</t>
+  </si>
+  <si>
+    <t>percentage growth emp education שדה התעופה עט 2035-2040</t>
+  </si>
+  <si>
+    <t>percentage growth emp education שועפאט - בית 2035-2040</t>
+  </si>
+  <si>
+    <t>percentage growth emp education תלפיות 2035-2040</t>
+  </si>
+  <si>
+    <t>percentage growth emp education תלפיות ארנונ 2035-2040</t>
+  </si>
+  <si>
+    <t>percentage growth emp education תלפיות מזרח 2035-2040</t>
+  </si>
+  <si>
+    <t>percentage growth emp education 0 2040-2045</t>
+  </si>
+  <si>
+    <t>percentage growth emp education א-טור 2040-2045</t>
+  </si>
+  <si>
+    <t>percentage growth emp education אבו טור סילוא 2040-2045</t>
+  </si>
+  <si>
+    <t>percentage growth emp education אזור תעשיה גב 2040-2045</t>
+  </si>
+  <si>
+    <t>percentage growth emp education אזור תעשיה עט 2040-2045</t>
+  </si>
+  <si>
+    <t>percentage growth emp education בית הכרם 2040-2045</t>
+  </si>
+  <si>
+    <t>percentage growth emp education בית צפפא,שרפת 2040-2045</t>
+  </si>
+  <si>
+    <t>percentage growth emp education בקעה מושבות 2040-2045</t>
+  </si>
+  <si>
+    <t>percentage growth emp education גבעת המטוס 2040-2045</t>
+  </si>
+  <si>
+    <t>percentage growth emp education גבעת משואה 2040-2045</t>
+  </si>
+  <si>
+    <t>percentage growth emp education גילה 2040-2045</t>
+  </si>
+  <si>
+    <t>percentage growth emp education הגבעה הצרפתי 2040-2045</t>
+  </si>
+  <si>
+    <t>percentage growth emp education העיר העתיקה 2040-2045</t>
+  </si>
+  <si>
+    <t>percentage growth emp education הקריות של ירו 2040-2045</t>
+  </si>
+  <si>
+    <t>percentage growth emp education הר החוצבים 2040-2045</t>
+  </si>
+  <si>
+    <t>percentage growth emp education הר הצופים 2040-2045</t>
+  </si>
+  <si>
+    <t>percentage growth emp education הר נוף 2040-2045</t>
+  </si>
+  <si>
+    <t>percentage growth emp education חומת שמואל - ה 2040-2045</t>
+  </si>
+  <si>
+    <t>percentage growth emp education חומת שמואל-מע 2040-2045</t>
+  </si>
+  <si>
+    <t>percentage growth emp education טלביה רחביה 2040-2045</t>
+  </si>
+  <si>
+    <t>percentage growth emp education יובלים גנים 2040-2045</t>
+  </si>
+  <si>
+    <t>percentage growth emp education כניסה לעיר 2040-2045</t>
+  </si>
+  <si>
+    <t>percentage growth emp education כניסה לעיר - ק 2040-2045</t>
+  </si>
+  <si>
+    <t>percentage growth emp education כפר עקב 2040-2045</t>
+  </si>
+  <si>
+    <t>percentage growth emp education מורשה 2040-2045</t>
+  </si>
+  <si>
+    <t>percentage growth emp education מחנה שועפט 2040-2045</t>
+  </si>
+  <si>
+    <t>percentage growth emp education מנחת - מלחה 2040-2045</t>
+  </si>
+  <si>
+    <t>percentage growth emp education מעלות דפנה 2040-2045</t>
+  </si>
+  <si>
+    <t>percentage growth emp education מער 2040-2045</t>
+  </si>
+  <si>
+    <t>percentage growth emp education מער חרדי 2040-2045</t>
+  </si>
+  <si>
+    <t>percentage growth emp education מער מזרח ואדי 2040-2045</t>
+  </si>
+  <si>
+    <t>percentage growth emp education מקור ברוך 2040-2045</t>
+  </si>
+  <si>
+    <t>percentage growth emp education מרכז רפואי הד 2040-2045</t>
+  </si>
+  <si>
+    <t>percentage growth emp education נוה יעקב 2040-2045</t>
+  </si>
+  <si>
+    <t>percentage growth emp education נחלאות שערי ח 2040-2045</t>
+  </si>
+  <si>
+    <t>percentage growth emp education ניות -גבעת מר 2040-2045</t>
+  </si>
+  <si>
+    <t>percentage growth emp education סנהדריה רמת א 2040-2045</t>
+  </si>
+  <si>
+    <t>percentage growth emp education עין כרם 2040-2045</t>
+  </si>
+  <si>
+    <t>percentage growth emp education עיסאוויה 2040-2045</t>
+  </si>
+  <si>
+    <t>percentage growth emp education פסגת זאב 2040-2045</t>
+  </si>
+  <si>
+    <t>percentage growth emp education פת - קטמונים 2040-2045</t>
+  </si>
+  <si>
+    <t>percentage growth emp education צור באהר מורח 2040-2045</t>
+  </si>
+  <si>
+    <t>percentage growth emp education קטמון הישנה 2040-2045</t>
+  </si>
+  <si>
+    <t>percentage growth emp education קריית הממשלה- 2040-2045</t>
+  </si>
+  <si>
+    <t>percentage growth emp education קריית משה -גב 2040-2045</t>
+  </si>
+  <si>
+    <t>percentage growth emp education ראס אל עמד - ג' 2040-2045</t>
+  </si>
+  <si>
+    <t>percentage growth emp education רכס לבן 2040-2045</t>
+  </si>
+  <si>
+    <t>percentage growth emp education רמות 2040-2045</t>
+  </si>
+  <si>
+    <t>percentage growth emp education רמת שלמה 2040-2045</t>
+  </si>
+  <si>
+    <t>percentage growth emp education רמת שרת - בית 2040-2045</t>
+  </si>
+  <si>
+    <t>percentage growth emp education רסקו 2040-2045</t>
+  </si>
+  <si>
+    <t>percentage growth emp education שדה התעופה עט 2040-2045</t>
+  </si>
+  <si>
+    <t>percentage growth emp education שועפאט - בית 2040-2045</t>
+  </si>
+  <si>
+    <t>percentage growth emp education תלפיות 2040-2045</t>
+  </si>
+  <si>
+    <t>percentage growth emp education תלפיות ארנונ 2040-2045</t>
+  </si>
+  <si>
+    <t>percentage growth emp education תלפיות מזרח 2040-2045</t>
+  </si>
+  <si>
+    <t>percentage growth emp education 0 2045-2050</t>
+  </si>
+  <si>
+    <t>percentage growth emp education א-טור 2045-2050</t>
+  </si>
+  <si>
+    <t>percentage growth emp education אבו טור סילוא 2045-2050</t>
+  </si>
+  <si>
+    <t>percentage growth emp education אזור תעשיה גב 2045-2050</t>
+  </si>
+  <si>
+    <t>percentage growth emp education אזור תעשיה עט 2045-2050</t>
+  </si>
+  <si>
+    <t>percentage growth emp education בית הכרם 2045-2050</t>
+  </si>
+  <si>
+    <t>percentage growth emp education בית צפפא,שרפת 2045-2050</t>
+  </si>
+  <si>
+    <t>percentage growth emp education בקעה מושבות 2045-2050</t>
+  </si>
+  <si>
+    <t>percentage growth emp education גבעת המטוס 2045-2050</t>
+  </si>
+  <si>
+    <t>percentage growth emp education גבעת משואה 2045-2050</t>
+  </si>
+  <si>
+    <t>percentage growth emp education גילה 2045-2050</t>
+  </si>
+  <si>
+    <t>percentage growth emp education הגבעה הצרפתי 2045-2050</t>
+  </si>
+  <si>
+    <t>percentage growth emp education העיר העתיקה 2045-2050</t>
+  </si>
+  <si>
+    <t>percentage growth emp education הקריות של ירו 2045-2050</t>
+  </si>
+  <si>
+    <t>percentage growth emp education הר החוצבים 2045-2050</t>
+  </si>
+  <si>
+    <t>percentage growth emp education הר הצופים 2045-2050</t>
+  </si>
+  <si>
+    <t>percentage growth emp education הר נוף 2045-2050</t>
+  </si>
+  <si>
+    <t>percentage growth emp education חומת שמואל - ה 2045-2050</t>
+  </si>
+  <si>
+    <t>percentage growth emp education חומת שמואל-מע 2045-2050</t>
+  </si>
+  <si>
+    <t>percentage growth emp education טלביה רחביה 2045-2050</t>
+  </si>
+  <si>
+    <t>percentage growth emp education יובלים גנים 2045-2050</t>
+  </si>
+  <si>
+    <t>percentage growth emp education כניסה לעיר 2045-2050</t>
+  </si>
+  <si>
+    <t>percentage growth emp education כניסה לעיר - ק 2045-2050</t>
+  </si>
+  <si>
+    <t>percentage growth emp education כפר עקב 2045-2050</t>
+  </si>
+  <si>
+    <t>percentage growth emp education מורשה 2045-2050</t>
+  </si>
+  <si>
+    <t>percentage growth emp education מחנה שועפט 2045-2050</t>
+  </si>
+  <si>
+    <t>percentage growth emp education מנחת - מלחה 2045-2050</t>
+  </si>
+  <si>
+    <t>percentage growth emp education מעלות דפנה 2045-2050</t>
+  </si>
+  <si>
+    <t>percentage growth emp education מער 2045-2050</t>
+  </si>
+  <si>
+    <t>percentage growth emp education מער חרדי 2045-2050</t>
+  </si>
+  <si>
+    <t>percentage growth emp education מער מזרח ואדי 2045-2050</t>
+  </si>
+  <si>
+    <t>percentage growth emp education מקור ברוך 2045-2050</t>
+  </si>
+  <si>
+    <t>percentage growth emp education מרכז רפואי הד 2045-2050</t>
+  </si>
+  <si>
+    <t>percentage growth emp education נוה יעקב 2045-2050</t>
+  </si>
+  <si>
+    <t>percentage growth emp education נחלאות שערי ח 2045-2050</t>
+  </si>
+  <si>
+    <t>percentage growth emp education ניות -גבעת מר 2045-2050</t>
+  </si>
+  <si>
+    <t>percentage growth emp education סנהדריה רמת א 2045-2050</t>
+  </si>
+  <si>
+    <t>percentage growth emp education עין כרם 2045-2050</t>
+  </si>
+  <si>
+    <t>percentage growth emp education עיסאוויה 2045-2050</t>
+  </si>
+  <si>
+    <t>percentage growth emp education פסגת זאב 2045-2050</t>
+  </si>
+  <si>
+    <t>percentage growth emp education פת - קטמונים 2045-2050</t>
+  </si>
+  <si>
+    <t>percentage growth emp education צור באהר מורח 2045-2050</t>
+  </si>
+  <si>
+    <t>percentage growth emp education קטמון הישנה 2045-2050</t>
+  </si>
+  <si>
+    <t>percentage growth emp education קריית הממשלה- 2045-2050</t>
+  </si>
+  <si>
+    <t>percentage growth emp education קריית משה -גב 2045-2050</t>
+  </si>
+  <si>
+    <t>percentage growth emp education ראס אל עמד - ג' 2045-2050</t>
+  </si>
+  <si>
+    <t>percentage growth emp education רכס לבן 2045-2050</t>
+  </si>
+  <si>
+    <t>percentage growth emp education רמות 2045-2050</t>
+  </si>
+  <si>
+    <t>percentage growth emp education רמת שלמה 2045-2050</t>
+  </si>
+  <si>
+    <t>percentage growth emp education רמת שרת - בית 2045-2050</t>
+  </si>
+  <si>
+    <t>percentage growth emp education רסקו 2045-2050</t>
+  </si>
+  <si>
+    <t>percentage growth emp education שדה התעופה עט 2045-2050</t>
+  </si>
+  <si>
+    <t>percentage growth emp education שועפאט - בית 2045-2050</t>
+  </si>
+  <si>
+    <t>percentage growth emp education תלפיות 2045-2050</t>
+  </si>
+  <si>
+    <t>percentage growth emp education תלפיות ארנונ 2045-2050</t>
+  </si>
+  <si>
+    <t>percentage growth emp education תלפיות מזרח 2045-2050</t>
   </si>
   <si>
     <t>1,758,461</t>
@@ -4982,7 +5990,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E1502"/>
+  <dimension ref="A1:E1838"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -5004,16 +6012,16 @@
         <v>4</v>
       </c>
       <c r="B2" t="s">
-        <v>1505</v>
+        <v>1841</v>
       </c>
       <c r="C2" t="s">
-        <v>1505</v>
+        <v>1841</v>
       </c>
       <c r="D2" t="s">
-        <v>1505</v>
+        <v>1841</v>
       </c>
       <c r="E2" t="s">
-        <v>1505</v>
+        <v>1841</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -5021,13 +6029,13 @@
         <v>5</v>
       </c>
       <c r="C3" t="s">
-        <v>1510</v>
+        <v>1846</v>
       </c>
       <c r="D3" t="s">
-        <v>1515</v>
+        <v>1851</v>
       </c>
       <c r="E3" t="s">
-        <v>1519</v>
+        <v>1855</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -5035,16 +6043,16 @@
         <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>1506</v>
+        <v>1842</v>
       </c>
       <c r="C4" t="s">
-        <v>1506</v>
+        <v>1842</v>
       </c>
       <c r="D4" t="s">
-        <v>1506</v>
+        <v>1842</v>
       </c>
       <c r="E4" t="s">
-        <v>1506</v>
+        <v>1842</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -5052,13 +6060,13 @@
         <v>7</v>
       </c>
       <c r="C5" t="s">
-        <v>1511</v>
+        <v>1847</v>
       </c>
       <c r="D5" t="s">
-        <v>1516</v>
+        <v>1852</v>
       </c>
       <c r="E5" t="s">
-        <v>1520</v>
+        <v>1856</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -5151,16 +6159,16 @@
         <v>13</v>
       </c>
       <c r="B11" t="s">
-        <v>1507</v>
+        <v>1843</v>
       </c>
       <c r="C11" t="s">
-        <v>1507</v>
+        <v>1843</v>
       </c>
       <c r="D11" t="s">
-        <v>1507</v>
+        <v>1843</v>
       </c>
       <c r="E11" t="s">
-        <v>1507</v>
+        <v>1843</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -5168,13 +6176,13 @@
         <v>14</v>
       </c>
       <c r="C12" t="s">
-        <v>1507</v>
+        <v>1843</v>
       </c>
       <c r="D12" t="s">
-        <v>1507</v>
+        <v>1843</v>
       </c>
       <c r="E12" t="s">
-        <v>1507</v>
+        <v>1843</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -5182,16 +6190,16 @@
         <v>15</v>
       </c>
       <c r="B13" t="s">
-        <v>1508</v>
+        <v>1844</v>
       </c>
       <c r="C13" t="s">
-        <v>1508</v>
+        <v>1844</v>
       </c>
       <c r="D13" t="s">
-        <v>1508</v>
+        <v>1844</v>
       </c>
       <c r="E13" t="s">
-        <v>1508</v>
+        <v>1844</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -5199,13 +6207,13 @@
         <v>16</v>
       </c>
       <c r="C14" t="s">
-        <v>1512</v>
+        <v>1848</v>
       </c>
       <c r="D14" t="s">
-        <v>1517</v>
+        <v>1853</v>
       </c>
       <c r="E14" t="s">
-        <v>1521</v>
+        <v>1857</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -5213,16 +6221,16 @@
         <v>17</v>
       </c>
       <c r="B15" t="s">
-        <v>1509</v>
+        <v>1845</v>
       </c>
       <c r="C15" t="s">
-        <v>1509</v>
+        <v>1845</v>
       </c>
       <c r="D15" t="s">
-        <v>1509</v>
+        <v>1845</v>
       </c>
       <c r="E15" t="s">
-        <v>1509</v>
+        <v>1845</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -5230,13 +6238,13 @@
         <v>18</v>
       </c>
       <c r="C16" t="s">
-        <v>1513</v>
+        <v>1849</v>
       </c>
       <c r="D16" t="s">
-        <v>1518</v>
+        <v>1854</v>
       </c>
       <c r="E16" t="s">
-        <v>1522</v>
+        <v>1858</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -5677,13 +6685,13 @@
         <v>48</v>
       </c>
       <c r="C46" t="s">
-        <v>1514</v>
+        <v>1850</v>
       </c>
       <c r="D46" t="s">
-        <v>1514</v>
+        <v>1850</v>
       </c>
       <c r="E46" t="s">
-        <v>1514</v>
+        <v>1850</v>
       </c>
     </row>
     <row r="47" spans="1:5">
@@ -26068,6 +27076,4599 @@
       </c>
       <c r="E1502">
         <v>1.291052166578559</v>
+      </c>
+    </row>
+    <row r="1503" spans="1:5">
+      <c r="A1503" s="1" t="s">
+        <v>1505</v>
+      </c>
+      <c r="C1503">
+        <v>-26.68354606628418</v>
+      </c>
+      <c r="D1503">
+        <v>-28.10066604614258</v>
+      </c>
+      <c r="E1503">
+        <v>-26.38949012756348</v>
+      </c>
+    </row>
+    <row r="1504" spans="1:5">
+      <c r="A1504" s="1" t="s">
+        <v>1506</v>
+      </c>
+      <c r="C1504">
+        <v>-32.00569534301758</v>
+      </c>
+      <c r="D1504">
+        <v>-32.0456657409668</v>
+      </c>
+      <c r="E1504">
+        <v>-31.86953926086426</v>
+      </c>
+    </row>
+    <row r="1505" spans="1:5">
+      <c r="A1505" s="1" t="s">
+        <v>1507</v>
+      </c>
+      <c r="C1505">
+        <v>-28.84376525878906</v>
+      </c>
+      <c r="D1505">
+        <v>-29.46407127380371</v>
+      </c>
+      <c r="E1505">
+        <v>-29.19508934020996</v>
+      </c>
+    </row>
+    <row r="1506" spans="1:5">
+      <c r="A1506" s="1" t="s">
+        <v>1508</v>
+      </c>
+      <c r="C1506">
+        <v>-3.878303050994873</v>
+      </c>
+      <c r="D1506">
+        <v>-4.062081813812256</v>
+      </c>
+      <c r="E1506">
+        <v>-3.74123477935791</v>
+      </c>
+    </row>
+    <row r="1507" spans="1:5">
+      <c r="A1507" s="1" t="s">
+        <v>1509</v>
+      </c>
+      <c r="C1507">
+        <v>-48</v>
+      </c>
+      <c r="D1507">
+        <v>-48</v>
+      </c>
+      <c r="E1507">
+        <v>-48</v>
+      </c>
+    </row>
+    <row r="1508" spans="1:5">
+      <c r="A1508" s="1" t="s">
+        <v>1510</v>
+      </c>
+      <c r="C1508">
+        <v>-8.130292892456055</v>
+      </c>
+      <c r="D1508">
+        <v>-10.69640827178955</v>
+      </c>
+      <c r="E1508">
+        <v>-9.893491744995117</v>
+      </c>
+    </row>
+    <row r="1509" spans="1:5">
+      <c r="A1509" s="1" t="s">
+        <v>1511</v>
+      </c>
+      <c r="C1509">
+        <v>-35.94775009155273</v>
+      </c>
+      <c r="D1509">
+        <v>-36.17729187011719</v>
+      </c>
+      <c r="E1509">
+        <v>-36.06415939331055</v>
+      </c>
+    </row>
+    <row r="1510" spans="1:5">
+      <c r="A1510" s="1" t="s">
+        <v>1512</v>
+      </c>
+      <c r="C1510">
+        <v>-30.21263885498047</v>
+      </c>
+      <c r="D1510">
+        <v>-31.93795585632324</v>
+      </c>
+      <c r="E1510">
+        <v>-31.15077018737793</v>
+      </c>
+    </row>
+    <row r="1511" spans="1:5">
+      <c r="A1511" s="1" t="s">
+        <v>1513</v>
+      </c>
+    </row>
+    <row r="1512" spans="1:5">
+      <c r="A1512" s="1" t="s">
+        <v>1514</v>
+      </c>
+      <c r="C1512">
+        <v>-18.57325172424316</v>
+      </c>
+      <c r="D1512">
+        <v>-20.67618560791016</v>
+      </c>
+      <c r="E1512">
+        <v>-18.5692310333252</v>
+      </c>
+    </row>
+    <row r="1513" spans="1:5">
+      <c r="A1513" s="1" t="s">
+        <v>1515</v>
+      </c>
+      <c r="C1513">
+        <v>-9.211896896362305</v>
+      </c>
+      <c r="D1513">
+        <v>-13.7275972366333</v>
+      </c>
+      <c r="E1513">
+        <v>-10.88778305053711</v>
+      </c>
+    </row>
+    <row r="1514" spans="1:5">
+      <c r="A1514" s="1" t="s">
+        <v>1516</v>
+      </c>
+      <c r="C1514">
+        <v>-16.35707473754883</v>
+      </c>
+      <c r="D1514">
+        <v>-17.41849517822266</v>
+      </c>
+      <c r="E1514">
+        <v>-15.27130794525146</v>
+      </c>
+    </row>
+    <row r="1515" spans="1:5">
+      <c r="A1515" s="1" t="s">
+        <v>1517</v>
+      </c>
+      <c r="C1515">
+        <v>-26.01636695861816</v>
+      </c>
+      <c r="D1515">
+        <v>-26.57264518737793</v>
+      </c>
+      <c r="E1515">
+        <v>-26.13095283508301</v>
+      </c>
+    </row>
+    <row r="1516" spans="1:5">
+      <c r="A1516" s="1" t="s">
+        <v>1518</v>
+      </c>
+      <c r="C1516">
+        <v>-29.68030548095703</v>
+      </c>
+      <c r="D1516">
+        <v>-32.88461303710938</v>
+      </c>
+      <c r="E1516">
+        <v>-33.0675163269043</v>
+      </c>
+    </row>
+    <row r="1517" spans="1:5">
+      <c r="A1517" s="1" t="s">
+        <v>1519</v>
+      </c>
+      <c r="C1517">
+        <v>18.4306526184082</v>
+      </c>
+      <c r="D1517">
+        <v>17.70398712158203</v>
+      </c>
+      <c r="E1517">
+        <v>18.94564628601074</v>
+      </c>
+    </row>
+    <row r="1518" spans="1:5">
+      <c r="A1518" s="1" t="s">
+        <v>1520</v>
+      </c>
+      <c r="C1518">
+        <v>0</v>
+      </c>
+      <c r="D1518">
+        <v>0</v>
+      </c>
+      <c r="E1518">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1519" spans="1:5">
+      <c r="A1519" s="1" t="s">
+        <v>1521</v>
+      </c>
+      <c r="C1519">
+        <v>-31.09913063049316</v>
+      </c>
+      <c r="D1519">
+        <v>-36.09987258911133</v>
+      </c>
+      <c r="E1519">
+        <v>-36.45967102050781</v>
+      </c>
+    </row>
+    <row r="1520" spans="1:5">
+      <c r="A1520" s="1" t="s">
+        <v>1522</v>
+      </c>
+      <c r="C1520">
+        <v>-10.5558385848999</v>
+      </c>
+      <c r="D1520">
+        <v>-12.36332607269287</v>
+      </c>
+      <c r="E1520">
+        <v>-9.896894454956055</v>
+      </c>
+    </row>
+    <row r="1521" spans="1:5">
+      <c r="A1521" s="1" t="s">
+        <v>1523</v>
+      </c>
+    </row>
+    <row r="1522" spans="1:5">
+      <c r="A1522" s="1" t="s">
+        <v>1524</v>
+      </c>
+      <c r="C1522">
+        <v>-21.99339294433594</v>
+      </c>
+      <c r="D1522">
+        <v>-25.09716415405273</v>
+      </c>
+      <c r="E1522">
+        <v>-23.80610847473145</v>
+      </c>
+    </row>
+    <row r="1523" spans="1:5">
+      <c r="A1523" s="1" t="s">
+        <v>1525</v>
+      </c>
+      <c r="C1523">
+        <v>0.05418065935373306</v>
+      </c>
+      <c r="D1523">
+        <v>-6.902203559875488</v>
+      </c>
+      <c r="E1523">
+        <v>-3.36484432220459</v>
+      </c>
+    </row>
+    <row r="1524" spans="1:5">
+      <c r="A1524" s="1" t="s">
+        <v>1526</v>
+      </c>
+      <c r="C1524" t="s">
+        <v>1850</v>
+      </c>
+      <c r="D1524" t="s">
+        <v>1850</v>
+      </c>
+      <c r="E1524" t="s">
+        <v>1850</v>
+      </c>
+    </row>
+    <row r="1525" spans="1:5">
+      <c r="A1525" s="1" t="s">
+        <v>1527</v>
+      </c>
+      <c r="C1525">
+        <v>-9.063723564147949</v>
+      </c>
+      <c r="D1525">
+        <v>-9.155792236328125</v>
+      </c>
+      <c r="E1525">
+        <v>-9.115406036376953</v>
+      </c>
+    </row>
+    <row r="1526" spans="1:5">
+      <c r="A1526" s="1" t="s">
+        <v>1528</v>
+      </c>
+      <c r="C1526">
+        <v>-9.065347671508789</v>
+      </c>
+      <c r="D1526">
+        <v>-9.53482723236084</v>
+      </c>
+      <c r="E1526">
+        <v>-9.130251884460449</v>
+      </c>
+    </row>
+    <row r="1527" spans="1:5">
+      <c r="A1527" s="1" t="s">
+        <v>1529</v>
+      </c>
+      <c r="C1527">
+        <v>-6.159069538116455</v>
+      </c>
+      <c r="D1527">
+        <v>-11.46291065216064</v>
+      </c>
+      <c r="E1527">
+        <v>-12.11958885192871</v>
+      </c>
+    </row>
+    <row r="1528" spans="1:5">
+      <c r="A1528" s="1" t="s">
+        <v>1530</v>
+      </c>
+      <c r="C1528">
+        <v>57.56622695922852</v>
+      </c>
+      <c r="D1528">
+        <v>54.45578002929688</v>
+      </c>
+      <c r="E1528">
+        <v>55.47430038452148</v>
+      </c>
+    </row>
+    <row r="1529" spans="1:5">
+      <c r="A1529" s="1" t="s">
+        <v>1531</v>
+      </c>
+      <c r="C1529">
+        <v>-12.88327026367188</v>
+      </c>
+      <c r="D1529">
+        <v>-15.31770133972168</v>
+      </c>
+      <c r="E1529">
+        <v>-13.61489200592041</v>
+      </c>
+    </row>
+    <row r="1530" spans="1:5">
+      <c r="A1530" s="1" t="s">
+        <v>1532</v>
+      </c>
+      <c r="C1530">
+        <v>-35.03279495239258</v>
+      </c>
+      <c r="D1530">
+        <v>-36.67386245727539</v>
+      </c>
+      <c r="E1530">
+        <v>-36.71773910522461</v>
+      </c>
+    </row>
+    <row r="1531" spans="1:5">
+      <c r="A1531" s="1" t="s">
+        <v>1533</v>
+      </c>
+      <c r="C1531">
+        <v>-8.945117950439453</v>
+      </c>
+      <c r="D1531">
+        <v>-12.90749454498291</v>
+      </c>
+      <c r="E1531">
+        <v>-11.85525226593018</v>
+      </c>
+    </row>
+    <row r="1532" spans="1:5">
+      <c r="A1532" s="1" t="s">
+        <v>1534</v>
+      </c>
+      <c r="C1532">
+        <v>-23.96588325500488</v>
+      </c>
+      <c r="D1532">
+        <v>-28.29411125183105</v>
+      </c>
+      <c r="E1532">
+        <v>-28.42296028137207</v>
+      </c>
+    </row>
+    <row r="1533" spans="1:5">
+      <c r="A1533" s="1" t="s">
+        <v>1535</v>
+      </c>
+      <c r="C1533">
+        <v>-38.67049789428711</v>
+      </c>
+      <c r="D1533">
+        <v>-38.77999496459961</v>
+      </c>
+      <c r="E1533">
+        <v>-38.68926239013672</v>
+      </c>
+    </row>
+    <row r="1534" spans="1:5">
+      <c r="A1534" s="1" t="s">
+        <v>1536</v>
+      </c>
+      <c r="C1534">
+        <v>-42.61593246459961</v>
+      </c>
+      <c r="D1534">
+        <v>-42.63225173950195</v>
+      </c>
+      <c r="E1534">
+        <v>-42.60436630249023</v>
+      </c>
+    </row>
+    <row r="1535" spans="1:5">
+      <c r="A1535" s="1" t="s">
+        <v>1537</v>
+      </c>
+      <c r="C1535">
+        <v>0</v>
+      </c>
+      <c r="D1535">
+        <v>0</v>
+      </c>
+      <c r="E1535">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1536" spans="1:5">
+      <c r="A1536" s="1" t="s">
+        <v>1538</v>
+      </c>
+      <c r="C1536">
+        <v>-29.41322326660156</v>
+      </c>
+      <c r="D1536">
+        <v>-35.62997055053711</v>
+      </c>
+      <c r="E1536">
+        <v>-36.37380599975586</v>
+      </c>
+    </row>
+    <row r="1537" spans="1:5">
+      <c r="A1537" s="1" t="s">
+        <v>1539</v>
+      </c>
+      <c r="C1537">
+        <v>6.809447765350342</v>
+      </c>
+      <c r="D1537">
+        <v>1.858007550239563</v>
+      </c>
+      <c r="E1537">
+        <v>3.165043354034424</v>
+      </c>
+    </row>
+    <row r="1538" spans="1:5">
+      <c r="A1538" s="1" t="s">
+        <v>1540</v>
+      </c>
+      <c r="C1538">
+        <v>-32.07715225219727</v>
+      </c>
+      <c r="D1538">
+        <v>-35.19334411621094</v>
+      </c>
+      <c r="E1538">
+        <v>-34.30155563354492</v>
+      </c>
+    </row>
+    <row r="1539" spans="1:5">
+      <c r="A1539" s="1" t="s">
+        <v>1541</v>
+      </c>
+      <c r="C1539">
+        <v>-33.05783462524414</v>
+      </c>
+      <c r="D1539">
+        <v>-37.58584213256836</v>
+      </c>
+      <c r="E1539">
+        <v>-37.75868988037109</v>
+      </c>
+    </row>
+    <row r="1540" spans="1:5">
+      <c r="A1540" s="1" t="s">
+        <v>1542</v>
+      </c>
+      <c r="C1540">
+        <v>76.52216339111328</v>
+      </c>
+      <c r="D1540">
+        <v>55.1190299987793</v>
+      </c>
+      <c r="E1540">
+        <v>64.63491821289062</v>
+      </c>
+    </row>
+    <row r="1541" spans="1:5">
+      <c r="A1541" s="1" t="s">
+        <v>1543</v>
+      </c>
+      <c r="C1541">
+        <v>-35.14753723144531</v>
+      </c>
+      <c r="D1541">
+        <v>-35.20293045043945</v>
+      </c>
+      <c r="E1541">
+        <v>-35.05650329589844</v>
+      </c>
+    </row>
+    <row r="1542" spans="1:5">
+      <c r="A1542" s="1" t="s">
+        <v>1544</v>
+      </c>
+      <c r="C1542">
+        <v>-0.1596934944391251</v>
+      </c>
+      <c r="D1542">
+        <v>-5.341487407684326</v>
+      </c>
+      <c r="E1542">
+        <v>-2.033071756362915</v>
+      </c>
+    </row>
+    <row r="1543" spans="1:5">
+      <c r="A1543" s="1" t="s">
+        <v>1545</v>
+      </c>
+      <c r="C1543">
+        <v>-36.70893096923828</v>
+      </c>
+      <c r="D1543">
+        <v>-39.07160949707031</v>
+      </c>
+      <c r="E1543">
+        <v>-38.08582305908203</v>
+      </c>
+    </row>
+    <row r="1544" spans="1:5">
+      <c r="A1544" s="1" t="s">
+        <v>1546</v>
+      </c>
+      <c r="C1544">
+        <v>-38.30388259887695</v>
+      </c>
+      <c r="D1544">
+        <v>-38.52179336547852</v>
+      </c>
+      <c r="E1544">
+        <v>-38.42876434326172</v>
+      </c>
+    </row>
+    <row r="1545" spans="1:5">
+      <c r="A1545" s="1" t="s">
+        <v>1547</v>
+      </c>
+      <c r="C1545">
+        <v>-31.73883247375488</v>
+      </c>
+      <c r="D1545">
+        <v>-35.13603591918945</v>
+      </c>
+      <c r="E1545">
+        <v>-33.77647018432617</v>
+      </c>
+    </row>
+    <row r="1546" spans="1:5">
+      <c r="A1546" s="1" t="s">
+        <v>1548</v>
+      </c>
+    </row>
+    <row r="1547" spans="1:5">
+      <c r="A1547" s="1" t="s">
+        <v>1549</v>
+      </c>
+      <c r="C1547">
+        <v>-31.99906349182129</v>
+      </c>
+      <c r="D1547">
+        <v>-35.80299758911133</v>
+      </c>
+      <c r="E1547">
+        <v>-35.58315277099609</v>
+      </c>
+    </row>
+    <row r="1548" spans="1:5">
+      <c r="A1548" s="1" t="s">
+        <v>1550</v>
+      </c>
+      <c r="C1548">
+        <v>-25.37919807434082</v>
+      </c>
+      <c r="D1548">
+        <v>-26.18971633911133</v>
+      </c>
+      <c r="E1548">
+        <v>-25.91293907165527</v>
+      </c>
+    </row>
+    <row r="1549" spans="1:5">
+      <c r="A1549" s="1" t="s">
+        <v>1551</v>
+      </c>
+    </row>
+    <row r="1550" spans="1:5">
+      <c r="A1550" s="1" t="s">
+        <v>1552</v>
+      </c>
+      <c r="C1550">
+        <v>-32.83298110961914</v>
+      </c>
+      <c r="D1550">
+        <v>-36.64394378662109</v>
+      </c>
+      <c r="E1550">
+        <v>-36.80082321166992</v>
+      </c>
+    </row>
+    <row r="1551" spans="1:5">
+      <c r="A1551" s="1" t="s">
+        <v>1553</v>
+      </c>
+      <c r="C1551">
+        <v>-14.41475296020508</v>
+      </c>
+      <c r="D1551">
+        <v>-23.85735893249512</v>
+      </c>
+      <c r="E1551">
+        <v>-24.89407348632812</v>
+      </c>
+    </row>
+    <row r="1552" spans="1:5">
+      <c r="A1552" s="1" t="s">
+        <v>1554</v>
+      </c>
+      <c r="C1552">
+        <v>-31.18929672241211</v>
+      </c>
+      <c r="D1552">
+        <v>-33.31166076660156</v>
+      </c>
+      <c r="E1552">
+        <v>-33.06906890869141</v>
+      </c>
+    </row>
+    <row r="1553" spans="1:5">
+      <c r="A1553" s="1" t="s">
+        <v>1555</v>
+      </c>
+      <c r="C1553">
+        <v>-15.74172115325928</v>
+      </c>
+      <c r="D1553">
+        <v>-21.2332878112793</v>
+      </c>
+      <c r="E1553">
+        <v>-18.85569763183594</v>
+      </c>
+    </row>
+    <row r="1554" spans="1:5">
+      <c r="A1554" s="1" t="s">
+        <v>1556</v>
+      </c>
+      <c r="C1554">
+        <v>-0.9745497703552246</v>
+      </c>
+      <c r="D1554">
+        <v>-11.40705108642578</v>
+      </c>
+      <c r="E1554">
+        <v>-12.34379768371582</v>
+      </c>
+    </row>
+    <row r="1555" spans="1:5">
+      <c r="A1555" s="1" t="s">
+        <v>1557</v>
+      </c>
+      <c r="C1555">
+        <v>-37.15622711181641</v>
+      </c>
+      <c r="D1555">
+        <v>-37.32415390014648</v>
+      </c>
+      <c r="E1555">
+        <v>-37.2395133972168</v>
+      </c>
+    </row>
+    <row r="1556" spans="1:5">
+      <c r="A1556" s="1" t="s">
+        <v>1558</v>
+      </c>
+      <c r="C1556">
+        <v>-8.390970230102539</v>
+      </c>
+      <c r="D1556">
+        <v>-10.87159442901611</v>
+      </c>
+      <c r="E1556">
+        <v>-9.368674278259277</v>
+      </c>
+    </row>
+    <row r="1557" spans="1:5">
+      <c r="A1557" s="1" t="s">
+        <v>1559</v>
+      </c>
+      <c r="C1557">
+        <v>-7.869227886199951</v>
+      </c>
+      <c r="D1557">
+        <v>-15.23948192596436</v>
+      </c>
+      <c r="E1557">
+        <v>-11.89180564880371</v>
+      </c>
+    </row>
+    <row r="1558" spans="1:5">
+      <c r="A1558" s="1" t="s">
+        <v>1560</v>
+      </c>
+      <c r="C1558">
+        <v>-16.02501678466797</v>
+      </c>
+      <c r="D1558">
+        <v>-19.24509429931641</v>
+      </c>
+      <c r="E1558">
+        <v>-17.13348960876465</v>
+      </c>
+    </row>
+    <row r="1559" spans="1:5">
+      <c r="A1559" s="1" t="s">
+        <v>1561</v>
+      </c>
+      <c r="C1559">
+        <v>22.70803070068359</v>
+      </c>
+      <c r="D1559">
+        <v>9.348258972167969</v>
+      </c>
+      <c r="E1559">
+        <v>18.4731616973877</v>
+      </c>
+    </row>
+    <row r="1560" spans="1:5">
+      <c r="A1560" s="1" t="s">
+        <v>1562</v>
+      </c>
+      <c r="C1560">
+        <v>4.520161151885986</v>
+      </c>
+      <c r="D1560">
+        <v>1.724244952201843</v>
+      </c>
+      <c r="E1560">
+        <v>2.427721500396729</v>
+      </c>
+    </row>
+    <row r="1561" spans="1:5">
+      <c r="A1561" s="1" t="s">
+        <v>1563</v>
+      </c>
+      <c r="C1561">
+        <v>10.45280838012695</v>
+      </c>
+      <c r="D1561">
+        <v>3.06100869178772</v>
+      </c>
+      <c r="E1561">
+        <v>4.626565456390381</v>
+      </c>
+    </row>
+    <row r="1562" spans="1:5">
+      <c r="A1562" s="1" t="s">
+        <v>1564</v>
+      </c>
+      <c r="C1562">
+        <v>0.4168809056282043</v>
+      </c>
+      <c r="D1562">
+        <v>0.2654622495174408</v>
+      </c>
+      <c r="E1562">
+        <v>0.4890567362308502</v>
+      </c>
+    </row>
+    <row r="1563" spans="1:5">
+      <c r="A1563" s="1" t="s">
+        <v>1565</v>
+      </c>
+      <c r="C1563">
+        <v>0</v>
+      </c>
+      <c r="D1563">
+        <v>0</v>
+      </c>
+      <c r="E1563">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1564" spans="1:5">
+      <c r="A1564" s="1" t="s">
+        <v>1566</v>
+      </c>
+      <c r="C1564">
+        <v>3.749504327774048</v>
+      </c>
+      <c r="D1564">
+        <v>1.920531988143921</v>
+      </c>
+      <c r="E1564">
+        <v>2.711210489273071</v>
+      </c>
+    </row>
+    <row r="1565" spans="1:5">
+      <c r="A1565" s="1" t="s">
+        <v>1567</v>
+      </c>
+      <c r="C1565">
+        <v>6.778697967529297</v>
+      </c>
+      <c r="D1565">
+        <v>1.91454815864563</v>
+      </c>
+      <c r="E1565">
+        <v>2.890730142593384</v>
+      </c>
+    </row>
+    <row r="1566" spans="1:5">
+      <c r="A1566" s="1" t="s">
+        <v>1568</v>
+      </c>
+      <c r="C1566">
+        <v>5.346025943756104</v>
+      </c>
+      <c r="D1566">
+        <v>2.942479848861694</v>
+      </c>
+      <c r="E1566">
+        <v>4.14374303817749</v>
+      </c>
+    </row>
+    <row r="1567" spans="1:5">
+      <c r="A1567" s="1" t="s">
+        <v>1569</v>
+      </c>
+      <c r="C1567" t="s">
+        <v>1850</v>
+      </c>
+      <c r="D1567" t="s">
+        <v>1850</v>
+      </c>
+      <c r="E1567" t="s">
+        <v>1850</v>
+      </c>
+    </row>
+    <row r="1568" spans="1:5">
+      <c r="A1568" s="1" t="s">
+        <v>1570</v>
+      </c>
+      <c r="C1568">
+        <v>10.13296318054199</v>
+      </c>
+      <c r="D1568">
+        <v>7.249392509460449</v>
+      </c>
+      <c r="E1568">
+        <v>9.265872955322266</v>
+      </c>
+    </row>
+    <row r="1569" spans="1:5">
+      <c r="A1569" s="1" t="s">
+        <v>1571</v>
+      </c>
+      <c r="C1569">
+        <v>13.34019088745117</v>
+      </c>
+      <c r="D1569">
+        <v>8.919155120849609</v>
+      </c>
+      <c r="E1569">
+        <v>11.74021434783936</v>
+      </c>
+    </row>
+    <row r="1570" spans="1:5">
+      <c r="A1570" s="1" t="s">
+        <v>1572</v>
+      </c>
+      <c r="C1570">
+        <v>19.51880073547363</v>
+      </c>
+      <c r="D1570">
+        <v>7.099644660949707</v>
+      </c>
+      <c r="E1570">
+        <v>9.392302513122559</v>
+      </c>
+    </row>
+    <row r="1571" spans="1:5">
+      <c r="A1571" s="1" t="s">
+        <v>1573</v>
+      </c>
+      <c r="C1571">
+        <v>7.805044174194336</v>
+      </c>
+      <c r="D1571">
+        <v>3.718878746032715</v>
+      </c>
+      <c r="E1571">
+        <v>4.626833438873291</v>
+      </c>
+    </row>
+    <row r="1572" spans="1:5">
+      <c r="A1572" s="1" t="s">
+        <v>1574</v>
+      </c>
+      <c r="C1572">
+        <v>5.217319488525391</v>
+      </c>
+      <c r="D1572">
+        <v>6.824065685272217</v>
+      </c>
+      <c r="E1572">
+        <v>5.33120059967041</v>
+      </c>
+    </row>
+    <row r="1573" spans="1:5">
+      <c r="A1573" s="1" t="s">
+        <v>1575</v>
+      </c>
+      <c r="C1573">
+        <v>8.284317970275879</v>
+      </c>
+      <c r="D1573">
+        <v>6.280087947845459</v>
+      </c>
+      <c r="E1573">
+        <v>8.000794410705566</v>
+      </c>
+    </row>
+    <row r="1574" spans="1:5">
+      <c r="A1574" s="1" t="s">
+        <v>1576</v>
+      </c>
+      <c r="C1574">
+        <v>0</v>
+      </c>
+      <c r="D1574">
+        <v>0</v>
+      </c>
+      <c r="E1574">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1575" spans="1:5">
+      <c r="A1575" s="1" t="s">
+        <v>1577</v>
+      </c>
+      <c r="C1575">
+        <v>6.394137382507324</v>
+      </c>
+      <c r="D1575">
+        <v>8.560955047607422</v>
+      </c>
+      <c r="E1575">
+        <v>6.362887382507324</v>
+      </c>
+    </row>
+    <row r="1576" spans="1:5">
+      <c r="A1576" s="1" t="s">
+        <v>1578</v>
+      </c>
+      <c r="C1576">
+        <v>11.05548572540283</v>
+      </c>
+      <c r="D1576">
+        <v>7.577051639556885</v>
+      </c>
+      <c r="E1576">
+        <v>9.578362464904785</v>
+      </c>
+    </row>
+    <row r="1577" spans="1:5">
+      <c r="A1577" s="1" t="s">
+        <v>1579</v>
+      </c>
+    </row>
+    <row r="1578" spans="1:5">
+      <c r="A1578" s="1" t="s">
+        <v>1580</v>
+      </c>
+      <c r="C1578">
+        <v>6.762693881988525</v>
+      </c>
+      <c r="D1578">
+        <v>4.042690277099609</v>
+      </c>
+      <c r="E1578">
+        <v>5.594243049621582</v>
+      </c>
+    </row>
+    <row r="1579" spans="1:5">
+      <c r="A1579" s="1" t="s">
+        <v>1581</v>
+      </c>
+      <c r="C1579">
+        <v>20.6947021484375</v>
+      </c>
+      <c r="D1579">
+        <v>13.15649127960205</v>
+      </c>
+      <c r="E1579">
+        <v>17.15447425842285</v>
+      </c>
+    </row>
+    <row r="1580" spans="1:5">
+      <c r="A1580" s="1" t="s">
+        <v>1582</v>
+      </c>
+      <c r="C1580">
+        <v>39.27326965332031</v>
+      </c>
+      <c r="D1580">
+        <v>28.6342945098877</v>
+      </c>
+      <c r="E1580">
+        <v>36.22970199584961</v>
+      </c>
+    </row>
+    <row r="1581" spans="1:5">
+      <c r="A1581" s="1" t="s">
+        <v>1583</v>
+      </c>
+      <c r="C1581">
+        <v>0.1719451993703842</v>
+      </c>
+      <c r="D1581">
+        <v>0.1043886616826057</v>
+      </c>
+      <c r="E1581">
+        <v>0.1447417587041855</v>
+      </c>
+    </row>
+    <row r="1582" spans="1:5">
+      <c r="A1582" s="1" t="s">
+        <v>1584</v>
+      </c>
+      <c r="C1582">
+        <v>11.74291896820068</v>
+      </c>
+      <c r="D1582">
+        <v>3.631730318069458</v>
+      </c>
+      <c r="E1582">
+        <v>5.364431381225586</v>
+      </c>
+    </row>
+    <row r="1583" spans="1:5">
+      <c r="A1583" s="1" t="s">
+        <v>1585</v>
+      </c>
+      <c r="C1583">
+        <v>3.301038503646851</v>
+      </c>
+      <c r="D1583">
+        <v>6.42235279083252</v>
+      </c>
+      <c r="E1583">
+        <v>3.348078012466431</v>
+      </c>
+    </row>
+    <row r="1584" spans="1:5">
+      <c r="A1584" s="1" t="s">
+        <v>1586</v>
+      </c>
+      <c r="C1584">
+        <v>32.87648391723633</v>
+      </c>
+      <c r="D1584">
+        <v>9.272294998168945</v>
+      </c>
+      <c r="E1584">
+        <v>14.05066108703613</v>
+      </c>
+    </row>
+    <row r="1585" spans="1:5">
+      <c r="A1585" s="1" t="s">
+        <v>1587</v>
+      </c>
+      <c r="C1585">
+        <v>7.761264801025391</v>
+      </c>
+      <c r="D1585">
+        <v>7.040313243865967</v>
+      </c>
+      <c r="E1585">
+        <v>9.064743995666504</v>
+      </c>
+    </row>
+    <row r="1586" spans="1:5">
+      <c r="A1586" s="1" t="s">
+        <v>1588</v>
+      </c>
+      <c r="C1586">
+        <v>3.006207942962646</v>
+      </c>
+      <c r="D1586">
+        <v>5.168623924255371</v>
+      </c>
+      <c r="E1586">
+        <v>2.691895246505737</v>
+      </c>
+    </row>
+    <row r="1587" spans="1:5">
+      <c r="A1587" s="1" t="s">
+        <v>1589</v>
+      </c>
+      <c r="C1587">
+        <v>8.42103385925293</v>
+      </c>
+      <c r="D1587">
+        <v>5.80614185333252</v>
+      </c>
+      <c r="E1587">
+        <v>6.721962928771973</v>
+      </c>
+    </row>
+    <row r="1588" spans="1:5">
+      <c r="A1588" s="1" t="s">
+        <v>1590</v>
+      </c>
+      <c r="C1588">
+        <v>6.32634162902832</v>
+      </c>
+      <c r="D1588">
+        <v>7.456802368164062</v>
+      </c>
+      <c r="E1588">
+        <v>6.625978946685791</v>
+      </c>
+    </row>
+    <row r="1589" spans="1:5">
+      <c r="A1589" s="1" t="s">
+        <v>1591</v>
+      </c>
+      <c r="C1589">
+        <v>4.557154178619385</v>
+      </c>
+      <c r="D1589">
+        <v>1.501488566398621</v>
+      </c>
+      <c r="E1589">
+        <v>2.179787397384644</v>
+      </c>
+    </row>
+    <row r="1590" spans="1:5">
+      <c r="A1590" s="1" t="s">
+        <v>1592</v>
+      </c>
+      <c r="C1590">
+        <v>1.038368105888367</v>
+      </c>
+      <c r="D1590">
+        <v>1.473990201950073</v>
+      </c>
+      <c r="E1590">
+        <v>0.7019628882408142</v>
+      </c>
+    </row>
+    <row r="1591" spans="1:5">
+      <c r="A1591" s="1" t="s">
+        <v>1593</v>
+      </c>
+      <c r="C1591">
+        <v>0</v>
+      </c>
+      <c r="D1591">
+        <v>0</v>
+      </c>
+      <c r="E1591">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1592" spans="1:5">
+      <c r="A1592" s="1" t="s">
+        <v>1594</v>
+      </c>
+      <c r="C1592">
+        <v>5.042815685272217</v>
+      </c>
+      <c r="D1592">
+        <v>11.15175247192383</v>
+      </c>
+      <c r="E1592">
+        <v>4.917540073394775</v>
+      </c>
+    </row>
+    <row r="1593" spans="1:5">
+      <c r="A1593" s="1" t="s">
+        <v>1595</v>
+      </c>
+      <c r="C1593">
+        <v>7.286547660827637</v>
+      </c>
+      <c r="D1593">
+        <v>5.586849212646484</v>
+      </c>
+      <c r="E1593">
+        <v>5.941165924072266</v>
+      </c>
+    </row>
+    <row r="1594" spans="1:5">
+      <c r="A1594" s="1" t="s">
+        <v>1596</v>
+      </c>
+      <c r="C1594">
+        <v>7.088432788848877</v>
+      </c>
+      <c r="D1594">
+        <v>4.300107002258301</v>
+      </c>
+      <c r="E1594">
+        <v>6.065775394439697</v>
+      </c>
+    </row>
+    <row r="1595" spans="1:5">
+      <c r="A1595" s="1" t="s">
+        <v>1597</v>
+      </c>
+      <c r="C1595">
+        <v>5.74303674697876</v>
+      </c>
+      <c r="D1595">
+        <v>10.17742156982422</v>
+      </c>
+      <c r="E1595">
+        <v>5.388164520263672</v>
+      </c>
+    </row>
+    <row r="1596" spans="1:5">
+      <c r="A1596" s="1" t="s">
+        <v>1598</v>
+      </c>
+      <c r="C1596">
+        <v>23.57781791687012</v>
+      </c>
+      <c r="D1596">
+        <v>16.32730293273926</v>
+      </c>
+      <c r="E1596">
+        <v>21.29144096374512</v>
+      </c>
+    </row>
+    <row r="1597" spans="1:5">
+      <c r="A1597" s="1" t="s">
+        <v>1599</v>
+      </c>
+      <c r="C1597">
+        <v>3.310650825500488</v>
+      </c>
+      <c r="D1597">
+        <v>1.475106120109558</v>
+      </c>
+      <c r="E1597">
+        <v>2.030621528625488</v>
+      </c>
+    </row>
+    <row r="1598" spans="1:5">
+      <c r="A1598" s="1" t="s">
+        <v>1600</v>
+      </c>
+      <c r="C1598">
+        <v>15.75833320617676</v>
+      </c>
+      <c r="D1598">
+        <v>9.981237411499023</v>
+      </c>
+      <c r="E1598">
+        <v>13.15714550018311</v>
+      </c>
+    </row>
+    <row r="1599" spans="1:5">
+      <c r="A1599" s="1" t="s">
+        <v>1601</v>
+      </c>
+      <c r="C1599">
+        <v>7.519229412078857</v>
+      </c>
+      <c r="D1599">
+        <v>3.782512426376343</v>
+      </c>
+      <c r="E1599">
+        <v>5.559781551361084</v>
+      </c>
+    </row>
+    <row r="1600" spans="1:5">
+      <c r="A1600" s="1" t="s">
+        <v>1602</v>
+      </c>
+      <c r="C1600">
+        <v>6.071076393127441</v>
+      </c>
+      <c r="D1600">
+        <v>2.045083284378052</v>
+      </c>
+      <c r="E1600">
+        <v>3.003821134567261</v>
+      </c>
+    </row>
+    <row r="1601" spans="1:5">
+      <c r="A1601" s="1" t="s">
+        <v>1603</v>
+      </c>
+      <c r="C1601">
+        <v>7.731221199035645</v>
+      </c>
+      <c r="D1601">
+        <v>4.353519439697266</v>
+      </c>
+      <c r="E1601">
+        <v>6.114250183105469</v>
+      </c>
+    </row>
+    <row r="1602" spans="1:5">
+      <c r="A1602" s="1" t="s">
+        <v>1604</v>
+      </c>
+    </row>
+    <row r="1603" spans="1:5">
+      <c r="A1603" s="1" t="s">
+        <v>1605</v>
+      </c>
+      <c r="C1603">
+        <v>5.454571723937988</v>
+      </c>
+      <c r="D1603">
+        <v>7.013100624084473</v>
+      </c>
+      <c r="E1603">
+        <v>5.521461486816406</v>
+      </c>
+    </row>
+    <row r="1604" spans="1:5">
+      <c r="A1604" s="1" t="s">
+        <v>1606</v>
+      </c>
+      <c r="C1604">
+        <v>16.88235473632812</v>
+      </c>
+      <c r="D1604">
+        <v>4.576400279998779</v>
+      </c>
+      <c r="E1604">
+        <v>7.035959720611572</v>
+      </c>
+    </row>
+    <row r="1605" spans="1:5">
+      <c r="A1605" s="1" t="s">
+        <v>1607</v>
+      </c>
+    </row>
+    <row r="1606" spans="1:5">
+      <c r="A1606" s="1" t="s">
+        <v>1608</v>
+      </c>
+      <c r="C1606">
+        <v>5.357293605804443</v>
+      </c>
+      <c r="D1606">
+        <v>7.675206184387207</v>
+      </c>
+      <c r="E1606">
+        <v>5.36582612991333</v>
+      </c>
+    </row>
+    <row r="1607" spans="1:5">
+      <c r="A1607" s="1" t="s">
+        <v>1609</v>
+      </c>
+      <c r="C1607">
+        <v>17.62862586975098</v>
+      </c>
+      <c r="D1607">
+        <v>24.42429733276367</v>
+      </c>
+      <c r="E1607">
+        <v>16.52124214172363</v>
+      </c>
+    </row>
+    <row r="1608" spans="1:5">
+      <c r="A1608" s="1" t="s">
+        <v>1610</v>
+      </c>
+      <c r="C1608">
+        <v>4.808327674865723</v>
+      </c>
+      <c r="D1608">
+        <v>5.206572532653809</v>
+      </c>
+      <c r="E1608">
+        <v>4.363952159881592</v>
+      </c>
+    </row>
+    <row r="1609" spans="1:5">
+      <c r="A1609" s="1" t="s">
+        <v>1611</v>
+      </c>
+      <c r="C1609">
+        <v>14.12550830841064</v>
+      </c>
+      <c r="D1609">
+        <v>7.923291683197021</v>
+      </c>
+      <c r="E1609">
+        <v>11.16167736053467</v>
+      </c>
+    </row>
+    <row r="1610" spans="1:5">
+      <c r="A1610" s="1" t="s">
+        <v>1612</v>
+      </c>
+      <c r="C1610">
+        <v>15.12810325622559</v>
+      </c>
+      <c r="D1610">
+        <v>14.47849941253662</v>
+      </c>
+      <c r="E1610">
+        <v>9.019692420959473</v>
+      </c>
+    </row>
+    <row r="1611" spans="1:5">
+      <c r="A1611" s="1" t="s">
+        <v>1613</v>
+      </c>
+      <c r="C1611">
+        <v>5.209517002105713</v>
+      </c>
+      <c r="D1611">
+        <v>1.556247591972351</v>
+      </c>
+      <c r="E1611">
+        <v>2.329716205596924</v>
+      </c>
+    </row>
+    <row r="1612" spans="1:5">
+      <c r="A1612" s="1" t="s">
+        <v>1614</v>
+      </c>
+      <c r="C1612">
+        <v>16.77919960021973</v>
+      </c>
+      <c r="D1612">
+        <v>10.11251068115234</v>
+      </c>
+      <c r="E1612">
+        <v>13.58703708648682</v>
+      </c>
+    </row>
+    <row r="1613" spans="1:5">
+      <c r="A1613" s="1" t="s">
+        <v>1615</v>
+      </c>
+      <c r="C1613">
+        <v>27.0897216796875</v>
+      </c>
+      <c r="D1613">
+        <v>16.36142158508301</v>
+      </c>
+      <c r="E1613">
+        <v>22.23388671875</v>
+      </c>
+    </row>
+    <row r="1614" spans="1:5">
+      <c r="A1614" s="1" t="s">
+        <v>1616</v>
+      </c>
+      <c r="C1614">
+        <v>10.69262409210205</v>
+      </c>
+      <c r="D1614">
+        <v>7.1543869972229</v>
+      </c>
+      <c r="E1614">
+        <v>9.418718338012695</v>
+      </c>
+    </row>
+    <row r="1615" spans="1:5">
+      <c r="A1615" s="1" t="s">
+        <v>1617</v>
+      </c>
+      <c r="C1615">
+        <v>15.13704109191895</v>
+      </c>
+      <c r="D1615">
+        <v>16.02740478515625</v>
+      </c>
+      <c r="E1615">
+        <v>14.33720111846924</v>
+      </c>
+    </row>
+    <row r="1616" spans="1:5">
+      <c r="A1616" s="1" t="s">
+        <v>1618</v>
+      </c>
+      <c r="C1616">
+        <v>5.605865478515625</v>
+      </c>
+      <c r="D1616">
+        <v>2.043757200241089</v>
+      </c>
+      <c r="E1616">
+        <v>2.638266801834106</v>
+      </c>
+    </row>
+    <row r="1617" spans="1:5">
+      <c r="A1617" s="1" t="s">
+        <v>1619</v>
+      </c>
+      <c r="C1617">
+        <v>9.738034248352051</v>
+      </c>
+      <c r="D1617">
+        <v>4.199984550476074</v>
+      </c>
+      <c r="E1617">
+        <v>5.366030216217041</v>
+      </c>
+    </row>
+    <row r="1618" spans="1:5">
+      <c r="A1618" s="1" t="s">
+        <v>1620</v>
+      </c>
+      <c r="C1618">
+        <v>0.5233414769172668</v>
+      </c>
+      <c r="D1618">
+        <v>0.4360266327857971</v>
+      </c>
+      <c r="E1618">
+        <v>0.8388299942016602</v>
+      </c>
+    </row>
+    <row r="1619" spans="1:5">
+      <c r="A1619" s="1" t="s">
+        <v>1621</v>
+      </c>
+      <c r="C1619">
+        <v>0</v>
+      </c>
+      <c r="D1619">
+        <v>0</v>
+      </c>
+      <c r="E1619">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1620" spans="1:5">
+      <c r="A1620" s="1" t="s">
+        <v>1622</v>
+      </c>
+      <c r="C1620">
+        <v>4.47007942199707</v>
+      </c>
+      <c r="D1620">
+        <v>1.277347683906555</v>
+      </c>
+      <c r="E1620">
+        <v>2.16560959815979</v>
+      </c>
+    </row>
+    <row r="1621" spans="1:5">
+      <c r="A1621" s="1" t="s">
+        <v>1623</v>
+      </c>
+      <c r="C1621">
+        <v>8.815543174743652</v>
+      </c>
+      <c r="D1621">
+        <v>3.850122690200806</v>
+      </c>
+      <c r="E1621">
+        <v>4.854906558990479</v>
+      </c>
+    </row>
+    <row r="1622" spans="1:5">
+      <c r="A1622" s="1" t="s">
+        <v>1624</v>
+      </c>
+      <c r="C1622">
+        <v>9.261082649230957</v>
+      </c>
+      <c r="D1622">
+        <v>2.884140491485596</v>
+      </c>
+      <c r="E1622">
+        <v>4.890402793884277</v>
+      </c>
+    </row>
+    <row r="1623" spans="1:5">
+      <c r="A1623" s="1" t="s">
+        <v>1625</v>
+      </c>
+      <c r="C1623">
+        <v>258.2917785644531</v>
+      </c>
+      <c r="D1623">
+        <v>136.466552734375</v>
+      </c>
+      <c r="E1623">
+        <v>175.5612945556641</v>
+      </c>
+    </row>
+    <row r="1624" spans="1:5">
+      <c r="A1624" s="1" t="s">
+        <v>1626</v>
+      </c>
+      <c r="C1624">
+        <v>16.54279899597168</v>
+      </c>
+      <c r="D1624">
+        <v>4.707825660705566</v>
+      </c>
+      <c r="E1624">
+        <v>12.96969699859619</v>
+      </c>
+    </row>
+    <row r="1625" spans="1:5">
+      <c r="A1625" s="1" t="s">
+        <v>1627</v>
+      </c>
+      <c r="C1625">
+        <v>19.8044319152832</v>
+      </c>
+      <c r="D1625">
+        <v>6.220066070556641</v>
+      </c>
+      <c r="E1625">
+        <v>11.0101261138916</v>
+      </c>
+    </row>
+    <row r="1626" spans="1:5">
+      <c r="A1626" s="1" t="s">
+        <v>1628</v>
+      </c>
+      <c r="C1626">
+        <v>24.73040199279785</v>
+      </c>
+      <c r="D1626">
+        <v>2.776750326156616</v>
+      </c>
+      <c r="E1626">
+        <v>5.739630699157715</v>
+      </c>
+    </row>
+    <row r="1627" spans="1:5">
+      <c r="A1627" s="1" t="s">
+        <v>1629</v>
+      </c>
+      <c r="C1627">
+        <v>7.492061614990234</v>
+      </c>
+      <c r="D1627">
+        <v>4.025644302368164</v>
+      </c>
+      <c r="E1627">
+        <v>5.096120357513428</v>
+      </c>
+    </row>
+    <row r="1628" spans="1:5">
+      <c r="A1628" s="1" t="s">
+        <v>1630</v>
+      </c>
+      <c r="C1628">
+        <v>5.104976654052734</v>
+      </c>
+      <c r="D1628">
+        <v>6.463869571685791</v>
+      </c>
+      <c r="E1628">
+        <v>6.69638729095459</v>
+      </c>
+    </row>
+    <row r="1629" spans="1:5">
+      <c r="A1629" s="1" t="s">
+        <v>1631</v>
+      </c>
+      <c r="C1629">
+        <v>8.252448081970215</v>
+      </c>
+      <c r="D1629">
+        <v>9.731402397155762</v>
+      </c>
+      <c r="E1629">
+        <v>11.58996772766113</v>
+      </c>
+    </row>
+    <row r="1630" spans="1:5">
+      <c r="A1630" s="1" t="s">
+        <v>1632</v>
+      </c>
+      <c r="C1630">
+        <v>0</v>
+      </c>
+      <c r="D1630">
+        <v>0</v>
+      </c>
+      <c r="E1630">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1631" spans="1:5">
+      <c r="A1631" s="1" t="s">
+        <v>1633</v>
+      </c>
+      <c r="C1631">
+        <v>6.43330192565918</v>
+      </c>
+      <c r="D1631">
+        <v>9.163071632385254</v>
+      </c>
+      <c r="E1631">
+        <v>9.475974082946777</v>
+      </c>
+    </row>
+    <row r="1632" spans="1:5">
+      <c r="A1632" s="1" t="s">
+        <v>1634</v>
+      </c>
+      <c r="C1632">
+        <v>11.69315528869629</v>
+      </c>
+      <c r="D1632">
+        <v>3.841461896896362</v>
+      </c>
+      <c r="E1632">
+        <v>6.245113372802734</v>
+      </c>
+    </row>
+    <row r="1633" spans="1:5">
+      <c r="A1633" s="1" t="s">
+        <v>1635</v>
+      </c>
+      <c r="C1633" t="s">
+        <v>1850</v>
+      </c>
+      <c r="D1633" t="s">
+        <v>1850</v>
+      </c>
+      <c r="E1633" t="s">
+        <v>1850</v>
+      </c>
+    </row>
+    <row r="1634" spans="1:5">
+      <c r="A1634" s="1" t="s">
+        <v>1636</v>
+      </c>
+      <c r="C1634">
+        <v>7.440120220184326</v>
+      </c>
+      <c r="D1634">
+        <v>3.032204627990723</v>
+      </c>
+      <c r="E1634">
+        <v>4.695976257324219</v>
+      </c>
+    </row>
+    <row r="1635" spans="1:5">
+      <c r="A1635" s="1" t="s">
+        <v>1637</v>
+      </c>
+      <c r="C1635">
+        <v>26.57224082946777</v>
+      </c>
+      <c r="D1635">
+        <v>8.425778388977051</v>
+      </c>
+      <c r="E1635">
+        <v>13.66039848327637</v>
+      </c>
+    </row>
+    <row r="1636" spans="1:5">
+      <c r="A1636" s="1" t="s">
+        <v>1638</v>
+      </c>
+      <c r="C1636">
+        <v>64.57964324951172</v>
+      </c>
+      <c r="D1636">
+        <v>27.20745658874512</v>
+      </c>
+      <c r="E1636">
+        <v>40.05918884277344</v>
+      </c>
+    </row>
+    <row r="1637" spans="1:5">
+      <c r="A1637" s="1" t="s">
+        <v>1639</v>
+      </c>
+      <c r="C1637">
+        <v>0.2020705193281174</v>
+      </c>
+      <c r="D1637">
+        <v>0.0731804296374321</v>
+      </c>
+      <c r="E1637">
+        <v>0.1195153743028641</v>
+      </c>
+    </row>
+    <row r="1638" spans="1:5">
+      <c r="A1638" s="1" t="s">
+        <v>1640</v>
+      </c>
+      <c r="C1638">
+        <v>12.48336982727051</v>
+      </c>
+      <c r="D1638">
+        <v>4.733230590820312</v>
+      </c>
+      <c r="E1638">
+        <v>6.109340190887451</v>
+      </c>
+    </row>
+    <row r="1639" spans="1:5">
+      <c r="A1639" s="1" t="s">
+        <v>1641</v>
+      </c>
+      <c r="C1639">
+        <v>3.567953586578369</v>
+      </c>
+      <c r="D1639">
+        <v>4.774534225463867</v>
+      </c>
+      <c r="E1639">
+        <v>4.447052001953125</v>
+      </c>
+    </row>
+    <row r="1640" spans="1:5">
+      <c r="A1640" s="1" t="s">
+        <v>1642</v>
+      </c>
+      <c r="C1640">
+        <v>22.79682350158691</v>
+      </c>
+      <c r="D1640">
+        <v>12.21390151977539</v>
+      </c>
+      <c r="E1640">
+        <v>14.74152374267578</v>
+      </c>
+    </row>
+    <row r="1641" spans="1:5">
+      <c r="A1641" s="1" t="s">
+        <v>1643</v>
+      </c>
+      <c r="C1641">
+        <v>7.997027397155762</v>
+      </c>
+      <c r="D1641">
+        <v>2.224300622940063</v>
+      </c>
+      <c r="E1641">
+        <v>3.400604009628296</v>
+      </c>
+    </row>
+    <row r="1642" spans="1:5">
+      <c r="A1642" s="1" t="s">
+        <v>1644</v>
+      </c>
+      <c r="C1642">
+        <v>5.722473621368408</v>
+      </c>
+      <c r="D1642">
+        <v>5.05992317199707</v>
+      </c>
+      <c r="E1642">
+        <v>4.53356409072876</v>
+      </c>
+    </row>
+    <row r="1643" spans="1:5">
+      <c r="A1643" s="1" t="s">
+        <v>1645</v>
+      </c>
+      <c r="C1643">
+        <v>12.35949611663818</v>
+      </c>
+      <c r="D1643">
+        <v>4.777587890625</v>
+      </c>
+      <c r="E1643">
+        <v>7.159670829772949</v>
+      </c>
+    </row>
+    <row r="1644" spans="1:5">
+      <c r="A1644" s="1" t="s">
+        <v>1646</v>
+      </c>
+      <c r="C1644">
+        <v>6.117447376251221</v>
+      </c>
+      <c r="D1644">
+        <v>8.340056419372559</v>
+      </c>
+      <c r="E1644">
+        <v>9.044095039367676</v>
+      </c>
+    </row>
+    <row r="1645" spans="1:5">
+      <c r="A1645" s="1" t="s">
+        <v>1647</v>
+      </c>
+      <c r="C1645">
+        <v>5.474507331848145</v>
+      </c>
+      <c r="D1645">
+        <v>2.286153316497803</v>
+      </c>
+      <c r="E1645">
+        <v>2.905562877655029</v>
+      </c>
+    </row>
+    <row r="1646" spans="1:5">
+      <c r="A1646" s="1" t="s">
+        <v>1648</v>
+      </c>
+      <c r="C1646">
+        <v>1.297892808914185</v>
+      </c>
+      <c r="D1646">
+        <v>0.7666367292404175</v>
+      </c>
+      <c r="E1646">
+        <v>0.6859222650527954</v>
+      </c>
+    </row>
+    <row r="1647" spans="1:5">
+      <c r="A1647" s="1" t="s">
+        <v>1649</v>
+      </c>
+      <c r="C1647">
+        <v>0</v>
+      </c>
+      <c r="D1647">
+        <v>0</v>
+      </c>
+      <c r="E1647">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1648" spans="1:5">
+      <c r="A1648" s="1" t="s">
+        <v>1650</v>
+      </c>
+      <c r="C1648">
+        <v>6.134452819824219</v>
+      </c>
+      <c r="D1648">
+        <v>8.365181922912598</v>
+      </c>
+      <c r="E1648">
+        <v>8.335940361022949</v>
+      </c>
+    </row>
+    <row r="1649" spans="1:5">
+      <c r="A1649" s="1" t="s">
+        <v>1651</v>
+      </c>
+      <c r="C1649">
+        <v>8.801318168640137</v>
+      </c>
+      <c r="D1649">
+        <v>4.475300312042236</v>
+      </c>
+      <c r="E1649">
+        <v>5.969583034515381</v>
+      </c>
+    </row>
+    <row r="1650" spans="1:5">
+      <c r="A1650" s="1" t="s">
+        <v>1652</v>
+      </c>
+      <c r="C1650">
+        <v>11.01436901092529</v>
+      </c>
+      <c r="D1650">
+        <v>6.203943252563477</v>
+      </c>
+      <c r="E1650">
+        <v>8.497133255004883</v>
+      </c>
+    </row>
+    <row r="1651" spans="1:5">
+      <c r="A1651" s="1" t="s">
+        <v>1653</v>
+      </c>
+      <c r="C1651">
+        <v>7.392740726470947</v>
+      </c>
+      <c r="D1651">
+        <v>6.905039310455322</v>
+      </c>
+      <c r="E1651">
+        <v>6.690525054931641</v>
+      </c>
+    </row>
+    <row r="1652" spans="1:5">
+      <c r="A1652" s="1" t="s">
+        <v>1654</v>
+      </c>
+      <c r="C1652">
+        <v>25.21620750427246</v>
+      </c>
+      <c r="D1652">
+        <v>10.66015148162842</v>
+      </c>
+      <c r="E1652">
+        <v>15.90944576263428</v>
+      </c>
+    </row>
+    <row r="1653" spans="1:5">
+      <c r="A1653" s="1" t="s">
+        <v>1655</v>
+      </c>
+      <c r="C1653">
+        <v>4.874935150146484</v>
+      </c>
+      <c r="D1653">
+        <v>1.590208768844604</v>
+      </c>
+      <c r="E1653">
+        <v>2.079553365707397</v>
+      </c>
+    </row>
+    <row r="1654" spans="1:5">
+      <c r="A1654" s="1" t="s">
+        <v>1656</v>
+      </c>
+      <c r="C1654">
+        <v>17.46056747436523</v>
+      </c>
+      <c r="D1654">
+        <v>6.123682498931885</v>
+      </c>
+      <c r="E1654">
+        <v>9.77171516418457</v>
+      </c>
+    </row>
+    <row r="1655" spans="1:5">
+      <c r="A1655" s="1" t="s">
+        <v>1657</v>
+      </c>
+      <c r="C1655">
+        <v>13.35766315460205</v>
+      </c>
+      <c r="D1655">
+        <v>3.324732542037964</v>
+      </c>
+      <c r="E1655">
+        <v>5.870448589324951</v>
+      </c>
+    </row>
+    <row r="1656" spans="1:5">
+      <c r="A1656" s="1" t="s">
+        <v>1658</v>
+      </c>
+      <c r="C1656">
+        <v>6.959475040435791</v>
+      </c>
+      <c r="D1656">
+        <v>2.993626594543457</v>
+      </c>
+      <c r="E1656">
+        <v>3.782405853271484</v>
+      </c>
+    </row>
+    <row r="1657" spans="1:5">
+      <c r="A1657" s="1" t="s">
+        <v>1659</v>
+      </c>
+      <c r="C1657">
+        <v>8.454241752624512</v>
+      </c>
+      <c r="D1657">
+        <v>2.80513072013855</v>
+      </c>
+      <c r="E1657">
+        <v>4.683521747589111</v>
+      </c>
+    </row>
+    <row r="1658" spans="1:5">
+      <c r="A1658" s="1" t="s">
+        <v>1660</v>
+      </c>
+    </row>
+    <row r="1659" spans="1:5">
+      <c r="A1659" s="1" t="s">
+        <v>1661</v>
+      </c>
+      <c r="C1659">
+        <v>6.308302402496338</v>
+      </c>
+      <c r="D1659">
+        <v>4.887923717498779</v>
+      </c>
+      <c r="E1659">
+        <v>5.484259128570557</v>
+      </c>
+    </row>
+    <row r="1660" spans="1:5">
+      <c r="A1660" s="1" t="s">
+        <v>1662</v>
+      </c>
+      <c r="C1660">
+        <v>18.95363616943359</v>
+      </c>
+      <c r="D1660">
+        <v>8.666867256164551</v>
+      </c>
+      <c r="E1660">
+        <v>10.93660354614258</v>
+      </c>
+    </row>
+    <row r="1661" spans="1:5">
+      <c r="A1661" s="1" t="s">
+        <v>1663</v>
+      </c>
+      <c r="C1661" t="s">
+        <v>1850</v>
+      </c>
+    </row>
+    <row r="1662" spans="1:5">
+      <c r="A1662" s="1" t="s">
+        <v>1664</v>
+      </c>
+      <c r="C1662">
+        <v>5.833412647247314</v>
+      </c>
+      <c r="D1662">
+        <v>6.496257781982422</v>
+      </c>
+      <c r="E1662">
+        <v>6.756235122680664</v>
+      </c>
+    </row>
+    <row r="1663" spans="1:5">
+      <c r="A1663" s="1" t="s">
+        <v>1665</v>
+      </c>
+      <c r="C1663">
+        <v>14.34436321258545</v>
+      </c>
+      <c r="D1663">
+        <v>18.62523078918457</v>
+      </c>
+      <c r="E1663">
+        <v>19.02203559875488</v>
+      </c>
+    </row>
+    <row r="1664" spans="1:5">
+      <c r="A1664" s="1" t="s">
+        <v>1666</v>
+      </c>
+      <c r="C1664">
+        <v>6.56011962890625</v>
+      </c>
+      <c r="D1664">
+        <v>4.989952564239502</v>
+      </c>
+      <c r="E1664">
+        <v>5.761343002319336</v>
+      </c>
+    </row>
+    <row r="1665" spans="1:5">
+      <c r="A1665" s="1" t="s">
+        <v>1667</v>
+      </c>
+      <c r="C1665">
+        <v>17.10034370422363</v>
+      </c>
+      <c r="D1665">
+        <v>6.879031658172607</v>
+      </c>
+      <c r="E1665">
+        <v>10.46094703674316</v>
+      </c>
+    </row>
+    <row r="1666" spans="1:5">
+      <c r="A1666" s="1" t="s">
+        <v>1668</v>
+      </c>
+      <c r="C1666">
+        <v>12.48107147216797</v>
+      </c>
+      <c r="D1666">
+        <v>10.26449584960938</v>
+      </c>
+      <c r="E1666">
+        <v>10.41531372070312</v>
+      </c>
+    </row>
+    <row r="1667" spans="1:5">
+      <c r="A1667" s="1" t="s">
+        <v>1669</v>
+      </c>
+      <c r="C1667">
+        <v>5.566607475280762</v>
+      </c>
+      <c r="D1667">
+        <v>2.252876043319702</v>
+      </c>
+      <c r="E1667">
+        <v>2.886575698852539</v>
+      </c>
+    </row>
+    <row r="1668" spans="1:5">
+      <c r="A1668" s="1" t="s">
+        <v>1670</v>
+      </c>
+      <c r="C1668">
+        <v>33.07224273681641</v>
+      </c>
+      <c r="D1668">
+        <v>9.461898803710938</v>
+      </c>
+      <c r="E1668">
+        <v>16.17212104797363</v>
+      </c>
+    </row>
+    <row r="1669" spans="1:5">
+      <c r="A1669" s="1" t="s">
+        <v>1671</v>
+      </c>
+      <c r="C1669">
+        <v>50.18161773681641</v>
+      </c>
+      <c r="D1669">
+        <v>14.6680850982666</v>
+      </c>
+      <c r="E1669">
+        <v>24.83562660217285</v>
+      </c>
+    </row>
+    <row r="1670" spans="1:5">
+      <c r="A1670" s="1" t="s">
+        <v>1672</v>
+      </c>
+      <c r="C1670">
+        <v>16.34963989257812</v>
+      </c>
+      <c r="D1670">
+        <v>4.572781085968018</v>
+      </c>
+      <c r="E1670">
+        <v>7.740046977996826</v>
+      </c>
+    </row>
+    <row r="1671" spans="1:5">
+      <c r="A1671" s="1" t="s">
+        <v>1673</v>
+      </c>
+      <c r="C1671">
+        <v>13.68764114379883</v>
+      </c>
+      <c r="D1671">
+        <v>15.86247730255127</v>
+      </c>
+      <c r="E1671">
+        <v>18.48310661315918</v>
+      </c>
+    </row>
+    <row r="1672" spans="1:5">
+      <c r="A1672" s="1" t="s">
+        <v>1674</v>
+      </c>
+      <c r="C1672">
+        <v>4.480499744415283</v>
+      </c>
+      <c r="D1672">
+        <v>1.744734525680542</v>
+      </c>
+      <c r="E1672">
+        <v>2.807522773742676</v>
+      </c>
+    </row>
+    <row r="1673" spans="1:5">
+      <c r="A1673" s="1" t="s">
+        <v>1675</v>
+      </c>
+      <c r="C1673">
+        <v>6.154001712799072</v>
+      </c>
+      <c r="D1673">
+        <v>2.314094543457031</v>
+      </c>
+      <c r="E1673">
+        <v>4.219831943511963</v>
+      </c>
+    </row>
+    <row r="1674" spans="1:5">
+      <c r="A1674" s="1" t="s">
+        <v>1676</v>
+      </c>
+      <c r="C1674">
+        <v>0.7848028540611267</v>
+      </c>
+      <c r="D1674">
+        <v>0.4901438653469086</v>
+      </c>
+      <c r="E1674">
+        <v>1.592004418373108</v>
+      </c>
+    </row>
+    <row r="1675" spans="1:5">
+      <c r="A1675" s="1" t="s">
+        <v>1677</v>
+      </c>
+      <c r="C1675">
+        <v>0</v>
+      </c>
+      <c r="D1675">
+        <v>0</v>
+      </c>
+      <c r="E1675">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1676" spans="1:5">
+      <c r="A1676" s="1" t="s">
+        <v>1678</v>
+      </c>
+      <c r="C1676">
+        <v>3.347595691680908</v>
+      </c>
+      <c r="D1676">
+        <v>1.190008282661438</v>
+      </c>
+      <c r="E1676">
+        <v>2.72197151184082</v>
+      </c>
+    </row>
+    <row r="1677" spans="1:5">
+      <c r="A1677" s="1" t="s">
+        <v>1679</v>
+      </c>
+      <c r="C1677">
+        <v>9.77546501159668</v>
+      </c>
+      <c r="D1677">
+        <v>4.10933780670166</v>
+      </c>
+      <c r="E1677">
+        <v>6.736494064331055</v>
+      </c>
+    </row>
+    <row r="1678" spans="1:5">
+      <c r="A1678" s="1" t="s">
+        <v>1680</v>
+      </c>
+      <c r="C1678">
+        <v>6.484137058258057</v>
+      </c>
+      <c r="D1678">
+        <v>2.65373420715332</v>
+      </c>
+      <c r="E1678">
+        <v>5.91418981552124</v>
+      </c>
+    </row>
+    <row r="1679" spans="1:5">
+      <c r="A1679" s="1" t="s">
+        <v>1681</v>
+      </c>
+      <c r="C1679">
+        <v>79.62158203125</v>
+      </c>
+      <c r="D1679">
+        <v>76.81961059570312</v>
+      </c>
+      <c r="E1679">
+        <v>114.1668548583984</v>
+      </c>
+    </row>
+    <row r="1680" spans="1:5">
+      <c r="A1680" s="1" t="s">
+        <v>1682</v>
+      </c>
+      <c r="C1680">
+        <v>39.60617828369141</v>
+      </c>
+      <c r="D1680">
+        <v>15.1965274810791</v>
+      </c>
+      <c r="E1680">
+        <v>66.42588806152344</v>
+      </c>
+    </row>
+    <row r="1681" spans="1:5">
+      <c r="A1681" s="1" t="s">
+        <v>1683</v>
+      </c>
+      <c r="C1681">
+        <v>22.52401733398438</v>
+      </c>
+      <c r="D1681">
+        <v>8.633131980895996</v>
+      </c>
+      <c r="E1681">
+        <v>22.21395683288574</v>
+      </c>
+    </row>
+    <row r="1682" spans="1:5">
+      <c r="A1682" s="1" t="s">
+        <v>1684</v>
+      </c>
+      <c r="C1682">
+        <v>19.22593116760254</v>
+      </c>
+      <c r="D1682">
+        <v>2.832573652267456</v>
+      </c>
+      <c r="E1682">
+        <v>8.968869209289551</v>
+      </c>
+    </row>
+    <row r="1683" spans="1:5">
+      <c r="A1683" s="1" t="s">
+        <v>1685</v>
+      </c>
+      <c r="C1683">
+        <v>4.321837425231934</v>
+      </c>
+      <c r="D1683">
+        <v>3.435940742492676</v>
+      </c>
+      <c r="E1683">
+        <v>5.030980110168457</v>
+      </c>
+    </row>
+    <row r="1684" spans="1:5">
+      <c r="A1684" s="1" t="s">
+        <v>1686</v>
+      </c>
+      <c r="C1684">
+        <v>5.418598651885986</v>
+      </c>
+      <c r="D1684">
+        <v>6.727268695831299</v>
+      </c>
+      <c r="E1684">
+        <v>8.240914344787598</v>
+      </c>
+    </row>
+    <row r="1685" spans="1:5">
+      <c r="A1685" s="1" t="s">
+        <v>1687</v>
+      </c>
+      <c r="C1685">
+        <v>5.568806648254395</v>
+      </c>
+      <c r="D1685">
+        <v>10.01254749298096</v>
+      </c>
+      <c r="E1685">
+        <v>12.93004512786865</v>
+      </c>
+    </row>
+    <row r="1686" spans="1:5">
+      <c r="A1686" s="1" t="s">
+        <v>1688</v>
+      </c>
+      <c r="C1686">
+        <v>0.8647152185440063</v>
+      </c>
+      <c r="D1686">
+        <v>0</v>
+      </c>
+      <c r="E1686">
+        <v>0.9485371708869934</v>
+      </c>
+    </row>
+    <row r="1687" spans="1:5">
+      <c r="A1687" s="1" t="s">
+        <v>1689</v>
+      </c>
+      <c r="C1687">
+        <v>6.01744270324707</v>
+      </c>
+      <c r="D1687">
+        <v>8.228984832763672</v>
+      </c>
+      <c r="E1687">
+        <v>10.12661266326904</v>
+      </c>
+    </row>
+    <row r="1688" spans="1:5">
+      <c r="A1688" s="1" t="s">
+        <v>1690</v>
+      </c>
+      <c r="C1688">
+        <v>9.4852294921875</v>
+      </c>
+      <c r="D1688">
+        <v>3.893314123153687</v>
+      </c>
+      <c r="E1688">
+        <v>8.124289512634277</v>
+      </c>
+    </row>
+    <row r="1689" spans="1:5">
+      <c r="A1689" s="1" t="s">
+        <v>1691</v>
+      </c>
+      <c r="C1689">
+        <v>186.4793243408203</v>
+      </c>
+      <c r="D1689">
+        <v>149.0765838623047</v>
+      </c>
+      <c r="E1689">
+        <v>265.7361145019531</v>
+      </c>
+    </row>
+    <row r="1690" spans="1:5">
+      <c r="A1690" s="1" t="s">
+        <v>1692</v>
+      </c>
+      <c r="C1690">
+        <v>5.047217845916748</v>
+      </c>
+      <c r="D1690">
+        <v>2.546925783157349</v>
+      </c>
+      <c r="E1690">
+        <v>5.138813495635986</v>
+      </c>
+    </row>
+    <row r="1691" spans="1:5">
+      <c r="A1691" s="1" t="s">
+        <v>1693</v>
+      </c>
+      <c r="C1691">
+        <v>23.08060264587402</v>
+      </c>
+      <c r="D1691">
+        <v>8.045557975769043</v>
+      </c>
+      <c r="E1691">
+        <v>17.99568748474121</v>
+      </c>
+    </row>
+    <row r="1692" spans="1:5">
+      <c r="A1692" s="1" t="s">
+        <v>1694</v>
+      </c>
+      <c r="C1692">
+        <v>88.39601135253906</v>
+      </c>
+      <c r="D1692">
+        <v>52.10440444946289</v>
+      </c>
+      <c r="E1692">
+        <v>98.48002624511719</v>
+      </c>
+    </row>
+    <row r="1693" spans="1:5">
+      <c r="A1693" s="1" t="s">
+        <v>1695</v>
+      </c>
+      <c r="C1693">
+        <v>0.1301821023225784</v>
+      </c>
+      <c r="D1693">
+        <v>0.05898470059037209</v>
+      </c>
+      <c r="E1693">
+        <v>0.1292644441127777</v>
+      </c>
+    </row>
+    <row r="1694" spans="1:5">
+      <c r="A1694" s="1" t="s">
+        <v>1696</v>
+      </c>
+      <c r="C1694">
+        <v>7.547549724578857</v>
+      </c>
+      <c r="D1694">
+        <v>2.703146457672119</v>
+      </c>
+      <c r="E1694">
+        <v>4.918186187744141</v>
+      </c>
+    </row>
+    <row r="1695" spans="1:5">
+      <c r="A1695" s="1" t="s">
+        <v>1697</v>
+      </c>
+      <c r="C1695">
+        <v>3.625307083129883</v>
+      </c>
+      <c r="D1695">
+        <v>4.513206005096436</v>
+      </c>
+      <c r="E1695">
+        <v>5.577173709869385</v>
+      </c>
+    </row>
+    <row r="1696" spans="1:5">
+      <c r="A1696" s="1" t="s">
+        <v>1698</v>
+      </c>
+      <c r="C1696">
+        <v>9.079269409179688</v>
+      </c>
+      <c r="D1696">
+        <v>4.562314510345459</v>
+      </c>
+      <c r="E1696">
+        <v>7.929461002349854</v>
+      </c>
+    </row>
+    <row r="1697" spans="1:5">
+      <c r="A1697" s="1" t="s">
+        <v>1699</v>
+      </c>
+      <c r="C1697">
+        <v>13.52333641052246</v>
+      </c>
+      <c r="D1697">
+        <v>2.543035745620728</v>
+      </c>
+      <c r="E1697">
+        <v>7.043727874755859</v>
+      </c>
+    </row>
+    <row r="1698" spans="1:5">
+      <c r="A1698" s="1" t="s">
+        <v>1700</v>
+      </c>
+      <c r="C1698">
+        <v>6.48016881942749</v>
+      </c>
+      <c r="D1698">
+        <v>7.621101379394531</v>
+      </c>
+      <c r="E1698">
+        <v>9.008834838867188</v>
+      </c>
+    </row>
+    <row r="1699" spans="1:5">
+      <c r="A1699" s="1" t="s">
+        <v>1701</v>
+      </c>
+      <c r="C1699">
+        <v>8.899893760681152</v>
+      </c>
+      <c r="D1699">
+        <v>4.69050121307373</v>
+      </c>
+      <c r="E1699">
+        <v>8.91774845123291</v>
+      </c>
+    </row>
+    <row r="1700" spans="1:5">
+      <c r="A1700" s="1" t="s">
+        <v>1702</v>
+      </c>
+      <c r="C1700">
+        <v>5.093542098999023</v>
+      </c>
+      <c r="D1700">
+        <v>7.328390598297119</v>
+      </c>
+      <c r="E1700">
+        <v>9.236117362976074</v>
+      </c>
+    </row>
+    <row r="1701" spans="1:5">
+      <c r="A1701" s="1" t="s">
+        <v>1703</v>
+      </c>
+      <c r="C1701">
+        <v>4.950162410736084</v>
+      </c>
+      <c r="D1701">
+        <v>2.124711513519287</v>
+      </c>
+      <c r="E1701">
+        <v>3.386761665344238</v>
+      </c>
+    </row>
+    <row r="1702" spans="1:5">
+      <c r="A1702" s="1" t="s">
+        <v>1704</v>
+      </c>
+      <c r="C1702">
+        <v>1.428417921066284</v>
+      </c>
+      <c r="D1702">
+        <v>1.353857278823853</v>
+      </c>
+      <c r="E1702">
+        <v>1.622195601463318</v>
+      </c>
+    </row>
+    <row r="1703" spans="1:5">
+      <c r="A1703" s="1" t="s">
+        <v>1705</v>
+      </c>
+      <c r="C1703">
+        <v>0</v>
+      </c>
+      <c r="D1703">
+        <v>0</v>
+      </c>
+      <c r="E1703">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1704" spans="1:5">
+      <c r="A1704" s="1" t="s">
+        <v>1706</v>
+      </c>
+      <c r="C1704">
+        <v>8.416378974914551</v>
+      </c>
+      <c r="D1704">
+        <v>12.31420135498047</v>
+      </c>
+      <c r="E1704">
+        <v>11.86402988433838</v>
+      </c>
+    </row>
+    <row r="1705" spans="1:5">
+      <c r="A1705" s="1" t="s">
+        <v>1707</v>
+      </c>
+      <c r="C1705">
+        <v>6.966753005981445</v>
+      </c>
+      <c r="D1705">
+        <v>4.523853778839111</v>
+      </c>
+      <c r="E1705">
+        <v>7.721343517303467</v>
+      </c>
+    </row>
+    <row r="1706" spans="1:5">
+      <c r="A1706" s="1" t="s">
+        <v>1708</v>
+      </c>
+      <c r="C1706">
+        <v>6.938195705413818</v>
+      </c>
+      <c r="D1706">
+        <v>5.957928657531738</v>
+      </c>
+      <c r="E1706">
+        <v>8.969576835632324</v>
+      </c>
+    </row>
+    <row r="1707" spans="1:5">
+      <c r="A1707" s="1" t="s">
+        <v>1709</v>
+      </c>
+      <c r="C1707">
+        <v>7.376992702484131</v>
+      </c>
+      <c r="D1707">
+        <v>8.71722412109375</v>
+      </c>
+      <c r="E1707">
+        <v>11.34281063079834</v>
+      </c>
+    </row>
+    <row r="1708" spans="1:5">
+      <c r="A1708" s="1" t="s">
+        <v>1710</v>
+      </c>
+      <c r="C1708">
+        <v>17.44312858581543</v>
+      </c>
+      <c r="D1708">
+        <v>8.985373497009277</v>
+      </c>
+      <c r="E1708">
+        <v>17.85552215576172</v>
+      </c>
+    </row>
+    <row r="1709" spans="1:5">
+      <c r="A1709" s="1" t="s">
+        <v>1711</v>
+      </c>
+      <c r="C1709">
+        <v>4.07367467880249</v>
+      </c>
+      <c r="D1709">
+        <v>1.525945901870728</v>
+      </c>
+      <c r="E1709">
+        <v>2.342447519302368</v>
+      </c>
+    </row>
+    <row r="1710" spans="1:5">
+      <c r="A1710" s="1" t="s">
+        <v>1712</v>
+      </c>
+      <c r="C1710">
+        <v>11.42725372314453</v>
+      </c>
+      <c r="D1710">
+        <v>5.693480968475342</v>
+      </c>
+      <c r="E1710">
+        <v>11.79154586791992</v>
+      </c>
+    </row>
+    <row r="1711" spans="1:5">
+      <c r="A1711" s="1" t="s">
+        <v>1713</v>
+      </c>
+      <c r="C1711">
+        <v>15.96875190734863</v>
+      </c>
+      <c r="D1711">
+        <v>3.220927000045776</v>
+      </c>
+      <c r="E1711">
+        <v>8.964547157287598</v>
+      </c>
+    </row>
+    <row r="1712" spans="1:5">
+      <c r="A1712" s="1" t="s">
+        <v>1714</v>
+      </c>
+      <c r="C1712">
+        <v>5.863672256469727</v>
+      </c>
+      <c r="D1712">
+        <v>2.409004926681519</v>
+      </c>
+      <c r="E1712">
+        <v>3.946512699127197</v>
+      </c>
+    </row>
+    <row r="1713" spans="1:5">
+      <c r="A1713" s="1" t="s">
+        <v>1715</v>
+      </c>
+      <c r="C1713">
+        <v>5.71294641494751</v>
+      </c>
+      <c r="D1713">
+        <v>2.225347757339478</v>
+      </c>
+      <c r="E1713">
+        <v>5.062297344207764</v>
+      </c>
+    </row>
+    <row r="1714" spans="1:5">
+      <c r="A1714" s="1" t="s">
+        <v>1716</v>
+      </c>
+    </row>
+    <row r="1715" spans="1:5">
+      <c r="A1715" s="1" t="s">
+        <v>1717</v>
+      </c>
+      <c r="C1715">
+        <v>5.789107322692871</v>
+      </c>
+      <c r="D1715">
+        <v>5.588135719299316</v>
+      </c>
+      <c r="E1715">
+        <v>7.650160789489746</v>
+      </c>
+    </row>
+    <row r="1716" spans="1:5">
+      <c r="A1716" s="1" t="s">
+        <v>1718</v>
+      </c>
+      <c r="C1716">
+        <v>15.93735122680664</v>
+      </c>
+      <c r="D1716">
+        <v>7.135069370269775</v>
+      </c>
+      <c r="E1716">
+        <v>11.90674877166748</v>
+      </c>
+    </row>
+    <row r="1717" spans="1:5">
+      <c r="A1717" s="1" t="s">
+        <v>1719</v>
+      </c>
+      <c r="C1717">
+        <v>225.3208770751953</v>
+      </c>
+    </row>
+    <row r="1718" spans="1:5">
+      <c r="A1718" s="1" t="s">
+        <v>1720</v>
+      </c>
+      <c r="C1718">
+        <v>7.280855655670166</v>
+      </c>
+      <c r="D1718">
+        <v>8.013579368591309</v>
+      </c>
+      <c r="E1718">
+        <v>9.62098503112793</v>
+      </c>
+    </row>
+    <row r="1719" spans="1:5">
+      <c r="A1719" s="1" t="s">
+        <v>1721</v>
+      </c>
+      <c r="C1719">
+        <v>11.10195350646973</v>
+      </c>
+      <c r="D1719">
+        <v>13.19218063354492</v>
+      </c>
+      <c r="E1719">
+        <v>16.57643127441406</v>
+      </c>
+    </row>
+    <row r="1720" spans="1:5">
+      <c r="A1720" s="1" t="s">
+        <v>1722</v>
+      </c>
+      <c r="C1720">
+        <v>5.762858867645264</v>
+      </c>
+      <c r="D1720">
+        <v>5.531624794006348</v>
+      </c>
+      <c r="E1720">
+        <v>7.983906745910645</v>
+      </c>
+    </row>
+    <row r="1721" spans="1:5">
+      <c r="A1721" s="1" t="s">
+        <v>1723</v>
+      </c>
+      <c r="C1721">
+        <v>13.01638031005859</v>
+      </c>
+      <c r="D1721">
+        <v>5.855890274047852</v>
+      </c>
+      <c r="E1721">
+        <v>11.73416233062744</v>
+      </c>
+    </row>
+    <row r="1722" spans="1:5">
+      <c r="A1722" s="1" t="s">
+        <v>1724</v>
+      </c>
+      <c r="C1722">
+        <v>8.336034774780273</v>
+      </c>
+      <c r="D1722">
+        <v>1029.931396484375</v>
+      </c>
+      <c r="E1722">
+        <v>1307.811645507812</v>
+      </c>
+    </row>
+    <row r="1723" spans="1:5">
+      <c r="A1723" s="1" t="s">
+        <v>1725</v>
+      </c>
+      <c r="C1723">
+        <v>3.25888204574585</v>
+      </c>
+      <c r="D1723">
+        <v>1.20785653591156</v>
+      </c>
+      <c r="E1723">
+        <v>2.156176805496216</v>
+      </c>
+    </row>
+    <row r="1724" spans="1:5">
+      <c r="A1724" s="1" t="s">
+        <v>1726</v>
+      </c>
+      <c r="C1724">
+        <v>30.15250587463379</v>
+      </c>
+      <c r="D1724">
+        <v>8.714869499206543</v>
+      </c>
+      <c r="E1724">
+        <v>20.47146034240723</v>
+      </c>
+    </row>
+    <row r="1725" spans="1:5">
+      <c r="A1725" s="1" t="s">
+        <v>1727</v>
+      </c>
+      <c r="C1725">
+        <v>27.61543655395508</v>
+      </c>
+      <c r="D1725">
+        <v>15.06936740875244</v>
+      </c>
+      <c r="E1725">
+        <v>37.01187133789062</v>
+      </c>
+    </row>
+    <row r="1726" spans="1:5">
+      <c r="A1726" s="1" t="s">
+        <v>1728</v>
+      </c>
+      <c r="C1726">
+        <v>16.88742065429688</v>
+      </c>
+      <c r="D1726">
+        <v>4.663036823272705</v>
+      </c>
+      <c r="E1726">
+        <v>11.41146373748779</v>
+      </c>
+    </row>
+    <row r="1727" spans="1:5">
+      <c r="A1727" s="1" t="s">
+        <v>1729</v>
+      </c>
+      <c r="C1727">
+        <v>0.8824127912521362</v>
+      </c>
+      <c r="D1727">
+        <v>2.5003662109375</v>
+      </c>
+      <c r="E1727">
+        <v>9.929659843444824</v>
+      </c>
+    </row>
+    <row r="1728" spans="1:5">
+      <c r="A1728" s="1" t="s">
+        <v>1730</v>
+      </c>
+      <c r="C1728">
+        <v>0.8985630869865417</v>
+      </c>
+      <c r="D1728">
+        <v>0.5951439738273621</v>
+      </c>
+      <c r="E1728">
+        <v>1.160842537879944</v>
+      </c>
+    </row>
+    <row r="1729" spans="1:5">
+      <c r="A1729" s="1" t="s">
+        <v>1731</v>
+      </c>
+      <c r="C1729">
+        <v>0.8642293214797974</v>
+      </c>
+      <c r="D1729">
+        <v>0.7251436114311218</v>
+      </c>
+      <c r="E1729">
+        <v>1.49602222442627</v>
+      </c>
+    </row>
+    <row r="1730" spans="1:5">
+      <c r="A1730" s="1" t="s">
+        <v>1732</v>
+      </c>
+      <c r="C1730">
+        <v>2.918008089065552</v>
+      </c>
+      <c r="D1730">
+        <v>0.4766729772090912</v>
+      </c>
+      <c r="E1730">
+        <v>6.445268154144287</v>
+      </c>
+    </row>
+    <row r="1731" spans="1:5">
+      <c r="A1731" s="1" t="s">
+        <v>1733</v>
+      </c>
+      <c r="C1731">
+        <v>0</v>
+      </c>
+      <c r="D1731">
+        <v>0</v>
+      </c>
+      <c r="E1731">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1732" spans="1:5">
+      <c r="A1732" s="1" t="s">
+        <v>1734</v>
+      </c>
+      <c r="C1732">
+        <v>6.691469192504883</v>
+      </c>
+      <c r="D1732">
+        <v>3.689842224121094</v>
+      </c>
+      <c r="E1732">
+        <v>6.629975318908691</v>
+      </c>
+    </row>
+    <row r="1733" spans="1:5">
+      <c r="A1733" s="1" t="s">
+        <v>1735</v>
+      </c>
+      <c r="C1733">
+        <v>4.017955303192139</v>
+      </c>
+      <c r="D1733">
+        <v>2.767811059951782</v>
+      </c>
+      <c r="E1733">
+        <v>5.852612018585205</v>
+      </c>
+    </row>
+    <row r="1734" spans="1:5">
+      <c r="A1734" s="1" t="s">
+        <v>1736</v>
+      </c>
+      <c r="C1734">
+        <v>5.918907165527344</v>
+      </c>
+      <c r="D1734">
+        <v>4.936748504638672</v>
+      </c>
+      <c r="E1734">
+        <v>7.342791557312012</v>
+      </c>
+    </row>
+    <row r="1735" spans="1:5">
+      <c r="A1735" s="1" t="s">
+        <v>1737</v>
+      </c>
+      <c r="C1735">
+        <v>28.7080020904541</v>
+      </c>
+      <c r="D1735">
+        <v>60.62048721313477</v>
+      </c>
+      <c r="E1735">
+        <v>46.50505065917969</v>
+      </c>
+    </row>
+    <row r="1736" spans="1:5">
+      <c r="A1736" s="1" t="s">
+        <v>1738</v>
+      </c>
+      <c r="C1736">
+        <v>16.10281181335449</v>
+      </c>
+      <c r="D1736">
+        <v>18.79543685913086</v>
+      </c>
+      <c r="E1736">
+        <v>36.87088775634766</v>
+      </c>
+    </row>
+    <row r="1737" spans="1:5">
+      <c r="A1737" s="1" t="s">
+        <v>1739</v>
+      </c>
+      <c r="C1737">
+        <v>16.87394332885742</v>
+      </c>
+      <c r="D1737">
+        <v>12.83489322662354</v>
+      </c>
+      <c r="E1737">
+        <v>19.94032096862793</v>
+      </c>
+    </row>
+    <row r="1738" spans="1:5">
+      <c r="A1738" s="1" t="s">
+        <v>1740</v>
+      </c>
+      <c r="C1738">
+        <v>24.0294361114502</v>
+      </c>
+      <c r="D1738">
+        <v>11.82046794891357</v>
+      </c>
+      <c r="E1738">
+        <v>25.92525100708008</v>
+      </c>
+    </row>
+    <row r="1739" spans="1:5">
+      <c r="A1739" s="1" t="s">
+        <v>1741</v>
+      </c>
+      <c r="C1739">
+        <v>2.721760749816895</v>
+      </c>
+      <c r="D1739">
+        <v>2.882450819015503</v>
+      </c>
+      <c r="E1739">
+        <v>4.083144664764404</v>
+      </c>
+    </row>
+    <row r="1740" spans="1:5">
+      <c r="A1740" s="1" t="s">
+        <v>1742</v>
+      </c>
+      <c r="C1740">
+        <v>7.339457988739014</v>
+      </c>
+      <c r="D1740">
+        <v>9.148576736450195</v>
+      </c>
+      <c r="E1740">
+        <v>10.64120006561279</v>
+      </c>
+    </row>
+    <row r="1741" spans="1:5">
+      <c r="A1741" s="1" t="s">
+        <v>1743</v>
+      </c>
+      <c r="C1741">
+        <v>11.36451816558838</v>
+      </c>
+      <c r="D1741">
+        <v>8.894525527954102</v>
+      </c>
+      <c r="E1741">
+        <v>11.86120414733887</v>
+      </c>
+    </row>
+    <row r="1742" spans="1:5">
+      <c r="A1742" s="1" t="s">
+        <v>1744</v>
+      </c>
+      <c r="C1742">
+        <v>1.361244440078735</v>
+      </c>
+      <c r="D1742">
+        <v>0</v>
+      </c>
+      <c r="E1742">
+        <v>0.9940803647041321</v>
+      </c>
+    </row>
+    <row r="1743" spans="1:5">
+      <c r="A1743" s="1" t="s">
+        <v>1745</v>
+      </c>
+      <c r="C1743">
+        <v>13.6785717010498</v>
+      </c>
+      <c r="D1743">
+        <v>21.93404579162598</v>
+      </c>
+      <c r="E1743">
+        <v>23.72637748718262</v>
+      </c>
+    </row>
+    <row r="1744" spans="1:5">
+      <c r="A1744" s="1" t="s">
+        <v>1746</v>
+      </c>
+      <c r="C1744">
+        <v>1.835204839706421</v>
+      </c>
+      <c r="D1744">
+        <v>1.323745369911194</v>
+      </c>
+      <c r="E1744">
+        <v>1.634479880332947</v>
+      </c>
+    </row>
+    <row r="1745" spans="1:5">
+      <c r="A1745" s="1" t="s">
+        <v>1747</v>
+      </c>
+      <c r="C1745">
+        <v>118.520881652832</v>
+      </c>
+      <c r="D1745">
+        <v>80.93462371826172</v>
+      </c>
+      <c r="E1745">
+        <v>182.2588043212891</v>
+      </c>
+    </row>
+    <row r="1746" spans="1:5">
+      <c r="A1746" s="1" t="s">
+        <v>1748</v>
+      </c>
+      <c r="C1746">
+        <v>3.38923978805542</v>
+      </c>
+      <c r="D1746">
+        <v>3.809303760528564</v>
+      </c>
+      <c r="E1746">
+        <v>5.064090728759766</v>
+      </c>
+    </row>
+    <row r="1747" spans="1:5">
+      <c r="A1747" s="1" t="s">
+        <v>1749</v>
+      </c>
+      <c r="C1747">
+        <v>17.75777626037598</v>
+      </c>
+      <c r="D1747">
+        <v>11.86329746246338</v>
+      </c>
+      <c r="E1747">
+        <v>17.54285621643066</v>
+      </c>
+    </row>
+    <row r="1748" spans="1:5">
+      <c r="A1748" s="1" t="s">
+        <v>1750</v>
+      </c>
+      <c r="C1748">
+        <v>27.00082969665527</v>
+      </c>
+      <c r="D1748">
+        <v>50.82209396362305</v>
+      </c>
+      <c r="E1748">
+        <v>44.83523941040039</v>
+      </c>
+    </row>
+    <row r="1749" spans="1:5">
+      <c r="A1749" s="1" t="s">
+        <v>1751</v>
+      </c>
+      <c r="C1749">
+        <v>0.1268114596605301</v>
+      </c>
+      <c r="D1749">
+        <v>0.0955243855714798</v>
+      </c>
+      <c r="E1749">
+        <v>0.1433282345533371</v>
+      </c>
+    </row>
+    <row r="1750" spans="1:5">
+      <c r="A1750" s="1" t="s">
+        <v>1752</v>
+      </c>
+      <c r="C1750">
+        <v>1.450285911560059</v>
+      </c>
+      <c r="D1750">
+        <v>0.9450945854187012</v>
+      </c>
+      <c r="E1750">
+        <v>2.400997877120972</v>
+      </c>
+    </row>
+    <row r="1751" spans="1:5">
+      <c r="A1751" s="1" t="s">
+        <v>1753</v>
+      </c>
+      <c r="C1751">
+        <v>8.238221168518066</v>
+      </c>
+      <c r="D1751">
+        <v>11.81199741363525</v>
+      </c>
+      <c r="E1751">
+        <v>13.37504959106445</v>
+      </c>
+    </row>
+    <row r="1752" spans="1:5">
+      <c r="A1752" s="1" t="s">
+        <v>1754</v>
+      </c>
+      <c r="C1752">
+        <v>1.275501251220703</v>
+      </c>
+      <c r="D1752">
+        <v>1.221671581268311</v>
+      </c>
+      <c r="E1752">
+        <v>2.620865821838379</v>
+      </c>
+    </row>
+    <row r="1753" spans="1:5">
+      <c r="A1753" s="1" t="s">
+        <v>1755</v>
+      </c>
+      <c r="C1753">
+        <v>13.63334655761719</v>
+      </c>
+      <c r="D1753">
+        <v>3.260971069335938</v>
+      </c>
+      <c r="E1753">
+        <v>7.764853000640869</v>
+      </c>
+    </row>
+    <row r="1754" spans="1:5">
+      <c r="A1754" s="1" t="s">
+        <v>1756</v>
+      </c>
+      <c r="C1754">
+        <v>13.6763219833374</v>
+      </c>
+      <c r="D1754">
+        <v>19.00408172607422</v>
+      </c>
+      <c r="E1754">
+        <v>20.40112686157227</v>
+      </c>
+    </row>
+    <row r="1755" spans="1:5">
+      <c r="A1755" s="1" t="s">
+        <v>1757</v>
+      </c>
+      <c r="C1755">
+        <v>9.168693542480469</v>
+      </c>
+      <c r="D1755">
+        <v>9.718683242797852</v>
+      </c>
+      <c r="E1755">
+        <v>12.23933029174805</v>
+      </c>
+    </row>
+    <row r="1756" spans="1:5">
+      <c r="A1756" s="1" t="s">
+        <v>1758</v>
+      </c>
+      <c r="C1756">
+        <v>9.287335395812988</v>
+      </c>
+      <c r="D1756">
+        <v>9.416241645812988</v>
+      </c>
+      <c r="E1756">
+        <v>11.25144100189209</v>
+      </c>
+    </row>
+    <row r="1757" spans="1:5">
+      <c r="A1757" s="1" t="s">
+        <v>1759</v>
+      </c>
+      <c r="C1757">
+        <v>1.58521044254303</v>
+      </c>
+      <c r="D1757">
+        <v>1.16988205909729</v>
+      </c>
+      <c r="E1757">
+        <v>2.43241548538208</v>
+      </c>
+    </row>
+    <row r="1758" spans="1:5">
+      <c r="A1758" s="1" t="s">
+        <v>1760</v>
+      </c>
+      <c r="C1758">
+        <v>1.313085317611694</v>
+      </c>
+      <c r="D1758">
+        <v>3.451415777206421</v>
+      </c>
+      <c r="E1758">
+        <v>3.366630792617798</v>
+      </c>
+    </row>
+    <row r="1759" spans="1:5">
+      <c r="A1759" s="1" t="s">
+        <v>1761</v>
+      </c>
+      <c r="C1759">
+        <v>0</v>
+      </c>
+      <c r="D1759">
+        <v>0</v>
+      </c>
+      <c r="E1759">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1760" spans="1:5">
+      <c r="A1760" s="1" t="s">
+        <v>1762</v>
+      </c>
+      <c r="C1760">
+        <v>13.00649261474609</v>
+      </c>
+      <c r="D1760">
+        <v>14.98176765441895</v>
+      </c>
+      <c r="E1760">
+        <v>19.45181083679199</v>
+      </c>
+    </row>
+    <row r="1761" spans="1:5">
+      <c r="A1761" s="1" t="s">
+        <v>1763</v>
+      </c>
+      <c r="C1761">
+        <v>5.294060707092285</v>
+      </c>
+      <c r="D1761">
+        <v>6.964319229125977</v>
+      </c>
+      <c r="E1761">
+        <v>8.865100860595703</v>
+      </c>
+    </row>
+    <row r="1762" spans="1:5">
+      <c r="A1762" s="1" t="s">
+        <v>1764</v>
+      </c>
+      <c r="C1762">
+        <v>5.26345682144165</v>
+      </c>
+      <c r="D1762">
+        <v>4.818901062011719</v>
+      </c>
+      <c r="E1762">
+        <v>6.360226154327393</v>
+      </c>
+    </row>
+    <row r="1763" spans="1:5">
+      <c r="A1763" s="1" t="s">
+        <v>1765</v>
+      </c>
+      <c r="C1763">
+        <v>8.325241088867188</v>
+      </c>
+      <c r="D1763">
+        <v>12.67552471160889</v>
+      </c>
+      <c r="E1763">
+        <v>15.34538745880127</v>
+      </c>
+    </row>
+    <row r="1764" spans="1:5">
+      <c r="A1764" s="1" t="s">
+        <v>1766</v>
+      </c>
+      <c r="C1764">
+        <v>10.51992321014404</v>
+      </c>
+      <c r="D1764">
+        <v>14.17668533325195</v>
+      </c>
+      <c r="E1764">
+        <v>16.6205883026123</v>
+      </c>
+    </row>
+    <row r="1765" spans="1:5">
+      <c r="A1765" s="1" t="s">
+        <v>1767</v>
+      </c>
+      <c r="C1765">
+        <v>1.077194333076477</v>
+      </c>
+      <c r="D1765">
+        <v>0.7209699153900146</v>
+      </c>
+      <c r="E1765">
+        <v>1.284729957580566</v>
+      </c>
+    </row>
+    <row r="1766" spans="1:5">
+      <c r="A1766" s="1" t="s">
+        <v>1768</v>
+      </c>
+      <c r="C1766">
+        <v>7.037332534790039</v>
+      </c>
+      <c r="D1766">
+        <v>8.7470703125</v>
+      </c>
+      <c r="E1766">
+        <v>11.3609561920166</v>
+      </c>
+    </row>
+    <row r="1767" spans="1:5">
+      <c r="A1767" s="1" t="s">
+        <v>1769</v>
+      </c>
+      <c r="C1767">
+        <v>13.65457916259766</v>
+      </c>
+      <c r="D1767">
+        <v>5.162581920623779</v>
+      </c>
+      <c r="E1767">
+        <v>10.25216197967529</v>
+      </c>
+    </row>
+    <row r="1768" spans="1:5">
+      <c r="A1768" s="1" t="s">
+        <v>1770</v>
+      </c>
+      <c r="C1768">
+        <v>2.096848487854004</v>
+      </c>
+      <c r="D1768">
+        <v>1.616759896278381</v>
+      </c>
+      <c r="E1768">
+        <v>2.911685943603516</v>
+      </c>
+    </row>
+    <row r="1769" spans="1:5">
+      <c r="A1769" s="1" t="s">
+        <v>1771</v>
+      </c>
+      <c r="C1769">
+        <v>23.19849967956543</v>
+      </c>
+      <c r="D1769">
+        <v>12.37741851806641</v>
+      </c>
+      <c r="E1769">
+        <v>23.20733451843262</v>
+      </c>
+    </row>
+    <row r="1770" spans="1:5">
+      <c r="A1770" s="1" t="s">
+        <v>1772</v>
+      </c>
+      <c r="C1770" t="s">
+        <v>1850</v>
+      </c>
+      <c r="E1770" t="s">
+        <v>1850</v>
+      </c>
+    </row>
+    <row r="1771" spans="1:5">
+      <c r="A1771" s="1" t="s">
+        <v>1773</v>
+      </c>
+      <c r="C1771">
+        <v>11.26494789123535</v>
+      </c>
+      <c r="D1771">
+        <v>12.90354442596436</v>
+      </c>
+      <c r="E1771">
+        <v>14.65089511871338</v>
+      </c>
+    </row>
+    <row r="1772" spans="1:5">
+      <c r="A1772" s="1" t="s">
+        <v>1774</v>
+      </c>
+      <c r="C1772">
+        <v>4.486217975616455</v>
+      </c>
+      <c r="D1772">
+        <v>4.022979259490967</v>
+      </c>
+      <c r="E1772">
+        <v>7.49942684173584</v>
+      </c>
+    </row>
+    <row r="1773" spans="1:5">
+      <c r="A1773" s="1" t="s">
+        <v>1775</v>
+      </c>
+      <c r="C1773">
+        <v>36.04162216186523</v>
+      </c>
+    </row>
+    <row r="1774" spans="1:5">
+      <c r="A1774" s="1" t="s">
+        <v>1776</v>
+      </c>
+      <c r="C1774">
+        <v>12.11575317382812</v>
+      </c>
+      <c r="D1774">
+        <v>15.88742065429688</v>
+      </c>
+      <c r="E1774">
+        <v>17.31737327575684</v>
+      </c>
+    </row>
+    <row r="1775" spans="1:5">
+      <c r="A1775" s="1" t="s">
+        <v>1777</v>
+      </c>
+      <c r="C1775">
+        <v>8.145047187805176</v>
+      </c>
+      <c r="D1775">
+        <v>15.19632720947266</v>
+      </c>
+      <c r="E1775">
+        <v>18.25994682312012</v>
+      </c>
+    </row>
+    <row r="1776" spans="1:5">
+      <c r="A1776" s="1" t="s">
+        <v>1778</v>
+      </c>
+      <c r="C1776">
+        <v>5.150447845458984</v>
+      </c>
+      <c r="D1776">
+        <v>7.794849395751953</v>
+      </c>
+      <c r="E1776">
+        <v>9.373167037963867</v>
+      </c>
+    </row>
+    <row r="1777" spans="1:5">
+      <c r="A1777" s="1" t="s">
+        <v>1779</v>
+      </c>
+      <c r="C1777">
+        <v>20.75418281555176</v>
+      </c>
+      <c r="D1777">
+        <v>12.88272476196289</v>
+      </c>
+      <c r="E1777">
+        <v>20.47726821899414</v>
+      </c>
+    </row>
+    <row r="1778" spans="1:5">
+      <c r="A1778" s="1" t="s">
+        <v>1780</v>
+      </c>
+      <c r="C1778">
+        <v>0.7862104773521423</v>
+      </c>
+      <c r="D1778">
+        <v>224.8590393066406</v>
+      </c>
+      <c r="E1778">
+        <v>234.6429748535156</v>
+      </c>
+    </row>
+    <row r="1779" spans="1:5">
+      <c r="A1779" s="1" t="s">
+        <v>1781</v>
+      </c>
+      <c r="C1779">
+        <v>0.8644489049911499</v>
+      </c>
+      <c r="D1779">
+        <v>0.6347739696502686</v>
+      </c>
+      <c r="E1779">
+        <v>1.311270475387573</v>
+      </c>
+    </row>
+    <row r="1780" spans="1:5">
+      <c r="A1780" s="1" t="s">
+        <v>1782</v>
+      </c>
+      <c r="C1780">
+        <v>26.20874786376953</v>
+      </c>
+      <c r="D1780">
+        <v>11.23091888427734</v>
+      </c>
+      <c r="E1780">
+        <v>19.3926830291748</v>
+      </c>
+    </row>
+    <row r="1781" spans="1:5">
+      <c r="A1781" s="1" t="s">
+        <v>1783</v>
+      </c>
+      <c r="C1781">
+        <v>21.19446182250977</v>
+      </c>
+      <c r="D1781">
+        <v>25.24505043029785</v>
+      </c>
+      <c r="E1781">
+        <v>38.52029800415039</v>
+      </c>
+    </row>
+    <row r="1782" spans="1:5">
+      <c r="A1782" s="1" t="s">
+        <v>1784</v>
+      </c>
+      <c r="C1782">
+        <v>21.53973388671875</v>
+      </c>
+      <c r="D1782">
+        <v>10.14539813995361</v>
+      </c>
+      <c r="E1782">
+        <v>17.07102584838867</v>
+      </c>
+    </row>
+    <row r="1783" spans="1:5">
+      <c r="A1783" s="1" t="s">
+        <v>1785</v>
+      </c>
+      <c r="C1783">
+        <v>6.790185451507568</v>
+      </c>
+      <c r="D1783">
+        <v>11.82536602020264</v>
+      </c>
+      <c r="E1783">
+        <v>10.5778923034668</v>
+      </c>
+    </row>
+    <row r="1784" spans="1:5">
+      <c r="A1784" s="1" t="s">
+        <v>1786</v>
+      </c>
+      <c r="C1784">
+        <v>0</v>
+      </c>
+      <c r="D1784">
+        <v>0.07275550067424774</v>
+      </c>
+      <c r="E1784">
+        <v>0.5250588059425354</v>
+      </c>
+    </row>
+    <row r="1785" spans="1:5">
+      <c r="A1785" s="1" t="s">
+        <v>1787</v>
+      </c>
+      <c r="C1785">
+        <v>0.03241138532757759</v>
+      </c>
+      <c r="D1785">
+        <v>0.1785308420658112</v>
+      </c>
+      <c r="E1785">
+        <v>0.6625459790229797</v>
+      </c>
+    </row>
+    <row r="1786" spans="1:5">
+      <c r="A1786" s="1" t="s">
+        <v>1788</v>
+      </c>
+      <c r="C1786">
+        <v>1.070126056671143</v>
+      </c>
+      <c r="D1786">
+        <v>0.4657852947711945</v>
+      </c>
+      <c r="E1786">
+        <v>3.269106388092041</v>
+      </c>
+    </row>
+    <row r="1787" spans="1:5">
+      <c r="A1787" s="1" t="s">
+        <v>1789</v>
+      </c>
+      <c r="C1787">
+        <v>0</v>
+      </c>
+      <c r="D1787">
+        <v>0</v>
+      </c>
+      <c r="E1787">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1788" spans="1:5">
+      <c r="A1788" s="1" t="s">
+        <v>1790</v>
+      </c>
+      <c r="C1788">
+        <v>2.565798759460449</v>
+      </c>
+      <c r="D1788">
+        <v>2.516010999679565</v>
+      </c>
+      <c r="E1788">
+        <v>3.559836149215698</v>
+      </c>
+    </row>
+    <row r="1789" spans="1:5">
+      <c r="A1789" s="1" t="s">
+        <v>1791</v>
+      </c>
+      <c r="C1789">
+        <v>0</v>
+      </c>
+      <c r="D1789">
+        <v>0.1614776998758316</v>
+      </c>
+      <c r="E1789">
+        <v>0.9587888717651367</v>
+      </c>
+    </row>
+    <row r="1790" spans="1:5">
+      <c r="A1790" s="1" t="s">
+        <v>1792</v>
+      </c>
+      <c r="C1790">
+        <v>2.245852947235107</v>
+      </c>
+      <c r="D1790">
+        <v>3.181836128234863</v>
+      </c>
+      <c r="E1790">
+        <v>3.852548837661743</v>
+      </c>
+    </row>
+    <row r="1791" spans="1:5">
+      <c r="A1791" s="1" t="s">
+        <v>1793</v>
+      </c>
+      <c r="C1791">
+        <v>8.006160736083984</v>
+      </c>
+      <c r="D1791">
+        <v>24.26560211181641</v>
+      </c>
+      <c r="E1791">
+        <v>15.89193153381348</v>
+      </c>
+    </row>
+    <row r="1792" spans="1:5">
+      <c r="A1792" s="1" t="s">
+        <v>1794</v>
+      </c>
+      <c r="C1792">
+        <v>5.542262077331543</v>
+      </c>
+      <c r="D1792">
+        <v>10.68194770812988</v>
+      </c>
+      <c r="E1792">
+        <v>14.47788619995117</v>
+      </c>
+    </row>
+    <row r="1793" spans="1:5">
+      <c r="A1793" s="1" t="s">
+        <v>1795</v>
+      </c>
+      <c r="C1793">
+        <v>6.609262943267822</v>
+      </c>
+      <c r="D1793">
+        <v>7.829609870910645</v>
+      </c>
+      <c r="E1793">
+        <v>9.878416061401367</v>
+      </c>
+    </row>
+    <row r="1794" spans="1:5">
+      <c r="A1794" s="1" t="s">
+        <v>1796</v>
+      </c>
+      <c r="C1794">
+        <v>10.88199520111084</v>
+      </c>
+      <c r="D1794">
+        <v>7.387710094451904</v>
+      </c>
+      <c r="E1794">
+        <v>12.3230619430542</v>
+      </c>
+    </row>
+    <row r="1795" spans="1:5">
+      <c r="A1795" s="1" t="s">
+        <v>1797</v>
+      </c>
+      <c r="C1795">
+        <v>1.177803754806519</v>
+      </c>
+      <c r="D1795">
+        <v>2.518086671829224</v>
+      </c>
+      <c r="E1795">
+        <v>3.68719482421875</v>
+      </c>
+    </row>
+    <row r="1796" spans="1:5">
+      <c r="A1796" s="1" t="s">
+        <v>1798</v>
+      </c>
+      <c r="C1796">
+        <v>4.1589035987854</v>
+      </c>
+      <c r="D1796">
+        <v>7.43221378326416</v>
+      </c>
+      <c r="E1796">
+        <v>9.63896656036377</v>
+      </c>
+    </row>
+    <row r="1797" spans="1:5">
+      <c r="A1797" s="1" t="s">
+        <v>1799</v>
+      </c>
+      <c r="C1797">
+        <v>4.161157131195068</v>
+      </c>
+      <c r="D1797">
+        <v>8.019498825073242</v>
+      </c>
+      <c r="E1797">
+        <v>11.21707725524902</v>
+      </c>
+    </row>
+    <row r="1798" spans="1:5">
+      <c r="A1798" s="1" t="s">
+        <v>1800</v>
+      </c>
+      <c r="C1798">
+        <v>0.4817444682121277</v>
+      </c>
+      <c r="D1798">
+        <v>0</v>
+      </c>
+      <c r="E1798">
+        <v>0.5024773478507996</v>
+      </c>
+    </row>
+    <row r="1799" spans="1:5">
+      <c r="A1799" s="1" t="s">
+        <v>1801</v>
+      </c>
+      <c r="C1799">
+        <v>13.52527809143066</v>
+      </c>
+      <c r="D1799">
+        <v>22.02934074401855</v>
+      </c>
+      <c r="E1799">
+        <v>25.81283187866211</v>
+      </c>
+    </row>
+    <row r="1800" spans="1:5">
+      <c r="A1800" s="1" t="s">
+        <v>1802</v>
+      </c>
+      <c r="C1800">
+        <v>0.6739151477813721</v>
+      </c>
+      <c r="D1800">
+        <v>1.534728288650513</v>
+      </c>
+      <c r="E1800">
+        <v>1.926530480384827</v>
+      </c>
+    </row>
+    <row r="1801" spans="1:5">
+      <c r="A1801" s="1" t="s">
+        <v>1803</v>
+      </c>
+      <c r="C1801">
+        <v>19.48347091674805</v>
+      </c>
+      <c r="D1801">
+        <v>29.03188896179199</v>
+      </c>
+      <c r="E1801">
+        <v>31.07629776000977</v>
+      </c>
+    </row>
+    <row r="1802" spans="1:5">
+      <c r="A1802" s="1" t="s">
+        <v>1804</v>
+      </c>
+      <c r="C1802">
+        <v>1.528901338577271</v>
+      </c>
+      <c r="D1802">
+        <v>2.463681936264038</v>
+      </c>
+      <c r="E1802">
+        <v>2.979595184326172</v>
+      </c>
+    </row>
+    <row r="1803" spans="1:5">
+      <c r="A1803" s="1" t="s">
+        <v>1805</v>
+      </c>
+      <c r="C1803">
+        <v>8.749588012695312</v>
+      </c>
+      <c r="D1803">
+        <v>8.187165260314941</v>
+      </c>
+      <c r="E1803">
+        <v>10.83564567565918</v>
+      </c>
+    </row>
+    <row r="1804" spans="1:5">
+      <c r="A1804" s="1" t="s">
+        <v>1806</v>
+      </c>
+      <c r="C1804">
+        <v>8.81158447265625</v>
+      </c>
+      <c r="D1804">
+        <v>22.7807788848877</v>
+      </c>
+      <c r="E1804">
+        <v>16.90532302856445</v>
+      </c>
+    </row>
+    <row r="1805" spans="1:5">
+      <c r="A1805" s="1" t="s">
+        <v>1807</v>
+      </c>
+      <c r="C1805">
+        <v>0.08189591765403748</v>
+      </c>
+      <c r="D1805">
+        <v>0.05897057056427002</v>
+      </c>
+      <c r="E1805">
+        <v>0.0870903953909874</v>
+      </c>
+    </row>
+    <row r="1806" spans="1:5">
+      <c r="A1806" s="1" t="s">
+        <v>1808</v>
+      </c>
+      <c r="C1806">
+        <v>0</v>
+      </c>
+      <c r="D1806">
+        <v>0.08999065309762955</v>
+      </c>
+      <c r="E1806">
+        <v>0.6320319771766663</v>
+      </c>
+    </row>
+    <row r="1807" spans="1:5">
+      <c r="A1807" s="1" t="s">
+        <v>1809</v>
+      </c>
+      <c r="C1807">
+        <v>3.797988891601562</v>
+      </c>
+      <c r="D1807">
+        <v>6.347126483917236</v>
+      </c>
+      <c r="E1807">
+        <v>8.179964065551758</v>
+      </c>
+    </row>
+    <row r="1808" spans="1:5">
+      <c r="A1808" s="1" t="s">
+        <v>1810</v>
+      </c>
+      <c r="C1808">
+        <v>0</v>
+      </c>
+      <c r="D1808">
+        <v>0.1029649749398232</v>
+      </c>
+      <c r="E1808">
+        <v>0.6577742099761963</v>
+      </c>
+    </row>
+    <row r="1809" spans="1:5">
+      <c r="A1809" s="1" t="s">
+        <v>1811</v>
+      </c>
+      <c r="C1809">
+        <v>4.370571136474609</v>
+      </c>
+      <c r="D1809">
+        <v>2.206554174423218</v>
+      </c>
+      <c r="E1809">
+        <v>3.956382513046265</v>
+      </c>
+    </row>
+    <row r="1810" spans="1:5">
+      <c r="A1810" s="1" t="s">
+        <v>1812</v>
+      </c>
+      <c r="C1810">
+        <v>8.373692512512207</v>
+      </c>
+      <c r="D1810">
+        <v>13.42401313781738</v>
+      </c>
+      <c r="E1810">
+        <v>16.43477630615234</v>
+      </c>
+    </row>
+    <row r="1811" spans="1:5">
+      <c r="A1811" s="1" t="s">
+        <v>1813</v>
+      </c>
+      <c r="C1811">
+        <v>3.818506002426147</v>
+      </c>
+      <c r="D1811">
+        <v>5.770203113555908</v>
+      </c>
+      <c r="E1811">
+        <v>6.87429141998291</v>
+      </c>
+    </row>
+    <row r="1812" spans="1:5">
+      <c r="A1812" s="1" t="s">
+        <v>1814</v>
+      </c>
+      <c r="C1812">
+        <v>3.776609420776367</v>
+      </c>
+      <c r="D1812">
+        <v>7.324535846710205</v>
+      </c>
+      <c r="E1812">
+        <v>9.888214111328125</v>
+      </c>
+    </row>
+    <row r="1813" spans="1:5">
+      <c r="A1813" s="1" t="s">
+        <v>1815</v>
+      </c>
+      <c r="C1813">
+        <v>0.02305141091346741</v>
+      </c>
+      <c r="D1813">
+        <v>0.1449735164642334</v>
+      </c>
+      <c r="E1813">
+        <v>0.6674965023994446</v>
+      </c>
+    </row>
+    <row r="1814" spans="1:5">
+      <c r="A1814" s="1" t="s">
+        <v>1816</v>
+      </c>
+      <c r="C1814">
+        <v>1.335697174072266</v>
+      </c>
+      <c r="D1814">
+        <v>2.81827974319458</v>
+      </c>
+      <c r="E1814">
+        <v>3.541366100311279</v>
+      </c>
+    </row>
+    <row r="1815" spans="1:5">
+      <c r="A1815" s="1" t="s">
+        <v>1817</v>
+      </c>
+      <c r="C1815">
+        <v>0</v>
+      </c>
+      <c r="D1815">
+        <v>0</v>
+      </c>
+      <c r="E1815">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1816" spans="1:5">
+      <c r="A1816" s="1" t="s">
+        <v>1818</v>
+      </c>
+      <c r="C1816">
+        <v>7.260571002960205</v>
+      </c>
+      <c r="D1816">
+        <v>9.585080146789551</v>
+      </c>
+      <c r="E1816">
+        <v>14.60299968719482</v>
+      </c>
+    </row>
+    <row r="1817" spans="1:5">
+      <c r="A1817" s="1" t="s">
+        <v>1819</v>
+      </c>
+      <c r="C1817">
+        <v>3.226261377334595</v>
+      </c>
+      <c r="D1817">
+        <v>5.08337926864624</v>
+      </c>
+      <c r="E1817">
+        <v>6.403004169464111</v>
+      </c>
+    </row>
+    <row r="1818" spans="1:5">
+      <c r="A1818" s="1" t="s">
+        <v>1820</v>
+      </c>
+      <c r="C1818">
+        <v>2.038934707641602</v>
+      </c>
+      <c r="D1818">
+        <v>4.51376485824585</v>
+      </c>
+      <c r="E1818">
+        <v>6.325920104980469</v>
+      </c>
+    </row>
+    <row r="1819" spans="1:5">
+      <c r="A1819" s="1" t="s">
+        <v>1821</v>
+      </c>
+      <c r="C1819">
+        <v>5.20449161529541</v>
+      </c>
+      <c r="D1819">
+        <v>8.906549453735352</v>
+      </c>
+      <c r="E1819">
+        <v>11.77964210510254</v>
+      </c>
+    </row>
+    <row r="1820" spans="1:5">
+      <c r="A1820" s="1" t="s">
+        <v>1822</v>
+      </c>
+      <c r="C1820">
+        <v>4.99324893951416</v>
+      </c>
+      <c r="D1820">
+        <v>8.69389533996582</v>
+      </c>
+      <c r="E1820">
+        <v>8.897510528564453</v>
+      </c>
+    </row>
+    <row r="1821" spans="1:5">
+      <c r="A1821" s="1" t="s">
+        <v>1823</v>
+      </c>
+      <c r="C1821">
+        <v>0</v>
+      </c>
+      <c r="D1821">
+        <v>0.04857146367430687</v>
+      </c>
+      <c r="E1821">
+        <v>0.3592060804367065</v>
+      </c>
+    </row>
+    <row r="1822" spans="1:5">
+      <c r="A1822" s="1" t="s">
+        <v>1824</v>
+      </c>
+      <c r="C1822">
+        <v>3.219017028808594</v>
+      </c>
+      <c r="D1822">
+        <v>6.023909568786621</v>
+      </c>
+      <c r="E1822">
+        <v>6.696412563323975</v>
+      </c>
+    </row>
+    <row r="1823" spans="1:5">
+      <c r="A1823" s="1" t="s">
+        <v>1825</v>
+      </c>
+      <c r="C1823">
+        <v>6.82002592086792</v>
+      </c>
+      <c r="D1823">
+        <v>3.44066309928894</v>
+      </c>
+      <c r="E1823">
+        <v>6.235110759735107</v>
+      </c>
+    </row>
+    <row r="1824" spans="1:5">
+      <c r="A1824" s="1" t="s">
+        <v>1826</v>
+      </c>
+      <c r="C1824">
+        <v>0</v>
+      </c>
+      <c r="D1824">
+        <v>0.1096699684858322</v>
+      </c>
+      <c r="E1824">
+        <v>0.6482245922088623</v>
+      </c>
+    </row>
+    <row r="1825" spans="1:5">
+      <c r="A1825" s="1" t="s">
+        <v>1827</v>
+      </c>
+      <c r="C1825">
+        <v>7.492904186248779</v>
+      </c>
+      <c r="D1825">
+        <v>7.322653293609619</v>
+      </c>
+      <c r="E1825">
+        <v>9.941239356994629</v>
+      </c>
+    </row>
+    <row r="1826" spans="1:5">
+      <c r="A1826" s="1" t="s">
+        <v>1828</v>
+      </c>
+      <c r="C1826">
+        <v>97.80448150634766</v>
+      </c>
+      <c r="E1826">
+        <v>130.9531555175781</v>
+      </c>
+    </row>
+    <row r="1827" spans="1:5">
+      <c r="A1827" s="1" t="s">
+        <v>1829</v>
+      </c>
+      <c r="C1827">
+        <v>5.522768020629883</v>
+      </c>
+      <c r="D1827">
+        <v>9.789958953857422</v>
+      </c>
+      <c r="E1827">
+        <v>12.5013952255249</v>
+      </c>
+    </row>
+    <row r="1828" spans="1:5">
+      <c r="A1828" s="1" t="s">
+        <v>1830</v>
+      </c>
+      <c r="C1828">
+        <v>0.03171971812844276</v>
+      </c>
+      <c r="D1828">
+        <v>0.3769749999046326</v>
+      </c>
+      <c r="E1828">
+        <v>1.666214466094971</v>
+      </c>
+    </row>
+    <row r="1829" spans="1:5">
+      <c r="A1829" s="1" t="s">
+        <v>1831</v>
+      </c>
+      <c r="C1829">
+        <v>10.77415943145752</v>
+      </c>
+    </row>
+    <row r="1830" spans="1:5">
+      <c r="A1830" s="1" t="s">
+        <v>1832</v>
+      </c>
+      <c r="C1830">
+        <v>8.154433250427246</v>
+      </c>
+      <c r="D1830">
+        <v>13.67916965484619</v>
+      </c>
+      <c r="E1830">
+        <v>16.47416877746582</v>
+      </c>
+    </row>
+    <row r="1831" spans="1:5">
+      <c r="A1831" s="1" t="s">
+        <v>1833</v>
+      </c>
+      <c r="C1831">
+        <v>4.905763626098633</v>
+      </c>
+      <c r="D1831">
+        <v>7.806684017181396</v>
+      </c>
+      <c r="E1831">
+        <v>10.56032943725586</v>
+      </c>
+    </row>
+    <row r="1832" spans="1:5">
+      <c r="A1832" s="1" t="s">
+        <v>1834</v>
+      </c>
+      <c r="C1832">
+        <v>3.381463527679443</v>
+      </c>
+      <c r="D1832">
+        <v>6.258751392364502</v>
+      </c>
+      <c r="E1832">
+        <v>7.945755004882812</v>
+      </c>
+    </row>
+    <row r="1833" spans="1:5">
+      <c r="A1833" s="1" t="s">
+        <v>1835</v>
+      </c>
+      <c r="C1833">
+        <v>8.433628082275391</v>
+      </c>
+      <c r="D1833">
+        <v>7.893136024475098</v>
+      </c>
+      <c r="E1833">
+        <v>10.43883991241455</v>
+      </c>
+    </row>
+    <row r="1834" spans="1:5">
+      <c r="A1834" s="1" t="s">
+        <v>1836</v>
+      </c>
+      <c r="C1834">
+        <v>1.425748467445374</v>
+      </c>
+      <c r="D1834">
+        <v>56.74431228637695</v>
+      </c>
+      <c r="E1834">
+        <v>63.71674346923828</v>
+      </c>
+    </row>
+    <row r="1835" spans="1:5">
+      <c r="A1835" s="1" t="s">
+        <v>1837</v>
+      </c>
+      <c r="C1835">
+        <v>0.00303438282571733</v>
+      </c>
+      <c r="D1835">
+        <v>0.0362035259604454</v>
+      </c>
+      <c r="E1835">
+        <v>0.1985399574041367</v>
+      </c>
+    </row>
+    <row r="1836" spans="1:5">
+      <c r="A1836" s="1" t="s">
+        <v>1838</v>
+      </c>
+      <c r="C1836">
+        <v>12.97202396392822</v>
+      </c>
+      <c r="D1836">
+        <v>7.139035224914551</v>
+      </c>
+      <c r="E1836">
+        <v>11.59365749359131</v>
+      </c>
+    </row>
+    <row r="1837" spans="1:5">
+      <c r="A1837" s="1" t="s">
+        <v>1839</v>
+      </c>
+      <c r="C1837">
+        <v>7.725818157196045</v>
+      </c>
+      <c r="D1837">
+        <v>13.35719203948975</v>
+      </c>
+      <c r="E1837">
+        <v>14.77319717407227</v>
+      </c>
+    </row>
+    <row r="1838" spans="1:5">
+      <c r="A1838" s="1" t="s">
+        <v>1840</v>
+      </c>
+      <c r="C1838">
+        <v>10.53853511810303</v>
+      </c>
+      <c r="D1838">
+        <v>6.446229457855225</v>
+      </c>
+      <c r="E1838">
+        <v>9.90286922454834</v>
       </c>
     </row>
   </sheetData>

--- a/create_forecast_basic/utils/monitoring_df_fixed_1.xlsx
+++ b/create_forecast_basic/utils/monitoring_df_fixed_1.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1891" uniqueCount="1859">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2083" uniqueCount="2033">
   <si>
     <t>2020</t>
   </si>
@@ -5579,6 +5579,546 @@
   </si>
   <si>
     <t>percentage growth emp education תלפיות מזרח 2045-2050</t>
+  </si>
+  <si>
+    <t>percentage growth emp education אבו גוש 2020-2025</t>
+  </si>
+  <si>
+    <t>percentage growth emp education אורנית 2020-2025</t>
+  </si>
+  <si>
+    <t>percentage growth emp education אלפי מנשה 2020-2025</t>
+  </si>
+  <si>
+    <t>percentage growth emp education אפרת 2020-2025</t>
+  </si>
+  <si>
+    <t>percentage growth emp education אריאל 2020-2025</t>
+  </si>
+  <si>
+    <t>percentage growth emp education בית אל 2020-2025</t>
+  </si>
+  <si>
+    <t>percentage growth emp education בית אריה-עופרים 2020-2025</t>
+  </si>
+  <si>
+    <t>percentage growth emp education בית שמש 2020-2025</t>
+  </si>
+  <si>
+    <t>percentage growth emp education ביתר עילית 2020-2025</t>
+  </si>
+  <si>
+    <t>percentage growth emp education גבעת זאב 2020-2025</t>
+  </si>
+  <si>
+    <t>percentage growth emp education גוש עציון 2020-2025</t>
+  </si>
+  <si>
+    <t>percentage growth emp education הר אדר 2020-2025</t>
+  </si>
+  <si>
+    <t>percentage growth emp education הר חברון_x005F_x000D_
+ 2020-2025</t>
+  </si>
+  <si>
+    <t>percentage growth emp education ירושלים 2020-2025</t>
+  </si>
+  <si>
+    <t>percentage growth emp education מבשרת ציון 2020-2025</t>
+  </si>
+  <si>
+    <t>percentage growth emp education מגילות ים המלח_x005F_x000D_
+ 2020-2025</t>
+  </si>
+  <si>
+    <t>percentage growth emp education מודיעין - מכבים - רעות 2020-2025</t>
+  </si>
+  <si>
+    <t>percentage growth emp education מודיעין עילית 2020-2025</t>
+  </si>
+  <si>
+    <t>percentage growth emp education מטה בנימין 2020-2025</t>
+  </si>
+  <si>
+    <t>percentage growth emp education מטה יהודה 2020-2025</t>
+  </si>
+  <si>
+    <t>percentage growth emp education מעלה אדומים 2020-2025</t>
+  </si>
+  <si>
+    <t>percentage growth emp education מעלה אפרים 2020-2025</t>
+  </si>
+  <si>
+    <t>percentage growth emp education עמנואל 2020-2025</t>
+  </si>
+  <si>
+    <t>percentage growth emp education ערבות הירדן_x005F_x000D_
+ 2020-2025</t>
+  </si>
+  <si>
+    <t>percentage growth emp education קדומים 2020-2025</t>
+  </si>
+  <si>
+    <t>percentage growth emp education קריית ארבע 2020-2025</t>
+  </si>
+  <si>
+    <t>percentage growth emp education קרית יערים 2020-2025</t>
+  </si>
+  <si>
+    <t>percentage growth emp education קרני שומרון 2020-2025</t>
+  </si>
+  <si>
+    <t>percentage growth emp education שומרון 2020-2025</t>
+  </si>
+  <si>
+    <t>percentage growth emp education אבו גוש 2025-2030</t>
+  </si>
+  <si>
+    <t>percentage growth emp education אורנית 2025-2030</t>
+  </si>
+  <si>
+    <t>percentage growth emp education אלפי מנשה 2025-2030</t>
+  </si>
+  <si>
+    <t>percentage growth emp education אפרת 2025-2030</t>
+  </si>
+  <si>
+    <t>percentage growth emp education אריאל 2025-2030</t>
+  </si>
+  <si>
+    <t>percentage growth emp education בית אל 2025-2030</t>
+  </si>
+  <si>
+    <t>percentage growth emp education בית אריה-עופרים 2025-2030</t>
+  </si>
+  <si>
+    <t>percentage growth emp education בית שמש 2025-2030</t>
+  </si>
+  <si>
+    <t>percentage growth emp education ביתר עילית 2025-2030</t>
+  </si>
+  <si>
+    <t>percentage growth emp education גבעת זאב 2025-2030</t>
+  </si>
+  <si>
+    <t>percentage growth emp education גוש עציון 2025-2030</t>
+  </si>
+  <si>
+    <t>percentage growth emp education הר אדר 2025-2030</t>
+  </si>
+  <si>
+    <t>percentage growth emp education הר חברון_x005F_x000D_
+ 2025-2030</t>
+  </si>
+  <si>
+    <t>percentage growth emp education ירושלים 2025-2030</t>
+  </si>
+  <si>
+    <t>percentage growth emp education מבשרת ציון 2025-2030</t>
+  </si>
+  <si>
+    <t>percentage growth emp education מגילות ים המלח_x005F_x000D_
+ 2025-2030</t>
+  </si>
+  <si>
+    <t>percentage growth emp education מודיעין - מכבים - רעות 2025-2030</t>
+  </si>
+  <si>
+    <t>percentage growth emp education מודיעין עילית 2025-2030</t>
+  </si>
+  <si>
+    <t>percentage growth emp education מטה בנימין 2025-2030</t>
+  </si>
+  <si>
+    <t>percentage growth emp education מטה יהודה 2025-2030</t>
+  </si>
+  <si>
+    <t>percentage growth emp education מעלה אדומים 2025-2030</t>
+  </si>
+  <si>
+    <t>percentage growth emp education מעלה אפרים 2025-2030</t>
+  </si>
+  <si>
+    <t>percentage growth emp education עמנואל 2025-2030</t>
+  </si>
+  <si>
+    <t>percentage growth emp education ערבות הירדן_x005F_x000D_
+ 2025-2030</t>
+  </si>
+  <si>
+    <t>percentage growth emp education קדומים 2025-2030</t>
+  </si>
+  <si>
+    <t>percentage growth emp education קריית ארבע 2025-2030</t>
+  </si>
+  <si>
+    <t>percentage growth emp education קרית יערים 2025-2030</t>
+  </si>
+  <si>
+    <t>percentage growth emp education קרני שומרון 2025-2030</t>
+  </si>
+  <si>
+    <t>percentage growth emp education שומרון 2025-2030</t>
+  </si>
+  <si>
+    <t>percentage growth emp education אבו גוש 2030-2035</t>
+  </si>
+  <si>
+    <t>percentage growth emp education אורנית 2030-2035</t>
+  </si>
+  <si>
+    <t>percentage growth emp education אלפי מנשה 2030-2035</t>
+  </si>
+  <si>
+    <t>percentage growth emp education אפרת 2030-2035</t>
+  </si>
+  <si>
+    <t>percentage growth emp education אריאל 2030-2035</t>
+  </si>
+  <si>
+    <t>percentage growth emp education בית אל 2030-2035</t>
+  </si>
+  <si>
+    <t>percentage growth emp education בית אריה-עופרים 2030-2035</t>
+  </si>
+  <si>
+    <t>percentage growth emp education בית שמש 2030-2035</t>
+  </si>
+  <si>
+    <t>percentage growth emp education ביתר עילית 2030-2035</t>
+  </si>
+  <si>
+    <t>percentage growth emp education גבעת זאב 2030-2035</t>
+  </si>
+  <si>
+    <t>percentage growth emp education גוש עציון 2030-2035</t>
+  </si>
+  <si>
+    <t>percentage growth emp education הר אדר 2030-2035</t>
+  </si>
+  <si>
+    <t>percentage growth emp education הר חברון_x005F_x000D_
+ 2030-2035</t>
+  </si>
+  <si>
+    <t>percentage growth emp education ירושלים 2030-2035</t>
+  </si>
+  <si>
+    <t>percentage growth emp education מבשרת ציון 2030-2035</t>
+  </si>
+  <si>
+    <t>percentage growth emp education מגילות ים המלח_x005F_x000D_
+ 2030-2035</t>
+  </si>
+  <si>
+    <t>percentage growth emp education מודיעין - מכבים - רעות 2030-2035</t>
+  </si>
+  <si>
+    <t>percentage growth emp education מודיעין עילית 2030-2035</t>
+  </si>
+  <si>
+    <t>percentage growth emp education מטה בנימין 2030-2035</t>
+  </si>
+  <si>
+    <t>percentage growth emp education מטה יהודה 2030-2035</t>
+  </si>
+  <si>
+    <t>percentage growth emp education מעלה אדומים 2030-2035</t>
+  </si>
+  <si>
+    <t>percentage growth emp education מעלה אפרים 2030-2035</t>
+  </si>
+  <si>
+    <t>percentage growth emp education עמנואל 2030-2035</t>
+  </si>
+  <si>
+    <t>percentage growth emp education ערבות הירדן_x005F_x000D_
+ 2030-2035</t>
+  </si>
+  <si>
+    <t>percentage growth emp education קדומים 2030-2035</t>
+  </si>
+  <si>
+    <t>percentage growth emp education קריית ארבע 2030-2035</t>
+  </si>
+  <si>
+    <t>percentage growth emp education קרית יערים 2030-2035</t>
+  </si>
+  <si>
+    <t>percentage growth emp education קרני שומרון 2030-2035</t>
+  </si>
+  <si>
+    <t>percentage growth emp education שומרון 2030-2035</t>
+  </si>
+  <si>
+    <t>percentage growth emp education אבו גוש 2035-2040</t>
+  </si>
+  <si>
+    <t>percentage growth emp education אורנית 2035-2040</t>
+  </si>
+  <si>
+    <t>percentage growth emp education אלפי מנשה 2035-2040</t>
+  </si>
+  <si>
+    <t>percentage growth emp education אפרת 2035-2040</t>
+  </si>
+  <si>
+    <t>percentage growth emp education אריאל 2035-2040</t>
+  </si>
+  <si>
+    <t>percentage growth emp education בית אל 2035-2040</t>
+  </si>
+  <si>
+    <t>percentage growth emp education בית אריה-עופרים 2035-2040</t>
+  </si>
+  <si>
+    <t>percentage growth emp education בית שמש 2035-2040</t>
+  </si>
+  <si>
+    <t>percentage growth emp education ביתר עילית 2035-2040</t>
+  </si>
+  <si>
+    <t>percentage growth emp education גבעת זאב 2035-2040</t>
+  </si>
+  <si>
+    <t>percentage growth emp education גוש עציון 2035-2040</t>
+  </si>
+  <si>
+    <t>percentage growth emp education הר אדר 2035-2040</t>
+  </si>
+  <si>
+    <t>percentage growth emp education הר חברון_x005F_x000D_
+ 2035-2040</t>
+  </si>
+  <si>
+    <t>percentage growth emp education ירושלים 2035-2040</t>
+  </si>
+  <si>
+    <t>percentage growth emp education מבשרת ציון 2035-2040</t>
+  </si>
+  <si>
+    <t>percentage growth emp education מגילות ים המלח_x005F_x000D_
+ 2035-2040</t>
+  </si>
+  <si>
+    <t>percentage growth emp education מודיעין - מכבים - רעות 2035-2040</t>
+  </si>
+  <si>
+    <t>percentage growth emp education מודיעין עילית 2035-2040</t>
+  </si>
+  <si>
+    <t>percentage growth emp education מטה בנימין 2035-2040</t>
+  </si>
+  <si>
+    <t>percentage growth emp education מטה יהודה 2035-2040</t>
+  </si>
+  <si>
+    <t>percentage growth emp education מעלה אדומים 2035-2040</t>
+  </si>
+  <si>
+    <t>percentage growth emp education מעלה אפרים 2035-2040</t>
+  </si>
+  <si>
+    <t>percentage growth emp education עמנואל 2035-2040</t>
+  </si>
+  <si>
+    <t>percentage growth emp education ערבות הירדן_x005F_x000D_
+ 2035-2040</t>
+  </si>
+  <si>
+    <t>percentage growth emp education קדומים 2035-2040</t>
+  </si>
+  <si>
+    <t>percentage growth emp education קריית ארבע 2035-2040</t>
+  </si>
+  <si>
+    <t>percentage growth emp education קרית יערים 2035-2040</t>
+  </si>
+  <si>
+    <t>percentage growth emp education קרני שומרון 2035-2040</t>
+  </si>
+  <si>
+    <t>percentage growth emp education שומרון 2035-2040</t>
+  </si>
+  <si>
+    <t>percentage growth emp education אבו גוש 2040-2045</t>
+  </si>
+  <si>
+    <t>percentage growth emp education אורנית 2040-2045</t>
+  </si>
+  <si>
+    <t>percentage growth emp education אלפי מנשה 2040-2045</t>
+  </si>
+  <si>
+    <t>percentage growth emp education אפרת 2040-2045</t>
+  </si>
+  <si>
+    <t>percentage growth emp education אריאל 2040-2045</t>
+  </si>
+  <si>
+    <t>percentage growth emp education בית אל 2040-2045</t>
+  </si>
+  <si>
+    <t>percentage growth emp education בית אריה-עופרים 2040-2045</t>
+  </si>
+  <si>
+    <t>percentage growth emp education בית שמש 2040-2045</t>
+  </si>
+  <si>
+    <t>percentage growth emp education ביתר עילית 2040-2045</t>
+  </si>
+  <si>
+    <t>percentage growth emp education גבעת זאב 2040-2045</t>
+  </si>
+  <si>
+    <t>percentage growth emp education גוש עציון 2040-2045</t>
+  </si>
+  <si>
+    <t>percentage growth emp education הר אדר 2040-2045</t>
+  </si>
+  <si>
+    <t>percentage growth emp education הר חברון_x005F_x000D_
+ 2040-2045</t>
+  </si>
+  <si>
+    <t>percentage growth emp education ירושלים 2040-2045</t>
+  </si>
+  <si>
+    <t>percentage growth emp education מבשרת ציון 2040-2045</t>
+  </si>
+  <si>
+    <t>percentage growth emp education מגילות ים המלח_x005F_x000D_
+ 2040-2045</t>
+  </si>
+  <si>
+    <t>percentage growth emp education מודיעין - מכבים - רעות 2040-2045</t>
+  </si>
+  <si>
+    <t>percentage growth emp education מודיעין עילית 2040-2045</t>
+  </si>
+  <si>
+    <t>percentage growth emp education מטה בנימין 2040-2045</t>
+  </si>
+  <si>
+    <t>percentage growth emp education מטה יהודה 2040-2045</t>
+  </si>
+  <si>
+    <t>percentage growth emp education מעלה אדומים 2040-2045</t>
+  </si>
+  <si>
+    <t>percentage growth emp education מעלה אפרים 2040-2045</t>
+  </si>
+  <si>
+    <t>percentage growth emp education עמנואל 2040-2045</t>
+  </si>
+  <si>
+    <t>percentage growth emp education ערבות הירדן_x005F_x000D_
+ 2040-2045</t>
+  </si>
+  <si>
+    <t>percentage growth emp education קדומים 2040-2045</t>
+  </si>
+  <si>
+    <t>percentage growth emp education קריית ארבע 2040-2045</t>
+  </si>
+  <si>
+    <t>percentage growth emp education קרית יערים 2040-2045</t>
+  </si>
+  <si>
+    <t>percentage growth emp education קרני שומרון 2040-2045</t>
+  </si>
+  <si>
+    <t>percentage growth emp education שומרון 2040-2045</t>
+  </si>
+  <si>
+    <t>percentage growth emp education אבו גוש 2045-2050</t>
+  </si>
+  <si>
+    <t>percentage growth emp education אורנית 2045-2050</t>
+  </si>
+  <si>
+    <t>percentage growth emp education אלפי מנשה 2045-2050</t>
+  </si>
+  <si>
+    <t>percentage growth emp education אפרת 2045-2050</t>
+  </si>
+  <si>
+    <t>percentage growth emp education אריאל 2045-2050</t>
+  </si>
+  <si>
+    <t>percentage growth emp education בית אל 2045-2050</t>
+  </si>
+  <si>
+    <t>percentage growth emp education בית אריה-עופרים 2045-2050</t>
+  </si>
+  <si>
+    <t>percentage growth emp education בית שמש 2045-2050</t>
+  </si>
+  <si>
+    <t>percentage growth emp education ביתר עילית 2045-2050</t>
+  </si>
+  <si>
+    <t>percentage growth emp education גבעת זאב 2045-2050</t>
+  </si>
+  <si>
+    <t>percentage growth emp education גוש עציון 2045-2050</t>
+  </si>
+  <si>
+    <t>percentage growth emp education הר אדר 2045-2050</t>
+  </si>
+  <si>
+    <t>percentage growth emp education הר חברון_x005F_x000D_
+ 2045-2050</t>
+  </si>
+  <si>
+    <t>percentage growth emp education ירושלים 2045-2050</t>
+  </si>
+  <si>
+    <t>percentage growth emp education מבשרת ציון 2045-2050</t>
+  </si>
+  <si>
+    <t>percentage growth emp education מגילות ים המלח_x005F_x000D_
+ 2045-2050</t>
+  </si>
+  <si>
+    <t>percentage growth emp education מודיעין - מכבים - רעות 2045-2050</t>
+  </si>
+  <si>
+    <t>percentage growth emp education מודיעין עילית 2045-2050</t>
+  </si>
+  <si>
+    <t>percentage growth emp education מטה בנימין 2045-2050</t>
+  </si>
+  <si>
+    <t>percentage growth emp education מטה יהודה 2045-2050</t>
+  </si>
+  <si>
+    <t>percentage growth emp education מעלה אדומים 2045-2050</t>
+  </si>
+  <si>
+    <t>percentage growth emp education מעלה אפרים 2045-2050</t>
+  </si>
+  <si>
+    <t>percentage growth emp education עמנואל 2045-2050</t>
+  </si>
+  <si>
+    <t>percentage growth emp education ערבות הירדן_x005F_x000D_
+ 2045-2050</t>
+  </si>
+  <si>
+    <t>percentage growth emp education קדומים 2045-2050</t>
+  </si>
+  <si>
+    <t>percentage growth emp education קריית ארבע 2045-2050</t>
+  </si>
+  <si>
+    <t>percentage growth emp education קרית יערים 2045-2050</t>
+  </si>
+  <si>
+    <t>percentage growth emp education קרני שומרון 2045-2050</t>
+  </si>
+  <si>
+    <t>percentage growth emp education שומרון 2045-2050</t>
   </si>
   <si>
     <t>1,758,461</t>
@@ -5990,7 +6530,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E1838"/>
+  <dimension ref="A1:E2012"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -6012,16 +6552,16 @@
         <v>4</v>
       </c>
       <c r="B2" t="s">
-        <v>1841</v>
+        <v>2015</v>
       </c>
       <c r="C2" t="s">
-        <v>1841</v>
+        <v>2015</v>
       </c>
       <c r="D2" t="s">
-        <v>1841</v>
+        <v>2015</v>
       </c>
       <c r="E2" t="s">
-        <v>1841</v>
+        <v>2015</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -6029,13 +6569,13 @@
         <v>5</v>
       </c>
       <c r="C3" t="s">
-        <v>1846</v>
+        <v>2020</v>
       </c>
       <c r="D3" t="s">
-        <v>1851</v>
+        <v>2025</v>
       </c>
       <c r="E3" t="s">
-        <v>1855</v>
+        <v>2029</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -6043,16 +6583,16 @@
         <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>1842</v>
+        <v>2016</v>
       </c>
       <c r="C4" t="s">
-        <v>1842</v>
+        <v>2016</v>
       </c>
       <c r="D4" t="s">
-        <v>1842</v>
+        <v>2016</v>
       </c>
       <c r="E4" t="s">
-        <v>1842</v>
+        <v>2016</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -6060,13 +6600,13 @@
         <v>7</v>
       </c>
       <c r="C5" t="s">
-        <v>1847</v>
+        <v>2021</v>
       </c>
       <c r="D5" t="s">
-        <v>1852</v>
+        <v>2026</v>
       </c>
       <c r="E5" t="s">
-        <v>1856</v>
+        <v>2030</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -6159,16 +6699,16 @@
         <v>13</v>
       </c>
       <c r="B11" t="s">
-        <v>1843</v>
+        <v>2017</v>
       </c>
       <c r="C11" t="s">
-        <v>1843</v>
+        <v>2017</v>
       </c>
       <c r="D11" t="s">
-        <v>1843</v>
+        <v>2017</v>
       </c>
       <c r="E11" t="s">
-        <v>1843</v>
+        <v>2017</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -6176,13 +6716,13 @@
         <v>14</v>
       </c>
       <c r="C12" t="s">
-        <v>1843</v>
+        <v>2017</v>
       </c>
       <c r="D12" t="s">
-        <v>1843</v>
+        <v>2017</v>
       </c>
       <c r="E12" t="s">
-        <v>1843</v>
+        <v>2017</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -6190,16 +6730,16 @@
         <v>15</v>
       </c>
       <c r="B13" t="s">
-        <v>1844</v>
+        <v>2018</v>
       </c>
       <c r="C13" t="s">
-        <v>1844</v>
+        <v>2018</v>
       </c>
       <c r="D13" t="s">
-        <v>1844</v>
+        <v>2018</v>
       </c>
       <c r="E13" t="s">
-        <v>1844</v>
+        <v>2018</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -6207,13 +6747,13 @@
         <v>16</v>
       </c>
       <c r="C14" t="s">
-        <v>1848</v>
+        <v>2022</v>
       </c>
       <c r="D14" t="s">
-        <v>1853</v>
+        <v>2027</v>
       </c>
       <c r="E14" t="s">
-        <v>1857</v>
+        <v>2031</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -6221,16 +6761,16 @@
         <v>17</v>
       </c>
       <c r="B15" t="s">
-        <v>1845</v>
+        <v>2019</v>
       </c>
       <c r="C15" t="s">
-        <v>1845</v>
+        <v>2019</v>
       </c>
       <c r="D15" t="s">
-        <v>1845</v>
+        <v>2019</v>
       </c>
       <c r="E15" t="s">
-        <v>1845</v>
+        <v>2019</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -6238,13 +6778,13 @@
         <v>18</v>
       </c>
       <c r="C16" t="s">
-        <v>1849</v>
+        <v>2023</v>
       </c>
       <c r="D16" t="s">
-        <v>1854</v>
+        <v>2028</v>
       </c>
       <c r="E16" t="s">
-        <v>1858</v>
+        <v>2032</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -6685,13 +7225,13 @@
         <v>48</v>
       </c>
       <c r="C46" t="s">
-        <v>1850</v>
+        <v>2024</v>
       </c>
       <c r="D46" t="s">
-        <v>1850</v>
+        <v>2024</v>
       </c>
       <c r="E46" t="s">
-        <v>1850</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="47" spans="1:5">
@@ -27083,13 +27623,13 @@
         <v>1505</v>
       </c>
       <c r="C1503">
-        <v>-26.68354606628418</v>
+        <v>-16.85929489135742</v>
       </c>
       <c r="D1503">
-        <v>-28.10066604614258</v>
+        <v>-17.64156723022461</v>
       </c>
       <c r="E1503">
-        <v>-26.38949012756348</v>
+        <v>-15.83106994628906</v>
       </c>
     </row>
     <row r="1504" spans="1:5">
@@ -27359,13 +27899,13 @@
         <v>1526</v>
       </c>
       <c r="C1524" t="s">
-        <v>1850</v>
+        <v>2024</v>
       </c>
       <c r="D1524" t="s">
-        <v>1850</v>
+        <v>2024</v>
       </c>
       <c r="E1524" t="s">
-        <v>1850</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="1525" spans="1:5">
@@ -27831,13 +28371,13 @@
         <v>1561</v>
       </c>
       <c r="C1559">
-        <v>22.70803070068359</v>
+        <v>4.33017110824585</v>
       </c>
       <c r="D1559">
-        <v>9.348258972167969</v>
+        <v>0.8684369325637817</v>
       </c>
       <c r="E1559">
-        <v>18.4731616973877</v>
+        <v>1.681298136711121</v>
       </c>
     </row>
     <row r="1560" spans="1:5">
@@ -27943,13 +28483,13 @@
         <v>1569</v>
       </c>
       <c r="C1567" t="s">
-        <v>1850</v>
+        <v>2024</v>
       </c>
       <c r="D1567" t="s">
-        <v>1850</v>
+        <v>2024</v>
       </c>
       <c r="E1567" t="s">
-        <v>1850</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="1568" spans="1:5">
@@ -28588,13 +29128,13 @@
         <v>1617</v>
       </c>
       <c r="C1615">
-        <v>15.13704109191895</v>
+        <v>3.691997051239014</v>
       </c>
       <c r="D1615">
-        <v>16.02740478515625</v>
+        <v>0.5136735439300537</v>
       </c>
       <c r="E1615">
-        <v>14.33720111846924</v>
+        <v>0.6098133325576782</v>
       </c>
     </row>
     <row r="1616" spans="1:5">
@@ -28840,13 +29380,13 @@
         <v>1635</v>
       </c>
       <c r="C1633" t="s">
-        <v>1850</v>
+        <v>2024</v>
       </c>
       <c r="D1633" t="s">
-        <v>1850</v>
+        <v>2024</v>
       </c>
       <c r="E1633" t="s">
-        <v>1850</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="1634" spans="1:5">
@@ -29223,7 +29763,7 @@
         <v>1663</v>
       </c>
       <c r="C1661" t="s">
-        <v>1850</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="1662" spans="1:5">
@@ -29357,13 +29897,13 @@
         <v>1673</v>
       </c>
       <c r="C1671">
-        <v>13.68764114379883</v>
+        <v>5.889151573181152</v>
       </c>
       <c r="D1671">
-        <v>15.86247730255127</v>
+        <v>0.5769818425178528</v>
       </c>
       <c r="E1671">
-        <v>18.48310661315918</v>
+        <v>1.787942409515381</v>
       </c>
     </row>
     <row r="1672" spans="1:5">
@@ -30126,13 +30666,13 @@
         <v>1729</v>
       </c>
       <c r="C1727">
-        <v>0.8824127912521362</v>
+        <v>0.6130074858665466</v>
       </c>
       <c r="D1727">
-        <v>2.5003662109375</v>
+        <v>0.5606398582458496</v>
       </c>
       <c r="E1727">
-        <v>9.929659843444824</v>
+        <v>0.7679650187492371</v>
       </c>
     </row>
     <row r="1728" spans="1:5">
@@ -30728,10 +31268,10 @@
         <v>1772</v>
       </c>
       <c r="C1770" t="s">
-        <v>1850</v>
+        <v>2024</v>
       </c>
       <c r="E1770" t="s">
-        <v>1850</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="1771" spans="1:5">
@@ -30901,13 +31441,13 @@
         <v>1785</v>
       </c>
       <c r="C1783">
-        <v>6.790185451507568</v>
+        <v>0.2484400272369385</v>
       </c>
       <c r="D1783">
-        <v>11.82536602020264</v>
+        <v>0.5473768711090088</v>
       </c>
       <c r="E1783">
-        <v>10.5778923034668</v>
+        <v>1.028585910797119</v>
       </c>
     </row>
     <row r="1784" spans="1:5">
@@ -31669,6 +32209,2397 @@
       </c>
       <c r="E1838">
         <v>9.90286922454834</v>
+      </c>
+    </row>
+    <row r="1839" spans="1:5">
+      <c r="A1839" s="1" t="s">
+        <v>1841</v>
+      </c>
+      <c r="C1839">
+        <v>-8.940157890319824</v>
+      </c>
+      <c r="D1839">
+        <v>-10.28324222564697</v>
+      </c>
+      <c r="E1839">
+        <v>-9.841169357299805</v>
+      </c>
+    </row>
+    <row r="1840" spans="1:5">
+      <c r="A1840" s="1" t="s">
+        <v>1842</v>
+      </c>
+      <c r="C1840">
+        <v>-28.45031547546387</v>
+      </c>
+      <c r="D1840">
+        <v>-100</v>
+      </c>
+      <c r="E1840">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="1841" spans="1:5">
+      <c r="A1841" s="1" t="s">
+        <v>1843</v>
+      </c>
+      <c r="C1841">
+        <v>27.62912940979004</v>
+      </c>
+      <c r="D1841">
+        <v>28.98475074768066</v>
+      </c>
+      <c r="E1841">
+        <v>30.40701866149902</v>
+      </c>
+    </row>
+    <row r="1842" spans="1:5">
+      <c r="A1842" s="1" t="s">
+        <v>1844</v>
+      </c>
+      <c r="C1842">
+        <v>-97.96548461914062</v>
+      </c>
+      <c r="D1842">
+        <v>-97.9892578125</v>
+      </c>
+      <c r="E1842">
+        <v>-97.94863128662109</v>
+      </c>
+    </row>
+    <row r="1843" spans="1:5">
+      <c r="A1843" s="1" t="s">
+        <v>1845</v>
+      </c>
+      <c r="C1843">
+        <v>-25.80515670776367</v>
+      </c>
+      <c r="D1843">
+        <v>-25.80810546875</v>
+      </c>
+      <c r="E1843">
+        <v>-25.80306816101074</v>
+      </c>
+    </row>
+    <row r="1844" spans="1:5">
+      <c r="A1844" s="1" t="s">
+        <v>1846</v>
+      </c>
+      <c r="C1844">
+        <v>-92.50789642333984</v>
+      </c>
+      <c r="D1844">
+        <v>-92.59545135498047</v>
+      </c>
+      <c r="E1844">
+        <v>-92.44584655761719</v>
+      </c>
+    </row>
+    <row r="1845" spans="1:5">
+      <c r="A1845" s="1" t="s">
+        <v>1847</v>
+      </c>
+      <c r="C1845">
+        <v>45.0267219543457</v>
+      </c>
+      <c r="D1845">
+        <v>33.20018005371094</v>
+      </c>
+      <c r="E1845">
+        <v>48.18932342529297</v>
+      </c>
+    </row>
+    <row r="1846" spans="1:5">
+      <c r="A1846" s="1" t="s">
+        <v>1848</v>
+      </c>
+      <c r="C1846">
+        <v>-26.64229202270508</v>
+      </c>
+      <c r="D1846">
+        <v>-31.61293411254883</v>
+      </c>
+      <c r="E1846">
+        <v>-29.40289115905762</v>
+      </c>
+    </row>
+    <row r="1847" spans="1:5">
+      <c r="A1847" s="1" t="s">
+        <v>1849</v>
+      </c>
+      <c r="C1847">
+        <v>-23.46528625488281</v>
+      </c>
+      <c r="D1847">
+        <v>-19.79804611206055</v>
+      </c>
+      <c r="E1847">
+        <v>-18.66863250732422</v>
+      </c>
+    </row>
+    <row r="1848" spans="1:5">
+      <c r="A1848" s="1" t="s">
+        <v>1850</v>
+      </c>
+      <c r="C1848">
+        <v>138.2331390380859</v>
+      </c>
+      <c r="D1848">
+        <v>162.4386138916016</v>
+      </c>
+      <c r="E1848">
+        <v>170.8627471923828</v>
+      </c>
+    </row>
+    <row r="1849" spans="1:5">
+      <c r="A1849" s="1" t="s">
+        <v>1851</v>
+      </c>
+      <c r="C1849">
+        <v>-10.17635631561279</v>
+      </c>
+      <c r="D1849">
+        <v>-10.70745944976807</v>
+      </c>
+      <c r="E1849">
+        <v>-9.646365165710449</v>
+      </c>
+    </row>
+    <row r="1850" spans="1:5">
+      <c r="A1850" s="1" t="s">
+        <v>1852</v>
+      </c>
+      <c r="C1850">
+        <v>43.4904670715332</v>
+      </c>
+      <c r="D1850">
+        <v>-100</v>
+      </c>
+      <c r="E1850">
+        <v>53.30073547363281</v>
+      </c>
+    </row>
+    <row r="1851" spans="1:5">
+      <c r="A1851" s="1" t="s">
+        <v>1853</v>
+      </c>
+      <c r="C1851">
+        <v>-22.16069221496582</v>
+      </c>
+      <c r="D1851">
+        <v>-21.57657432556152</v>
+      </c>
+      <c r="E1851">
+        <v>-19.96999931335449</v>
+      </c>
+    </row>
+    <row r="1852" spans="1:5">
+      <c r="A1852" s="1" t="s">
+        <v>1854</v>
+      </c>
+      <c r="C1852">
+        <v>-23.71253204345703</v>
+      </c>
+      <c r="D1852">
+        <v>-25.97347068786621</v>
+      </c>
+      <c r="E1852">
+        <v>-25.61108779907227</v>
+      </c>
+    </row>
+    <row r="1853" spans="1:5">
+      <c r="A1853" s="1" t="s">
+        <v>1855</v>
+      </c>
+      <c r="C1853">
+        <v>-30.15028762817383</v>
+      </c>
+      <c r="D1853">
+        <v>-33.98865127563477</v>
+      </c>
+      <c r="E1853">
+        <v>-32.14559173583984</v>
+      </c>
+    </row>
+    <row r="1854" spans="1:5">
+      <c r="A1854" s="1" t="s">
+        <v>1856</v>
+      </c>
+      <c r="C1854">
+        <v>-100</v>
+      </c>
+      <c r="D1854">
+        <v>-100</v>
+      </c>
+      <c r="E1854">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="1855" spans="1:5">
+      <c r="A1855" s="1" t="s">
+        <v>1857</v>
+      </c>
+      <c r="C1855">
+        <v>-29.41009140014648</v>
+      </c>
+      <c r="D1855">
+        <v>-29.41009140014648</v>
+      </c>
+      <c r="E1855">
+        <v>-29.41009140014648</v>
+      </c>
+    </row>
+    <row r="1856" spans="1:5">
+      <c r="A1856" s="1" t="s">
+        <v>1858</v>
+      </c>
+      <c r="C1856">
+        <v>-25.99195861816406</v>
+      </c>
+      <c r="D1856">
+        <v>-22.63495254516602</v>
+      </c>
+      <c r="E1856">
+        <v>-20.26705169677734</v>
+      </c>
+    </row>
+    <row r="1857" spans="1:5">
+      <c r="A1857" s="1" t="s">
+        <v>1859</v>
+      </c>
+      <c r="C1857">
+        <v>-29.07699394226074</v>
+      </c>
+      <c r="D1857">
+        <v>-29.23058891296387</v>
+      </c>
+      <c r="E1857">
+        <v>-28.31185913085938</v>
+      </c>
+    </row>
+    <row r="1858" spans="1:5">
+      <c r="A1858" s="1" t="s">
+        <v>1860</v>
+      </c>
+      <c r="C1858">
+        <v>17.64059066772461</v>
+      </c>
+      <c r="D1858">
+        <v>8.361394882202148</v>
+      </c>
+      <c r="E1858">
+        <v>12.10616874694824</v>
+      </c>
+    </row>
+    <row r="1859" spans="1:5">
+      <c r="A1859" s="1" t="s">
+        <v>1861</v>
+      </c>
+      <c r="C1859">
+        <v>-39.1231689453125</v>
+      </c>
+      <c r="D1859">
+        <v>-37.74115371704102</v>
+      </c>
+      <c r="E1859">
+        <v>-37.02981948852539</v>
+      </c>
+    </row>
+    <row r="1860" spans="1:5">
+      <c r="A1860" s="1" t="s">
+        <v>1862</v>
+      </c>
+      <c r="C1860">
+        <v>-88.8736572265625</v>
+      </c>
+      <c r="D1860">
+        <v>-89.00368499755859</v>
+      </c>
+      <c r="E1860">
+        <v>-88.78150939941406</v>
+      </c>
+    </row>
+    <row r="1861" spans="1:5">
+      <c r="A1861" s="1" t="s">
+        <v>1863</v>
+      </c>
+      <c r="C1861">
+        <v>249.8621673583984</v>
+      </c>
+      <c r="D1861">
+        <v>265.9898376464844</v>
+      </c>
+      <c r="E1861">
+        <v>277.5034484863281</v>
+      </c>
+    </row>
+    <row r="1862" spans="1:5">
+      <c r="A1862" s="1" t="s">
+        <v>1864</v>
+      </c>
+      <c r="C1862">
+        <v>-21.96667289733887</v>
+      </c>
+      <c r="D1862">
+        <v>-20.1750545501709</v>
+      </c>
+      <c r="E1862">
+        <v>-16.58968353271484</v>
+      </c>
+    </row>
+    <row r="1863" spans="1:5">
+      <c r="A1863" s="1" t="s">
+        <v>1865</v>
+      </c>
+      <c r="C1863">
+        <v>-99.01702880859375</v>
+      </c>
+      <c r="D1863">
+        <v>-99.02851867675781</v>
+      </c>
+      <c r="E1863">
+        <v>-99.00888824462891</v>
+      </c>
+    </row>
+    <row r="1864" spans="1:5">
+      <c r="A1864" s="1" t="s">
+        <v>1866</v>
+      </c>
+      <c r="C1864">
+        <v>-97.70296478271484</v>
+      </c>
+      <c r="D1864">
+        <v>-97.72980499267578</v>
+      </c>
+      <c r="E1864">
+        <v>-97.68393707275391</v>
+      </c>
+    </row>
+    <row r="1865" spans="1:5">
+      <c r="A1865" s="1" t="s">
+        <v>1867</v>
+      </c>
+      <c r="C1865">
+        <v>-85.38395690917969</v>
+      </c>
+      <c r="D1865">
+        <v>-85.55476379394531</v>
+      </c>
+      <c r="E1865">
+        <v>-85.26290130615234</v>
+      </c>
+    </row>
+    <row r="1866" spans="1:5">
+      <c r="A1866" s="1" t="s">
+        <v>1868</v>
+      </c>
+      <c r="C1866">
+        <v>-94.00336456298828</v>
+      </c>
+      <c r="D1866">
+        <v>-94.07344818115234</v>
+      </c>
+      <c r="E1866">
+        <v>-93.95370483398438</v>
+      </c>
+    </row>
+    <row r="1867" spans="1:5">
+      <c r="A1867" s="1" t="s">
+        <v>1869</v>
+      </c>
+      <c r="C1867">
+        <v>-27.35002708435059</v>
+      </c>
+      <c r="D1867">
+        <v>-27.77956199645996</v>
+      </c>
+      <c r="E1867">
+        <v>-26.5982551574707</v>
+      </c>
+    </row>
+    <row r="1868" spans="1:5">
+      <c r="A1868" s="1" t="s">
+        <v>1870</v>
+      </c>
+      <c r="C1868">
+        <v>6.862723827362061</v>
+      </c>
+      <c r="D1868">
+        <v>-100</v>
+      </c>
+      <c r="E1868">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="1869" spans="1:5">
+      <c r="A1869" s="1" t="s">
+        <v>1871</v>
+      </c>
+      <c r="C1869">
+        <v>7.58171272277832</v>
+      </c>
+    </row>
+    <row r="1870" spans="1:5">
+      <c r="A1870" s="1" t="s">
+        <v>1872</v>
+      </c>
+      <c r="C1870">
+        <v>24.05439949035645</v>
+      </c>
+      <c r="D1870">
+        <v>10.6007251739502</v>
+      </c>
+      <c r="E1870">
+        <v>13.46783351898193</v>
+      </c>
+    </row>
+    <row r="1871" spans="1:5">
+      <c r="A1871" s="1" t="s">
+        <v>1873</v>
+      </c>
+      <c r="C1871">
+        <v>2657.453125</v>
+      </c>
+      <c r="D1871">
+        <v>12.02837181091309</v>
+      </c>
+      <c r="E1871">
+        <v>15.17903900146484</v>
+      </c>
+    </row>
+    <row r="1872" spans="1:5">
+      <c r="A1872" s="1" t="s">
+        <v>1874</v>
+      </c>
+      <c r="C1872">
+        <v>25.22663307189941</v>
+      </c>
+      <c r="D1872">
+        <v>25.99800300598145</v>
+      </c>
+      <c r="E1872">
+        <v>27.37622261047363</v>
+      </c>
+    </row>
+    <row r="1873" spans="1:5">
+      <c r="A1873" s="1" t="s">
+        <v>1875</v>
+      </c>
+      <c r="C1873">
+        <v>903.446044921875</v>
+      </c>
+      <c r="D1873">
+        <v>780.440185546875</v>
+      </c>
+      <c r="E1873">
+        <v>796.982666015625</v>
+      </c>
+    </row>
+    <row r="1874" spans="1:5">
+      <c r="A1874" s="1" t="s">
+        <v>1876</v>
+      </c>
+      <c r="C1874">
+        <v>27.49294853210449</v>
+      </c>
+      <c r="D1874">
+        <v>-100</v>
+      </c>
+      <c r="E1874">
+        <v>16.58352088928223</v>
+      </c>
+    </row>
+    <row r="1875" spans="1:5">
+      <c r="A1875" s="1" t="s">
+        <v>1877</v>
+      </c>
+      <c r="C1875">
+        <v>27.82895469665527</v>
+      </c>
+      <c r="D1875">
+        <v>28.59170532226562</v>
+      </c>
+      <c r="E1875">
+        <v>35.24016571044922</v>
+      </c>
+    </row>
+    <row r="1876" spans="1:5">
+      <c r="A1876" s="1" t="s">
+        <v>1878</v>
+      </c>
+      <c r="C1876">
+        <v>11.80511569976807</v>
+      </c>
+      <c r="D1876">
+        <v>9.253467559814453</v>
+      </c>
+      <c r="E1876">
+        <v>16.24175643920898</v>
+      </c>
+    </row>
+    <row r="1877" spans="1:5">
+      <c r="A1877" s="1" t="s">
+        <v>1879</v>
+      </c>
+      <c r="C1877">
+        <v>18.82792282104492</v>
+      </c>
+      <c r="D1877">
+        <v>14.69610500335693</v>
+      </c>
+      <c r="E1877">
+        <v>22.01045989990234</v>
+      </c>
+    </row>
+    <row r="1878" spans="1:5">
+      <c r="A1878" s="1" t="s">
+        <v>1880</v>
+      </c>
+      <c r="C1878">
+        <v>6.692920684814453</v>
+      </c>
+      <c r="D1878">
+        <v>3.490712404251099</v>
+      </c>
+      <c r="E1878">
+        <v>4.539451599121094</v>
+      </c>
+    </row>
+    <row r="1879" spans="1:5">
+      <c r="A1879" s="1" t="s">
+        <v>1881</v>
+      </c>
+      <c r="C1879">
+        <v>1.643964290618896</v>
+      </c>
+      <c r="E1879">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="1880" spans="1:5">
+      <c r="A1880" s="1" t="s">
+        <v>1882</v>
+      </c>
+      <c r="C1880">
+        <v>22.28820610046387</v>
+      </c>
+      <c r="D1880">
+        <v>3.529137849807739</v>
+      </c>
+      <c r="E1880">
+        <v>7.26594352722168</v>
+      </c>
+    </row>
+    <row r="1881" spans="1:5">
+      <c r="A1881" s="1" t="s">
+        <v>1883</v>
+      </c>
+      <c r="C1881">
+        <v>7.137650489807129</v>
+      </c>
+      <c r="D1881">
+        <v>4.957151889801025</v>
+      </c>
+      <c r="E1881">
+        <v>5.108507633209229</v>
+      </c>
+    </row>
+    <row r="1882" spans="1:5">
+      <c r="A1882" s="1" t="s">
+        <v>1884</v>
+      </c>
+      <c r="C1882">
+        <v>20.13122367858887</v>
+      </c>
+      <c r="D1882">
+        <v>14.03321838378906</v>
+      </c>
+      <c r="E1882">
+        <v>17.37783241271973</v>
+      </c>
+    </row>
+    <row r="1883" spans="1:5">
+      <c r="A1883" s="1" t="s">
+        <v>1885</v>
+      </c>
+      <c r="C1883" t="s">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="1884" spans="1:5">
+      <c r="A1884" s="1" t="s">
+        <v>1886</v>
+      </c>
+      <c r="C1884">
+        <v>17.09033584594727</v>
+      </c>
+      <c r="D1884">
+        <v>17.09033584594727</v>
+      </c>
+      <c r="E1884">
+        <v>17.09033584594727</v>
+      </c>
+    </row>
+    <row r="1885" spans="1:5">
+      <c r="A1885" s="1" t="s">
+        <v>1887</v>
+      </c>
+      <c r="C1885">
+        <v>9.402849197387695</v>
+      </c>
+      <c r="D1885">
+        <v>6.647522926330566</v>
+      </c>
+      <c r="E1885">
+        <v>11.64308643341064</v>
+      </c>
+    </row>
+    <row r="1886" spans="1:5">
+      <c r="A1886" s="1" t="s">
+        <v>1888</v>
+      </c>
+      <c r="C1886">
+        <v>15.52823543548584</v>
+      </c>
+      <c r="D1886">
+        <v>1.851727604866028</v>
+      </c>
+      <c r="E1886">
+        <v>6.139818668365479</v>
+      </c>
+    </row>
+    <row r="1887" spans="1:5">
+      <c r="A1887" s="1" t="s">
+        <v>1889</v>
+      </c>
+      <c r="C1887">
+        <v>9.152072906494141</v>
+      </c>
+      <c r="D1887">
+        <v>3.019472599029541</v>
+      </c>
+      <c r="E1887">
+        <v>5.885316371917725</v>
+      </c>
+    </row>
+    <row r="1888" spans="1:5">
+      <c r="A1888" s="1" t="s">
+        <v>1890</v>
+      </c>
+      <c r="C1888">
+        <v>17.12021064758301</v>
+      </c>
+      <c r="D1888">
+        <v>5.537042617797852</v>
+      </c>
+      <c r="E1888">
+        <v>7.69061279296875</v>
+      </c>
+    </row>
+    <row r="1889" spans="1:5">
+      <c r="A1889" s="1" t="s">
+        <v>1891</v>
+      </c>
+      <c r="C1889">
+        <v>1246.728271484375</v>
+      </c>
+      <c r="D1889">
+        <v>1134.054565429688</v>
+      </c>
+      <c r="E1889">
+        <v>1155.896606445312</v>
+      </c>
+    </row>
+    <row r="1890" spans="1:5">
+      <c r="A1890" s="1" t="s">
+        <v>1892</v>
+      </c>
+      <c r="C1890">
+        <v>32.31802749633789</v>
+      </c>
+      <c r="D1890">
+        <v>29.08674812316895</v>
+      </c>
+      <c r="E1890">
+        <v>35.35954666137695</v>
+      </c>
+    </row>
+    <row r="1891" spans="1:5">
+      <c r="A1891" s="1" t="s">
+        <v>1893</v>
+      </c>
+      <c r="C1891">
+        <v>16.34242248535156</v>
+      </c>
+      <c r="D1891">
+        <v>3.881914377212524</v>
+      </c>
+      <c r="E1891">
+        <v>7.013106346130371</v>
+      </c>
+    </row>
+    <row r="1892" spans="1:5">
+      <c r="A1892" s="1" t="s">
+        <v>1894</v>
+      </c>
+      <c r="C1892">
+        <v>7679.8896484375</v>
+      </c>
+      <c r="D1892">
+        <v>6154.1376953125</v>
+      </c>
+      <c r="E1892">
+        <v>6765.2626953125</v>
+      </c>
+    </row>
+    <row r="1893" spans="1:5">
+      <c r="A1893" s="1" t="s">
+        <v>1895</v>
+      </c>
+      <c r="C1893">
+        <v>2312.51416015625</v>
+      </c>
+      <c r="D1893">
+        <v>12.02837181091309</v>
+      </c>
+      <c r="E1893">
+        <v>15.17903900146484</v>
+      </c>
+    </row>
+    <row r="1894" spans="1:5">
+      <c r="A1894" s="1" t="s">
+        <v>1896</v>
+      </c>
+      <c r="C1894">
+        <v>667.0103149414062</v>
+      </c>
+      <c r="D1894">
+        <v>641.07568359375</v>
+      </c>
+      <c r="E1894">
+        <v>605.4154052734375</v>
+      </c>
+    </row>
+    <row r="1895" spans="1:5">
+      <c r="A1895" s="1" t="s">
+        <v>1897</v>
+      </c>
+      <c r="C1895">
+        <v>753.2020263671875</v>
+      </c>
+      <c r="D1895">
+        <v>12.02837181091309</v>
+      </c>
+      <c r="E1895">
+        <v>15.17903900146484</v>
+      </c>
+    </row>
+    <row r="1896" spans="1:5">
+      <c r="A1896" s="1" t="s">
+        <v>1898</v>
+      </c>
+      <c r="C1896">
+        <v>11.64621639251709</v>
+      </c>
+      <c r="D1896">
+        <v>-94.14774322509766</v>
+      </c>
+      <c r="E1896">
+        <v>2.993500709533691</v>
+      </c>
+    </row>
+    <row r="1897" spans="1:5">
+      <c r="A1897" s="1" t="s">
+        <v>1899</v>
+      </c>
+      <c r="C1897">
+        <v>7.468527317047119</v>
+      </c>
+      <c r="D1897" t="s">
+        <v>2024</v>
+      </c>
+      <c r="E1897" t="s">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="1898" spans="1:5">
+      <c r="A1898" s="1" t="s">
+        <v>1900</v>
+      </c>
+      <c r="C1898">
+        <v>8.318314552307129</v>
+      </c>
+    </row>
+    <row r="1899" spans="1:5">
+      <c r="A1899" s="1" t="s">
+        <v>1901</v>
+      </c>
+      <c r="C1899">
+        <v>8.760002136230469</v>
+      </c>
+      <c r="D1899">
+        <v>-99.64057159423828</v>
+      </c>
+      <c r="E1899">
+        <v>-99.62746429443359</v>
+      </c>
+    </row>
+    <row r="1900" spans="1:5">
+      <c r="A1900" s="1" t="s">
+        <v>1902</v>
+      </c>
+      <c r="C1900">
+        <v>13.06198024749756</v>
+      </c>
+      <c r="D1900">
+        <v>2262.28076171875</v>
+      </c>
+      <c r="E1900">
+        <v>2295.578369140625</v>
+      </c>
+    </row>
+    <row r="1901" spans="1:5">
+      <c r="A1901" s="1" t="s">
+        <v>1903</v>
+      </c>
+      <c r="C1901">
+        <v>3.836580038070679</v>
+      </c>
+      <c r="D1901">
+        <v>17.32173728942871</v>
+      </c>
+      <c r="E1901">
+        <v>20.05820655822754</v>
+      </c>
+    </row>
+    <row r="1902" spans="1:5">
+      <c r="A1902" s="1" t="s">
+        <v>1904</v>
+      </c>
+      <c r="C1902">
+        <v>4.046356201171875</v>
+      </c>
+      <c r="D1902">
+        <v>-85.02593994140625</v>
+      </c>
+      <c r="E1902">
+        <v>-84.51177978515625</v>
+      </c>
+    </row>
+    <row r="1903" spans="1:5">
+      <c r="A1903" s="1" t="s">
+        <v>1905</v>
+      </c>
+      <c r="C1903">
+        <v>22.17300224304199</v>
+      </c>
+      <c r="D1903" t="s">
+        <v>2024</v>
+      </c>
+      <c r="E1903">
+        <v>15.68651962280273</v>
+      </c>
+    </row>
+    <row r="1904" spans="1:5">
+      <c r="A1904" s="1" t="s">
+        <v>1906</v>
+      </c>
+      <c r="C1904">
+        <v>20.58630561828613</v>
+      </c>
+      <c r="D1904">
+        <v>19.47366905212402</v>
+      </c>
+      <c r="E1904">
+        <v>22.5789794921875</v>
+      </c>
+    </row>
+    <row r="1905" spans="1:5">
+      <c r="A1905" s="1" t="s">
+        <v>1907</v>
+      </c>
+      <c r="C1905">
+        <v>12.10302829742432</v>
+      </c>
+      <c r="D1905">
+        <v>9.294498443603516</v>
+      </c>
+      <c r="E1905">
+        <v>13.84101581573486</v>
+      </c>
+    </row>
+    <row r="1906" spans="1:5">
+      <c r="A1906" s="1" t="s">
+        <v>1908</v>
+      </c>
+      <c r="C1906">
+        <v>7.851326465606689</v>
+      </c>
+      <c r="D1906">
+        <v>-69.68054962158203</v>
+      </c>
+      <c r="E1906">
+        <v>-68.89122009277344</v>
+      </c>
+    </row>
+    <row r="1907" spans="1:5">
+      <c r="A1907" s="1" t="s">
+        <v>1909</v>
+      </c>
+      <c r="C1907">
+        <v>7.136096477508545</v>
+      </c>
+      <c r="D1907">
+        <v>5.08370304107666</v>
+      </c>
+      <c r="E1907">
+        <v>6.099717140197754</v>
+      </c>
+    </row>
+    <row r="1908" spans="1:5">
+      <c r="A1908" s="1" t="s">
+        <v>1910</v>
+      </c>
+      <c r="C1908">
+        <v>0.4043438136577606</v>
+      </c>
+    </row>
+    <row r="1909" spans="1:5">
+      <c r="A1909" s="1" t="s">
+        <v>1911</v>
+      </c>
+      <c r="C1909">
+        <v>18.1339111328125</v>
+      </c>
+      <c r="D1909">
+        <v>3.263134002685547</v>
+      </c>
+      <c r="E1909">
+        <v>14.61375045776367</v>
+      </c>
+    </row>
+    <row r="1910" spans="1:5">
+      <c r="A1910" s="1" t="s">
+        <v>1912</v>
+      </c>
+      <c r="C1910">
+        <v>8.71646785736084</v>
+      </c>
+      <c r="D1910">
+        <v>4.783885478973389</v>
+      </c>
+      <c r="E1910">
+        <v>6.025421619415283</v>
+      </c>
+    </row>
+    <row r="1911" spans="1:5">
+      <c r="A1911" s="1" t="s">
+        <v>1913</v>
+      </c>
+      <c r="C1911">
+        <v>7.151594161987305</v>
+      </c>
+      <c r="D1911">
+        <v>2.854996204376221</v>
+      </c>
+      <c r="E1911">
+        <v>4.24039888381958</v>
+      </c>
+    </row>
+    <row r="1912" spans="1:5">
+      <c r="A1912" s="1" t="s">
+        <v>1914</v>
+      </c>
+      <c r="C1912">
+        <v>6.514657974243164</v>
+      </c>
+    </row>
+    <row r="1913" spans="1:5">
+      <c r="A1913" s="1" t="s">
+        <v>1915</v>
+      </c>
+      <c r="C1913">
+        <v>22.69301605224609</v>
+      </c>
+      <c r="D1913">
+        <v>22.69301605224609</v>
+      </c>
+      <c r="E1913">
+        <v>22.69301605224609</v>
+      </c>
+    </row>
+    <row r="1914" spans="1:5">
+      <c r="A1914" s="1" t="s">
+        <v>1916</v>
+      </c>
+      <c r="C1914">
+        <v>5.309175491333008</v>
+      </c>
+      <c r="D1914">
+        <v>3.499712944030762</v>
+      </c>
+      <c r="E1914">
+        <v>7.045456886291504</v>
+      </c>
+    </row>
+    <row r="1915" spans="1:5">
+      <c r="A1915" s="1" t="s">
+        <v>1917</v>
+      </c>
+      <c r="C1915">
+        <v>16.73989486694336</v>
+      </c>
+      <c r="D1915">
+        <v>6.554084300994873</v>
+      </c>
+      <c r="E1915">
+        <v>14.0118465423584</v>
+      </c>
+    </row>
+    <row r="1916" spans="1:5">
+      <c r="A1916" s="1" t="s">
+        <v>1918</v>
+      </c>
+      <c r="C1916">
+        <v>43.83361434936523</v>
+      </c>
+      <c r="D1916">
+        <v>33.55083847045898</v>
+      </c>
+      <c r="E1916">
+        <v>32.8935661315918</v>
+      </c>
+    </row>
+    <row r="1917" spans="1:5">
+      <c r="A1917" s="1" t="s">
+        <v>1919</v>
+      </c>
+      <c r="C1917">
+        <v>13.81486988067627</v>
+      </c>
+      <c r="D1917">
+        <v>20.50991439819336</v>
+      </c>
+      <c r="E1917">
+        <v>31.8197078704834</v>
+      </c>
+    </row>
+    <row r="1918" spans="1:5">
+      <c r="A1918" s="1" t="s">
+        <v>1920</v>
+      </c>
+      <c r="C1918">
+        <v>7.464813232421875</v>
+      </c>
+      <c r="D1918">
+        <v>-89.31671142578125</v>
+      </c>
+      <c r="E1918">
+        <v>-88.93804931640625</v>
+      </c>
+    </row>
+    <row r="1919" spans="1:5">
+      <c r="A1919" s="1" t="s">
+        <v>1921</v>
+      </c>
+      <c r="C1919">
+        <v>15.54188823699951</v>
+      </c>
+      <c r="D1919">
+        <v>12.45337200164795</v>
+      </c>
+      <c r="E1919">
+        <v>17.29500770568848</v>
+      </c>
+    </row>
+    <row r="1920" spans="1:5">
+      <c r="A1920" s="1" t="s">
+        <v>1922</v>
+      </c>
+      <c r="C1920">
+        <v>12.48497772216797</v>
+      </c>
+      <c r="D1920">
+        <v>-96.79002380371094</v>
+      </c>
+      <c r="E1920">
+        <v>2.522807598114014</v>
+      </c>
+    </row>
+    <row r="1921" spans="1:5">
+      <c r="A1921" s="1" t="s">
+        <v>1923</v>
+      </c>
+      <c r="C1921">
+        <v>42.09703063964844</v>
+      </c>
+      <c r="D1921">
+        <v>22.67024040222168</v>
+      </c>
+      <c r="E1921">
+        <v>36.33816909790039</v>
+      </c>
+    </row>
+    <row r="1922" spans="1:5">
+      <c r="A1922" s="1" t="s">
+        <v>1924</v>
+      </c>
+      <c r="C1922">
+        <v>11.00553321838379</v>
+      </c>
+      <c r="D1922">
+        <v>17.68236923217773</v>
+      </c>
+      <c r="E1922">
+        <v>20.61801719665527</v>
+      </c>
+    </row>
+    <row r="1923" spans="1:5">
+      <c r="A1923" s="1" t="s">
+        <v>1925</v>
+      </c>
+      <c r="C1923">
+        <v>9.618955612182617</v>
+      </c>
+      <c r="D1923">
+        <v>11.66934490203857</v>
+      </c>
+      <c r="E1923">
+        <v>11.94405364990234</v>
+      </c>
+    </row>
+    <row r="1924" spans="1:5">
+      <c r="A1924" s="1" t="s">
+        <v>1926</v>
+      </c>
+      <c r="C1924">
+        <v>7.006062030792236</v>
+      </c>
+      <c r="D1924">
+        <v>17.68236923217773</v>
+      </c>
+      <c r="E1924">
+        <v>20.61801719665527</v>
+      </c>
+    </row>
+    <row r="1925" spans="1:5">
+      <c r="A1925" s="1" t="s">
+        <v>1927</v>
+      </c>
+      <c r="C1925">
+        <v>9.17125415802002</v>
+      </c>
+      <c r="D1925">
+        <v>1625.178588867188</v>
+      </c>
+      <c r="E1925">
+        <v>2.40341854095459</v>
+      </c>
+    </row>
+    <row r="1926" spans="1:5">
+      <c r="A1926" s="1" t="s">
+        <v>1928</v>
+      </c>
+      <c r="C1926">
+        <v>8.000015258789062</v>
+      </c>
+      <c r="D1926">
+        <v>3.901735305786133</v>
+      </c>
+      <c r="E1926">
+        <v>5.82514762878418</v>
+      </c>
+    </row>
+    <row r="1927" spans="1:5">
+      <c r="A1927" s="1" t="s">
+        <v>1929</v>
+      </c>
+      <c r="C1927">
+        <v>18.00707054138184</v>
+      </c>
+      <c r="D1927" t="s">
+        <v>2024</v>
+      </c>
+      <c r="E1927" t="s">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="1928" spans="1:5">
+      <c r="A1928" s="1" t="s">
+        <v>1930</v>
+      </c>
+      <c r="C1928">
+        <v>8.043951034545898</v>
+      </c>
+      <c r="D1928">
+        <v>29602.5546875</v>
+      </c>
+      <c r="E1928">
+        <v>28343.052734375</v>
+      </c>
+    </row>
+    <row r="1929" spans="1:5">
+      <c r="A1929" s="1" t="s">
+        <v>1931</v>
+      </c>
+      <c r="C1929">
+        <v>11.10453128814697</v>
+      </c>
+      <c r="D1929">
+        <v>13.94086265563965</v>
+      </c>
+      <c r="E1929">
+        <v>25.02372550964355</v>
+      </c>
+    </row>
+    <row r="1930" spans="1:5">
+      <c r="A1930" s="1" t="s">
+        <v>1932</v>
+      </c>
+      <c r="C1930">
+        <v>2.330730676651001</v>
+      </c>
+      <c r="D1930">
+        <v>11.10030174255371</v>
+      </c>
+      <c r="E1930">
+        <v>12.53560543060303</v>
+      </c>
+    </row>
+    <row r="1931" spans="1:5">
+      <c r="A1931" s="1" t="s">
+        <v>1933</v>
+      </c>
+      <c r="C1931">
+        <v>3.449650526046753</v>
+      </c>
+      <c r="D1931">
+        <v>582.2554321289062</v>
+      </c>
+      <c r="E1931">
+        <v>21.28029632568359</v>
+      </c>
+    </row>
+    <row r="1932" spans="1:5">
+      <c r="A1932" s="1" t="s">
+        <v>1934</v>
+      </c>
+      <c r="C1932">
+        <v>17.85250663757324</v>
+      </c>
+      <c r="D1932">
+        <v>11.73312568664551</v>
+      </c>
+      <c r="E1932">
+        <v>12.11813449859619</v>
+      </c>
+    </row>
+    <row r="1933" spans="1:5">
+      <c r="A1933" s="1" t="s">
+        <v>1935</v>
+      </c>
+      <c r="C1933">
+        <v>10.27401828765869</v>
+      </c>
+      <c r="D1933">
+        <v>4.47040319442749</v>
+      </c>
+      <c r="E1933">
+        <v>7.517856597900391</v>
+      </c>
+    </row>
+    <row r="1934" spans="1:5">
+      <c r="A1934" s="1" t="s">
+        <v>1936</v>
+      </c>
+      <c r="C1934">
+        <v>11.84947204589844</v>
+      </c>
+      <c r="D1934">
+        <v>6.557873725891113</v>
+      </c>
+      <c r="E1934">
+        <v>8.900356292724609</v>
+      </c>
+    </row>
+    <row r="1935" spans="1:5">
+      <c r="A1935" s="1" t="s">
+        <v>1937</v>
+      </c>
+      <c r="C1935">
+        <v>15.08343124389648</v>
+      </c>
+      <c r="D1935">
+        <v>260.1383056640625</v>
+      </c>
+      <c r="E1935">
+        <v>283.6507568359375</v>
+      </c>
+    </row>
+    <row r="1936" spans="1:5">
+      <c r="A1936" s="1" t="s">
+        <v>1938</v>
+      </c>
+      <c r="C1936">
+        <v>20.92133712768555</v>
+      </c>
+      <c r="D1936">
+        <v>19.52780151367188</v>
+      </c>
+      <c r="E1936">
+        <v>45.95585632324219</v>
+      </c>
+    </row>
+    <row r="1937" spans="1:5">
+      <c r="A1937" s="1" t="s">
+        <v>1939</v>
+      </c>
+      <c r="C1937">
+        <v>0.4027154445648193</v>
+      </c>
+    </row>
+    <row r="1938" spans="1:5">
+      <c r="A1938" s="1" t="s">
+        <v>1940</v>
+      </c>
+      <c r="C1938">
+        <v>14.06790542602539</v>
+      </c>
+      <c r="D1938">
+        <v>9.393896102905273</v>
+      </c>
+      <c r="E1938">
+        <v>10.7661018371582</v>
+      </c>
+    </row>
+    <row r="1939" spans="1:5">
+      <c r="A1939" s="1" t="s">
+        <v>1941</v>
+      </c>
+      <c r="C1939">
+        <v>7.772922515869141</v>
+      </c>
+      <c r="D1939">
+        <v>5.264143466949463</v>
+      </c>
+      <c r="E1939">
+        <v>8.392663955688477</v>
+      </c>
+    </row>
+    <row r="1940" spans="1:5">
+      <c r="A1940" s="1" t="s">
+        <v>1942</v>
+      </c>
+      <c r="C1940">
+        <v>17.69796943664551</v>
+      </c>
+      <c r="D1940">
+        <v>1.137654304504395</v>
+      </c>
+      <c r="E1940">
+        <v>3.189161539077759</v>
+      </c>
+    </row>
+    <row r="1941" spans="1:5">
+      <c r="A1941" s="1" t="s">
+        <v>1943</v>
+      </c>
+      <c r="C1941">
+        <v>6.116208076477051</v>
+      </c>
+      <c r="D1941" t="s">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="1942" spans="1:5">
+      <c r="A1942" s="1" t="s">
+        <v>1944</v>
+      </c>
+      <c r="C1942">
+        <v>15.85595703125</v>
+      </c>
+      <c r="D1942">
+        <v>15.85595703125</v>
+      </c>
+      <c r="E1942">
+        <v>15.85595703125</v>
+      </c>
+    </row>
+    <row r="1943" spans="1:5">
+      <c r="A1943" s="1" t="s">
+        <v>1945</v>
+      </c>
+      <c r="C1943">
+        <v>4.366089820861816</v>
+      </c>
+      <c r="D1943">
+        <v>1.675084471702576</v>
+      </c>
+      <c r="E1943">
+        <v>3.053096055984497</v>
+      </c>
+    </row>
+    <row r="1944" spans="1:5">
+      <c r="A1944" s="1" t="s">
+        <v>1946</v>
+      </c>
+      <c r="C1944">
+        <v>21.99891471862793</v>
+      </c>
+      <c r="D1944">
+        <v>7.843052387237549</v>
+      </c>
+      <c r="E1944">
+        <v>18.04816818237305</v>
+      </c>
+    </row>
+    <row r="1945" spans="1:5">
+      <c r="A1945" s="1" t="s">
+        <v>1947</v>
+      </c>
+      <c r="C1945">
+        <v>29.99481391906738</v>
+      </c>
+      <c r="D1945">
+        <v>25.09633636474609</v>
+      </c>
+      <c r="E1945">
+        <v>26.42307090759277</v>
+      </c>
+    </row>
+    <row r="1946" spans="1:5">
+      <c r="A1946" s="1" t="s">
+        <v>1948</v>
+      </c>
+      <c r="C1946">
+        <v>29.35686111450195</v>
+      </c>
+      <c r="D1946">
+        <v>59.33816146850586</v>
+      </c>
+      <c r="E1946">
+        <v>70.34635925292969</v>
+      </c>
+    </row>
+    <row r="1947" spans="1:5">
+      <c r="A1947" s="1" t="s">
+        <v>1949</v>
+      </c>
+      <c r="C1947">
+        <v>1.436096549034119</v>
+      </c>
+      <c r="D1947">
+        <v>16.96403312683105</v>
+      </c>
+      <c r="E1947">
+        <v>21.28029632568359</v>
+      </c>
+    </row>
+    <row r="1948" spans="1:5">
+      <c r="A1948" s="1" t="s">
+        <v>1950</v>
+      </c>
+      <c r="C1948">
+        <v>11.4394702911377</v>
+      </c>
+      <c r="D1948">
+        <v>5.691106796264648</v>
+      </c>
+      <c r="E1948">
+        <v>7.954504013061523</v>
+      </c>
+    </row>
+    <row r="1949" spans="1:5">
+      <c r="A1949" s="1" t="s">
+        <v>1951</v>
+      </c>
+      <c r="C1949">
+        <v>11.00747966766357</v>
+      </c>
+      <c r="D1949">
+        <v>3064.06201171875</v>
+      </c>
+      <c r="E1949">
+        <v>5.331850051879883</v>
+      </c>
+    </row>
+    <row r="1950" spans="1:5">
+      <c r="A1950" s="1" t="s">
+        <v>1952</v>
+      </c>
+      <c r="C1950">
+        <v>18.76491355895996</v>
+      </c>
+      <c r="D1950">
+        <v>12.48562145233154</v>
+      </c>
+      <c r="E1950">
+        <v>13.15376281738281</v>
+      </c>
+    </row>
+    <row r="1951" spans="1:5">
+      <c r="A1951" s="1" t="s">
+        <v>1953</v>
+      </c>
+      <c r="C1951">
+        <v>9.910930633544922</v>
+      </c>
+      <c r="D1951">
+        <v>1630.290283203125</v>
+      </c>
+      <c r="E1951">
+        <v>1701.338256835938</v>
+      </c>
+    </row>
+    <row r="1952" spans="1:5">
+      <c r="A1952" s="1" t="s">
+        <v>1954</v>
+      </c>
+      <c r="C1952">
+        <v>8.229348182678223</v>
+      </c>
+      <c r="D1952">
+        <v>5.859855651855469</v>
+      </c>
+      <c r="E1952">
+        <v>7.219461917877197</v>
+      </c>
+    </row>
+    <row r="1953" spans="1:5">
+      <c r="A1953" s="1" t="s">
+        <v>1955</v>
+      </c>
+      <c r="C1953">
+        <v>70.09065246582031</v>
+      </c>
+      <c r="D1953">
+        <v>817.7852783203125</v>
+      </c>
+      <c r="E1953">
+        <v>867.1316528320312</v>
+      </c>
+    </row>
+    <row r="1954" spans="1:5">
+      <c r="A1954" s="1" t="s">
+        <v>1956</v>
+      </c>
+      <c r="C1954">
+        <v>11.60948181152344</v>
+      </c>
+      <c r="D1954">
+        <v>1.506057262420654</v>
+      </c>
+      <c r="E1954">
+        <v>6.103707790374756</v>
+      </c>
+    </row>
+    <row r="1955" spans="1:5">
+      <c r="A1955" s="1" t="s">
+        <v>1957</v>
+      </c>
+      <c r="C1955">
+        <v>-100</v>
+      </c>
+      <c r="D1955">
+        <v>-100</v>
+      </c>
+      <c r="E1955">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="1956" spans="1:5">
+      <c r="A1956" s="1" t="s">
+        <v>1958</v>
+      </c>
+      <c r="C1956">
+        <v>-100</v>
+      </c>
+      <c r="D1956">
+        <v>-100</v>
+      </c>
+      <c r="E1956">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="1957" spans="1:5">
+      <c r="A1957" s="1" t="s">
+        <v>1959</v>
+      </c>
+      <c r="C1957">
+        <v>0.3800555467605591</v>
+      </c>
+      <c r="D1957">
+        <v>17.14908790588379</v>
+      </c>
+      <c r="E1957">
+        <v>9.923203468322754</v>
+      </c>
+    </row>
+    <row r="1958" spans="1:5">
+      <c r="A1958" s="1" t="s">
+        <v>1960</v>
+      </c>
+      <c r="C1958">
+        <v>0.7732897996902466</v>
+      </c>
+      <c r="D1958">
+        <v>3.639347791671753</v>
+      </c>
+      <c r="E1958">
+        <v>39.60202789306641</v>
+      </c>
+    </row>
+    <row r="1959" spans="1:5">
+      <c r="A1959" s="1" t="s">
+        <v>1961</v>
+      </c>
+      <c r="C1959">
+        <v>2.592678546905518</v>
+      </c>
+      <c r="D1959">
+        <v>22.79574012756348</v>
+      </c>
+      <c r="E1959">
+        <v>24.56206703186035</v>
+      </c>
+    </row>
+    <row r="1960" spans="1:5">
+      <c r="A1960" s="1" t="s">
+        <v>1962</v>
+      </c>
+      <c r="C1960">
+        <v>4.663471698760986</v>
+      </c>
+      <c r="D1960">
+        <v>20.24318695068359</v>
+      </c>
+      <c r="E1960">
+        <v>522.3865356445312</v>
+      </c>
+    </row>
+    <row r="1961" spans="1:5">
+      <c r="A1961" s="1" t="s">
+        <v>1963</v>
+      </c>
+      <c r="C1961">
+        <v>24.07377815246582</v>
+      </c>
+      <c r="D1961">
+        <v>39.88592529296875</v>
+      </c>
+      <c r="E1961">
+        <v>35.90115737915039</v>
+      </c>
+    </row>
+    <row r="1962" spans="1:5">
+      <c r="A1962" s="1" t="s">
+        <v>1964</v>
+      </c>
+      <c r="C1962">
+        <v>3.406226396560669</v>
+      </c>
+      <c r="D1962">
+        <v>1.574849605560303</v>
+      </c>
+      <c r="E1962">
+        <v>3.970083236694336</v>
+      </c>
+    </row>
+    <row r="1963" spans="1:5">
+      <c r="A1963" s="1" t="s">
+        <v>1965</v>
+      </c>
+      <c r="C1963">
+        <v>1.955814480781555</v>
+      </c>
+      <c r="D1963">
+        <v>2.318260431289673</v>
+      </c>
+      <c r="E1963">
+        <v>3.032900333404541</v>
+      </c>
+    </row>
+    <row r="1964" spans="1:5">
+      <c r="A1964" s="1" t="s">
+        <v>1966</v>
+      </c>
+      <c r="C1964">
+        <v>9.736428260803223</v>
+      </c>
+      <c r="D1964">
+        <v>21.3304615020752</v>
+      </c>
+      <c r="E1964">
+        <v>22.41931343078613</v>
+      </c>
+    </row>
+    <row r="1965" spans="1:5">
+      <c r="A1965" s="1" t="s">
+        <v>1967</v>
+      </c>
+      <c r="C1965">
+        <v>9.909064292907715</v>
+      </c>
+      <c r="D1965">
+        <v>19.69295883178711</v>
+      </c>
+      <c r="E1965">
+        <v>39.79788970947266</v>
+      </c>
+    </row>
+    <row r="1966" spans="1:5">
+      <c r="A1966" s="1" t="s">
+        <v>1968</v>
+      </c>
+      <c r="C1966">
+        <v>0.4011001586914062</v>
+      </c>
+      <c r="D1966" t="s">
+        <v>2024</v>
+      </c>
+      <c r="E1966" t="s">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="1967" spans="1:5">
+      <c r="A1967" s="1" t="s">
+        <v>1969</v>
+      </c>
+      <c r="C1967">
+        <v>7.203895568847656</v>
+      </c>
+      <c r="D1967">
+        <v>22.62425994873047</v>
+      </c>
+      <c r="E1967">
+        <v>17.17148017883301</v>
+      </c>
+    </row>
+    <row r="1968" spans="1:5">
+      <c r="A1968" s="1" t="s">
+        <v>1970</v>
+      </c>
+      <c r="C1968">
+        <v>7.024309635162354</v>
+      </c>
+      <c r="D1968">
+        <v>8.091565132141113</v>
+      </c>
+      <c r="E1968">
+        <v>11.07551765441895</v>
+      </c>
+    </row>
+    <row r="1969" spans="1:5">
+      <c r="A1969" s="1" t="s">
+        <v>1971</v>
+      </c>
+      <c r="C1969">
+        <v>4.059111595153809</v>
+      </c>
+      <c r="D1969">
+        <v>7.404355049133301</v>
+      </c>
+      <c r="E1969">
+        <v>9.057644844055176</v>
+      </c>
+    </row>
+    <row r="1970" spans="1:5">
+      <c r="A1970" s="1" t="s">
+        <v>1972</v>
+      </c>
+      <c r="C1970">
+        <v>-100</v>
+      </c>
+      <c r="D1970">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="1971" spans="1:5">
+      <c r="A1971" s="1" t="s">
+        <v>1973</v>
+      </c>
+      <c r="C1971">
+        <v>0</v>
+      </c>
+      <c r="D1971">
+        <v>0</v>
+      </c>
+      <c r="E1971">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1972" spans="1:5">
+      <c r="A1972" s="1" t="s">
+        <v>1974</v>
+      </c>
+      <c r="C1972">
+        <v>2.626588106155396</v>
+      </c>
+      <c r="D1972">
+        <v>2.276456356048584</v>
+      </c>
+      <c r="E1972">
+        <v>3.594907522201538</v>
+      </c>
+    </row>
+    <row r="1973" spans="1:5">
+      <c r="A1973" s="1" t="s">
+        <v>1975</v>
+      </c>
+      <c r="C1973">
+        <v>9.776825904846191</v>
+      </c>
+      <c r="D1973">
+        <v>9.25357723236084</v>
+      </c>
+      <c r="E1973">
+        <v>20.41475105285645</v>
+      </c>
+    </row>
+    <row r="1974" spans="1:5">
+      <c r="A1974" s="1" t="s">
+        <v>1976</v>
+      </c>
+      <c r="C1974">
+        <v>-3.59332275390625</v>
+      </c>
+      <c r="D1974">
+        <v>-42.47799301147461</v>
+      </c>
+      <c r="E1974">
+        <v>4.293241024017334</v>
+      </c>
+    </row>
+    <row r="1975" spans="1:5">
+      <c r="A1975" s="1" t="s">
+        <v>1977</v>
+      </c>
+      <c r="C1975">
+        <v>11.90443992614746</v>
+      </c>
+      <c r="D1975">
+        <v>41.63571166992188</v>
+      </c>
+      <c r="E1975">
+        <v>46.91225433349609</v>
+      </c>
+    </row>
+    <row r="1976" spans="1:5">
+      <c r="A1976" s="1" t="s">
+        <v>1978</v>
+      </c>
+      <c r="C1976">
+        <v>2.393425941467285</v>
+      </c>
+      <c r="D1976">
+        <v>848.453125</v>
+      </c>
+      <c r="E1976">
+        <v>740.5821533203125</v>
+      </c>
+    </row>
+    <row r="1977" spans="1:5">
+      <c r="A1977" s="1" t="s">
+        <v>1979</v>
+      </c>
+      <c r="C1977">
+        <v>3.402884721755981</v>
+      </c>
+      <c r="D1977">
+        <v>10.24697780609131</v>
+      </c>
+      <c r="E1977">
+        <v>11.45570468902588</v>
+      </c>
+    </row>
+    <row r="1978" spans="1:5">
+      <c r="A1978" s="1" t="s">
+        <v>1980</v>
+      </c>
+      <c r="C1978">
+        <v>2.553990125656128</v>
+      </c>
+      <c r="D1978">
+        <v>6.50149393081665</v>
+      </c>
+      <c r="E1978">
+        <v>6.499076843261719</v>
+      </c>
+    </row>
+    <row r="1979" spans="1:5">
+      <c r="A1979" s="1" t="s">
+        <v>1981</v>
+      </c>
+      <c r="C1979">
+        <v>13.32607173919678</v>
+      </c>
+      <c r="D1979">
+        <v>30.6917610168457</v>
+      </c>
+      <c r="E1979">
+        <v>24.96785736083984</v>
+      </c>
+    </row>
+    <row r="1980" spans="1:5">
+      <c r="A1980" s="1" t="s">
+        <v>1982</v>
+      </c>
+      <c r="C1980">
+        <v>-94.15592956542969</v>
+      </c>
+      <c r="D1980">
+        <v>-92.28206634521484</v>
+      </c>
+      <c r="E1980">
+        <v>-92.04338073730469</v>
+      </c>
+    </row>
+    <row r="1981" spans="1:5">
+      <c r="A1981" s="1" t="s">
+        <v>1983</v>
+      </c>
+      <c r="C1981">
+        <v>-81.09664154052734</v>
+      </c>
+      <c r="D1981">
+        <v>-79.90297698974609</v>
+      </c>
+      <c r="E1981">
+        <v>-76.48257446289062</v>
+      </c>
+    </row>
+    <row r="1982" spans="1:5">
+      <c r="A1982" s="1" t="s">
+        <v>1984</v>
+      </c>
+      <c r="C1982">
+        <v>13.64478874206543</v>
+      </c>
+      <c r="D1982">
+        <v>26.05955505371094</v>
+      </c>
+      <c r="E1982">
+        <v>23.21361351013184</v>
+      </c>
+    </row>
+    <row r="1983" spans="1:5">
+      <c r="A1983" s="1" t="s">
+        <v>1985</v>
+      </c>
+      <c r="C1983">
+        <v>2.479773044586182</v>
+      </c>
+      <c r="D1983">
+        <v>5.608715534210205</v>
+      </c>
+      <c r="E1983">
+        <v>9.677143096923828</v>
+      </c>
+    </row>
+    <row r="1984" spans="1:5">
+      <c r="A1984" s="1" t="s">
+        <v>1986</v>
+      </c>
+      <c r="C1984" t="s">
+        <v>2024</v>
+      </c>
+      <c r="D1984" t="s">
+        <v>2024</v>
+      </c>
+      <c r="E1984" t="s">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="1985" spans="1:5">
+      <c r="A1985" s="1" t="s">
+        <v>1987</v>
+      </c>
+      <c r="C1985" t="s">
+        <v>2024</v>
+      </c>
+      <c r="D1985" t="s">
+        <v>2024</v>
+      </c>
+      <c r="E1985" t="s">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="1986" spans="1:5">
+      <c r="A1986" s="1" t="s">
+        <v>1988</v>
+      </c>
+      <c r="C1986">
+        <v>0.3451904952526093</v>
+      </c>
+      <c r="D1986">
+        <v>3.687396287918091</v>
+      </c>
+      <c r="E1986">
+        <v>-99.46699523925781</v>
+      </c>
+    </row>
+    <row r="1987" spans="1:5">
+      <c r="A1987" s="1" t="s">
+        <v>1989</v>
+      </c>
+      <c r="C1987">
+        <v>0.3129008412361145</v>
+      </c>
+      <c r="D1987">
+        <v>50.03044128417969</v>
+      </c>
+      <c r="E1987">
+        <v>72.09524536132812</v>
+      </c>
+    </row>
+    <row r="1988" spans="1:5">
+      <c r="A1988" s="1" t="s">
+        <v>1990</v>
+      </c>
+      <c r="C1988">
+        <v>2.811794519424438</v>
+      </c>
+      <c r="D1988">
+        <v>17.21816825866699</v>
+      </c>
+      <c r="E1988">
+        <v>18.66708755493164</v>
+      </c>
+    </row>
+    <row r="1989" spans="1:5">
+      <c r="A1989" s="1" t="s">
+        <v>1991</v>
+      </c>
+      <c r="C1989">
+        <v>3.052391052246094</v>
+      </c>
+      <c r="D1989">
+        <v>6.871538639068604</v>
+      </c>
+      <c r="E1989">
+        <v>-77.92270660400391</v>
+      </c>
+    </row>
+    <row r="1990" spans="1:5">
+      <c r="A1990" s="1" t="s">
+        <v>1992</v>
+      </c>
+      <c r="C1990">
+        <v>19.40279197692871</v>
+      </c>
+      <c r="D1990">
+        <v>-100</v>
+      </c>
+      <c r="E1990">
+        <v>17.5788402557373</v>
+      </c>
+    </row>
+    <row r="1991" spans="1:5">
+      <c r="A1991" s="1" t="s">
+        <v>1993</v>
+      </c>
+      <c r="C1991">
+        <v>2.188337564468384</v>
+      </c>
+      <c r="D1991">
+        <v>5.889395713806152</v>
+      </c>
+      <c r="E1991">
+        <v>8.623011589050293</v>
+      </c>
+    </row>
+    <row r="1992" spans="1:5">
+      <c r="A1992" s="1" t="s">
+        <v>1994</v>
+      </c>
+      <c r="C1992">
+        <v>1.177012801170349</v>
+      </c>
+      <c r="D1992">
+        <v>2.77308201789856</v>
+      </c>
+      <c r="E1992">
+        <v>4.479422569274902</v>
+      </c>
+    </row>
+    <row r="1993" spans="1:5">
+      <c r="A1993" s="1" t="s">
+        <v>1995</v>
+      </c>
+      <c r="C1993">
+        <v>-20.85583114624023</v>
+      </c>
+      <c r="D1993">
+        <v>-20.57200622558594</v>
+      </c>
+      <c r="E1993">
+        <v>-19.89276695251465</v>
+      </c>
+    </row>
+    <row r="1994" spans="1:5">
+      <c r="A1994" s="1" t="s">
+        <v>1996</v>
+      </c>
+      <c r="C1994">
+        <v>17.93227767944336</v>
+      </c>
+      <c r="D1994">
+        <v>20.84437561035156</v>
+      </c>
+      <c r="E1994">
+        <v>40.6120719909668</v>
+      </c>
+    </row>
+    <row r="1995" spans="1:5">
+      <c r="A1995" s="1" t="s">
+        <v>1997</v>
+      </c>
+      <c r="C1995">
+        <v>0.399497777223587</v>
+      </c>
+      <c r="D1995">
+        <v>3.639297723770142</v>
+      </c>
+      <c r="E1995">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="1996" spans="1:5">
+      <c r="A1996" s="1" t="s">
+        <v>1998</v>
+      </c>
+      <c r="C1996">
+        <v>9.841521263122559</v>
+      </c>
+      <c r="D1996">
+        <v>11.68402194976807</v>
+      </c>
+      <c r="E1996">
+        <v>9.311573028564453</v>
+      </c>
+    </row>
+    <row r="1997" spans="1:5">
+      <c r="A1997" s="1" t="s">
+        <v>1999</v>
+      </c>
+      <c r="C1997">
+        <v>3.434762477874756</v>
+      </c>
+      <c r="D1997">
+        <v>5.923059940338135</v>
+      </c>
+      <c r="E1997">
+        <v>7.93340015411377</v>
+      </c>
+    </row>
+    <row r="1998" spans="1:5">
+      <c r="A1998" s="1" t="s">
+        <v>2000</v>
+      </c>
+      <c r="C1998">
+        <v>3.793755292892456</v>
+      </c>
+      <c r="D1998">
+        <v>6.665188312530518</v>
+      </c>
+      <c r="E1998">
+        <v>8.342541694641113</v>
+      </c>
+    </row>
+    <row r="1999" spans="1:5">
+      <c r="A1999" s="1" t="s">
+        <v>2001</v>
+      </c>
+      <c r="C1999" t="s">
+        <v>2024</v>
+      </c>
+      <c r="D1999" t="s">
+        <v>2024</v>
+      </c>
+      <c r="E1999" t="s">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="2000" spans="1:5">
+      <c r="A2000" s="1" t="s">
+        <v>2002</v>
+      </c>
+      <c r="C2000">
+        <v>0</v>
+      </c>
+      <c r="D2000">
+        <v>0</v>
+      </c>
+      <c r="E2000">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2001" spans="1:5">
+      <c r="A2001" s="1" t="s">
+        <v>2003</v>
+      </c>
+      <c r="C2001">
+        <v>2.583913564682007</v>
+      </c>
+      <c r="D2001">
+        <v>3.495292186737061</v>
+      </c>
+      <c r="E2001">
+        <v>4.579998970031738</v>
+      </c>
+    </row>
+    <row r="2002" spans="1:5">
+      <c r="A2002" s="1" t="s">
+        <v>2004</v>
+      </c>
+      <c r="C2002">
+        <v>11.3723611831665</v>
+      </c>
+      <c r="D2002">
+        <v>6.747061252593994</v>
+      </c>
+      <c r="E2002">
+        <v>10.55101108551025</v>
+      </c>
+    </row>
+    <row r="2003" spans="1:5">
+      <c r="A2003" s="1" t="s">
+        <v>2005</v>
+      </c>
+      <c r="C2003">
+        <v>7.819004058837891</v>
+      </c>
+      <c r="D2003">
+        <v>90.38050842285156</v>
+      </c>
+      <c r="E2003">
+        <v>5.406156063079834</v>
+      </c>
+    </row>
+    <row r="2004" spans="1:5">
+      <c r="A2004" s="1" t="s">
+        <v>2006</v>
+      </c>
+      <c r="C2004">
+        <v>11.47342491149902</v>
+      </c>
+      <c r="D2004">
+        <v>19.12232971191406</v>
+      </c>
+      <c r="E2004">
+        <v>18.26775741577148</v>
+      </c>
+    </row>
+    <row r="2005" spans="1:5">
+      <c r="A2005" s="1" t="s">
+        <v>2007</v>
+      </c>
+      <c r="C2005">
+        <v>1.28216540813446</v>
+      </c>
+      <c r="D2005">
+        <v>4.958264350891113</v>
+      </c>
+      <c r="E2005">
+        <v>-83.65345764160156</v>
+      </c>
+    </row>
+    <row r="2006" spans="1:5">
+      <c r="A2006" s="1" t="s">
+        <v>2008</v>
+      </c>
+      <c r="C2006">
+        <v>8.433977127075195</v>
+      </c>
+      <c r="D2006">
+        <v>9.899059295654297</v>
+      </c>
+      <c r="E2006">
+        <v>10.91853713989258</v>
+      </c>
+    </row>
+    <row r="2007" spans="1:5">
+      <c r="A2007" s="1" t="s">
+        <v>2009</v>
+      </c>
+      <c r="C2007">
+        <v>4.245435237884521</v>
+      </c>
+      <c r="D2007">
+        <v>3.101895809173584</v>
+      </c>
+      <c r="E2007">
+        <v>9.799628257751465</v>
+      </c>
+    </row>
+    <row r="2008" spans="1:5">
+      <c r="A2008" s="1" t="s">
+        <v>2010</v>
+      </c>
+      <c r="C2008">
+        <v>9.317231178283691</v>
+      </c>
+      <c r="D2008">
+        <v>11.17052459716797</v>
+      </c>
+      <c r="E2008">
+        <v>7.177564144134521</v>
+      </c>
+    </row>
+    <row r="2009" spans="1:5">
+      <c r="A2009" s="1" t="s">
+        <v>2011</v>
+      </c>
+      <c r="C2009">
+        <v>1090.74609375</v>
+      </c>
+      <c r="D2009">
+        <v>973.3925170898438</v>
+      </c>
+      <c r="E2009">
+        <v>885.6720581054688</v>
+      </c>
+    </row>
+    <row r="2010" spans="1:5">
+      <c r="A2010" s="1" t="s">
+        <v>2012</v>
+      </c>
+      <c r="C2010">
+        <v>350.5106811523438</v>
+      </c>
+      <c r="D2010">
+        <v>362.3034362792969</v>
+      </c>
+      <c r="E2010">
+        <v>314.7750854492188</v>
+      </c>
+    </row>
+    <row r="2011" spans="1:5">
+      <c r="A2011" s="1" t="s">
+        <v>2013</v>
+      </c>
+      <c r="C2011">
+        <v>15.91605186462402</v>
+      </c>
+      <c r="D2011">
+        <v>15.83144378662109</v>
+      </c>
+      <c r="E2011">
+        <v>15.29609203338623</v>
+      </c>
+    </row>
+    <row r="2012" spans="1:5">
+      <c r="A2012" s="1" t="s">
+        <v>2014</v>
+      </c>
+      <c r="C2012">
+        <v>10.05361270904541</v>
+      </c>
+      <c r="D2012">
+        <v>6.979473114013672</v>
+      </c>
+      <c r="E2012">
+        <v>12.2914342880249</v>
       </c>
     </row>
   </sheetData>
